--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E343"/>
+  <dimension ref="A1:E344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6537,6 +6537,25 @@
         <v>6.9639</v>
       </c>
     </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-03-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>155500</v>
+      </c>
+      <c r="C344" t="n">
+        <v>22537.21</v>
+      </c>
+      <c r="D344" t="n">
+        <v>19944.44</v>
+      </c>
+      <c r="E344" t="n">
+        <v>6.8728</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E344"/>
+  <dimension ref="A1:E345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6556,6 +6556,25 @@
         <v>6.8728</v>
       </c>
     </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-03-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>152500</v>
+      </c>
+      <c r="C345" t="n">
+        <v>22067.87</v>
+      </c>
+      <c r="D345" t="n">
+        <v>19529.09</v>
+      </c>
+      <c r="E345" t="n">
+        <v>6.873</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E345"/>
+  <dimension ref="A1:E346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6575,6 +6575,25 @@
         <v>6.873</v>
       </c>
     </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-03-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>149000</v>
+      </c>
+      <c r="C346" t="n">
+        <v>21589.82</v>
+      </c>
+      <c r="D346" t="n">
+        <v>19106.04</v>
+      </c>
+      <c r="E346" t="n">
+        <v>6.9004</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E346"/>
+  <dimension ref="A1:E347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6594,6 +6594,25 @@
         <v>6.9004</v>
       </c>
     </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-03-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>149000</v>
+      </c>
+      <c r="C347" t="n">
+        <v>21589.82</v>
+      </c>
+      <c r="D347" t="n">
+        <v>19106.04</v>
+      </c>
+      <c r="E347" t="n">
+        <v>6.8864</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E347"/>
+  <dimension ref="A1:E348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6613,6 +6613,25 @@
         <v>6.8864</v>
       </c>
     </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-03-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>149000</v>
+      </c>
+      <c r="C348" t="n">
+        <v>21589.82</v>
+      </c>
+      <c r="D348" t="n">
+        <v>19106.04</v>
+      </c>
+      <c r="E348" t="n">
+        <v>6.8864</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E348"/>
+  <dimension ref="A1:E349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6632,6 +6632,25 @@
         <v>6.8864</v>
       </c>
     </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-03-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>146500</v>
+      </c>
+      <c r="C349" t="n">
+        <v>21146.99</v>
+      </c>
+      <c r="D349" t="n">
+        <v>18714.15</v>
+      </c>
+      <c r="E349" t="n">
+        <v>6.8864</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E349"/>
+  <dimension ref="A1:E350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6651,6 +6651,25 @@
         <v>6.8864</v>
       </c>
     </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-03-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>147500</v>
+      </c>
+      <c r="C350" t="n">
+        <v>21350.51</v>
+      </c>
+      <c r="D350" t="n">
+        <v>18894.26</v>
+      </c>
+      <c r="E350" t="n">
+        <v>6.8805</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E350"/>
+  <dimension ref="A1:E351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6670,6 +6670,25 @@
         <v>6.8805</v>
       </c>
     </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-03-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>152500</v>
+      </c>
+      <c r="C351" t="n">
+        <v>22088.64</v>
+      </c>
+      <c r="D351" t="n">
+        <v>19547.47</v>
+      </c>
+      <c r="E351" t="n">
+        <v>6.8927</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E351"/>
+  <dimension ref="A1:E352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6689,6 +6689,25 @@
         <v>6.8927</v>
       </c>
     </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>156500</v>
+      </c>
+      <c r="C352" t="n">
+        <v>22612.34</v>
+      </c>
+      <c r="D352" t="n">
+        <v>20010.92</v>
+      </c>
+      <c r="E352" t="n">
+        <v>6.9015</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E352"/>
+  <dimension ref="A1:E353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6708,6 +6708,25 @@
         <v>6.9015</v>
       </c>
     </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-03-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>158000</v>
+      </c>
+      <c r="C353" t="n">
+        <v>22781.67</v>
+      </c>
+      <c r="D353" t="n">
+        <v>20160.77</v>
+      </c>
+      <c r="E353" t="n">
+        <v>6.9114</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E353"/>
+  <dimension ref="A1:E354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6727,6 +6727,25 @@
         <v>6.9114</v>
       </c>
     </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>158000</v>
+      </c>
+      <c r="C354" t="n">
+        <v>22781.67</v>
+      </c>
+      <c r="D354" t="n">
+        <v>20160.77</v>
+      </c>
+      <c r="E354" t="n">
+        <v>6.9118</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E354"/>
+  <dimension ref="A1:E355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6746,6 +6746,25 @@
         <v>6.9118</v>
       </c>
     </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-03-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>158000</v>
+      </c>
+      <c r="C355" t="n">
+        <v>22781.67</v>
+      </c>
+      <c r="D355" t="n">
+        <v>20160.77</v>
+      </c>
+      <c r="E355" t="n">
+        <v>6.9118</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E355"/>
+  <dimension ref="A1:E356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6765,6 +6765,25 @@
         <v>6.9118</v>
       </c>
     </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-03-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>164500</v>
+      </c>
+      <c r="C356" t="n">
+        <v>23719.92</v>
+      </c>
+      <c r="D356" t="n">
+        <v>20991.08</v>
+      </c>
+      <c r="E356" t="n">
+        <v>6.9118</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E356"/>
+  <dimension ref="A1:E357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6784,6 +6784,25 @@
         <v>6.9118</v>
       </c>
     </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-04-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>174500</v>
+      </c>
+      <c r="C357" t="n">
+        <v>25438.43</v>
+      </c>
+      <c r="D357" t="n">
+        <v>22511.89</v>
+      </c>
+      <c r="E357" t="n">
+        <v>6.8374</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E357"/>
+  <dimension ref="A1:E358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6803,6 +6803,25 @@
         <v>6.8374</v>
       </c>
     </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-04-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>177000</v>
+      </c>
+      <c r="C358" t="n">
+        <v>25790.47</v>
+      </c>
+      <c r="D358" t="n">
+        <v>22823.43</v>
+      </c>
+      <c r="E358" t="n">
+        <v>6.8383</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E358"/>
+  <dimension ref="A1:E359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6822,6 +6822,25 @@
         <v>6.8383</v>
       </c>
     </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-05-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>177000</v>
+      </c>
+      <c r="C359" t="n">
+        <v>25790.47</v>
+      </c>
+      <c r="D359" t="n">
+        <v>22823.43</v>
+      </c>
+      <c r="E359" t="n">
+        <v>6.8282</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E359"/>
+  <dimension ref="A1:E360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6841,6 +6841,25 @@
         <v>6.8282</v>
       </c>
     </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-05-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>177000</v>
+      </c>
+      <c r="C360" t="n">
+        <v>25790.47</v>
+      </c>
+      <c r="D360" t="n">
+        <v>22823.43</v>
+      </c>
+      <c r="E360" t="n">
+        <v>6.8283</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E360"/>
+  <dimension ref="A1:E361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6860,6 +6860,25 @@
         <v>6.8283</v>
       </c>
     </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-05-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>177000</v>
+      </c>
+      <c r="C361" t="n">
+        <v>25790.47</v>
+      </c>
+      <c r="D361" t="n">
+        <v>22823.43</v>
+      </c>
+      <c r="E361" t="n">
+        <v>6.8283</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E361"/>
+  <dimension ref="A1:E362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6879,6 +6879,25 @@
         <v>6.8283</v>
       </c>
     </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-05-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>177000</v>
+      </c>
+      <c r="C362" t="n">
+        <v>25790.47</v>
+      </c>
+      <c r="D362" t="n">
+        <v>22823.43</v>
+      </c>
+      <c r="E362" t="n">
+        <v>6.8282</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E362"/>
+  <dimension ref="A1:E363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6898,6 +6898,25 @@
         <v>6.8282</v>
       </c>
     </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-05-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>177000</v>
+      </c>
+      <c r="C363" t="n">
+        <v>25790.47</v>
+      </c>
+      <c r="D363" t="n">
+        <v>22823.43</v>
+      </c>
+      <c r="E363" t="n">
+        <v>6.8302</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E363"/>
+  <dimension ref="A1:E364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6917,6 +6917,25 @@
         <v>6.8302</v>
       </c>
     </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-05-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>187500</v>
+      </c>
+      <c r="C364" t="n">
+        <v>27417.49</v>
+      </c>
+      <c r="D364" t="n">
+        <v>24263.27</v>
+      </c>
+      <c r="E364" t="n">
+        <v>6.8304</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E364"/>
+  <dimension ref="A1:E365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6936,6 +6936,25 @@
         <v>6.8304</v>
       </c>
     </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>190500</v>
+      </c>
+      <c r="C365" t="n">
+        <v>27911.27</v>
+      </c>
+      <c r="D365" t="n">
+        <v>24700.24</v>
+      </c>
+      <c r="E365" t="n">
+        <v>6.8113</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E365"/>
+  <dimension ref="A1:E366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6955,6 +6955,25 @@
         <v>6.8113</v>
       </c>
     </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-05-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>194000</v>
+      </c>
+      <c r="C366" t="n">
+        <v>28411.59</v>
+      </c>
+      <c r="D366" t="n">
+        <v>25143</v>
+      </c>
+      <c r="E366" t="n">
+        <v>6.8008</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E366"/>
+  <dimension ref="A1:E367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6974,6 +6974,25 @@
         <v>6.8008</v>
       </c>
     </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-05-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>194000</v>
+      </c>
+      <c r="C367" t="n">
+        <v>28411.59</v>
+      </c>
+      <c r="D367" t="n">
+        <v>25143</v>
+      </c>
+      <c r="E367" t="n">
+        <v>6.8008</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E367"/>
+  <dimension ref="A1:E368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6993,6 +6993,25 @@
         <v>6.8008</v>
       </c>
     </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-05-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>195250</v>
+      </c>
+      <c r="C368" t="n">
+        <v>28594.65</v>
+      </c>
+      <c r="D368" t="n">
+        <v>25305</v>
+      </c>
+      <c r="E368" t="n">
+        <v>6.8008</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E368"/>
+  <dimension ref="A1:E369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7012,6 +7012,25 @@
         <v>6.8008</v>
       </c>
     </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-05-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>200000</v>
+      </c>
+      <c r="C369" t="n">
+        <v>29362.11</v>
+      </c>
+      <c r="D369" t="n">
+        <v>25984.17</v>
+      </c>
+      <c r="E369" t="n">
+        <v>6.795</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E369"/>
+  <dimension ref="A1:N370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,22 +440,67 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Original (CNY/mt)</t>
+          <t>Li Original (CNY/mt)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>VAT Included (USD/mt)</t>
+          <t>Li VAT Incl (USD/mt)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>VAT Excluded (USD/mt)</t>
+          <t>Li VAT Excl (USD/mt)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>USD/CNY</t>
+          <t>Cu Original (CNY/mt)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Cu VAT Incl (USD/mt)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cu VAT Excl (USD/mt)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Al Original (CNY/mt)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Al VAT Incl (USD/mt)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Al VAT Excl (USD/mt)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LiPF6 Original (CNY/mt)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LiPF6 VAT Incl (USD/mt)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LiPF6 VAT Excl (USD/mt)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Exchange Rate (USD/CNY)</t>
         </is>
       </c>
     </row>
@@ -469,6 +514,15 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -480,6 +534,15 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -491,6 +554,15 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -502,6 +574,15 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -513,6 +594,15 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -524,6 +614,15 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -535,6 +634,15 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -546,6 +654,15 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -557,6 +674,15 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -568,6 +694,15 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -579,6 +714,15 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -590,6 +734,15 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -601,6 +754,15 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -612,6 +774,15 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -623,6 +794,15 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -634,6 +814,15 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -645,6 +834,15 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -656,6 +854,15 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -667,6 +874,15 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -678,6 +894,15 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -689,6 +914,15 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -700,6 +934,15 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -711,6 +954,15 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -722,6 +974,15 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -733,6 +994,15 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -744,6 +1014,15 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -755,6 +1034,15 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -766,6 +1054,15 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -777,6 +1074,15 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -788,6 +1094,15 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -799,6 +1114,15 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -810,6 +1134,15 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -821,6 +1154,15 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -832,6 +1174,15 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -843,6 +1194,15 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -854,6 +1214,15 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -865,6 +1234,15 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -876,6 +1254,15 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -887,6 +1274,15 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -898,6 +1294,15 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -909,6 +1314,15 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -920,6 +1334,15 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -931,6 +1354,15 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -942,6 +1374,15 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -953,6 +1394,15 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -964,6 +1414,15 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -975,6 +1434,15 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -986,6 +1454,15 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -997,6 +1474,15 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -1008,6 +1494,15 @@
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -1019,6 +1514,15 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -1030,6 +1534,15 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -1044,9 +1557,16 @@
       <c r="D54" t="n">
         <v>9267.469999999999</v>
       </c>
-      <c r="E54" t="n">
-        <v>7.043</v>
-      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -1061,9 +1581,16 @@
       <c r="D55" t="n">
         <v>9281.35</v>
       </c>
-      <c r="E55" t="n">
-        <v>7.0318</v>
-      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1080,9 +1607,16 @@
       <c r="D56" t="n">
         <v>9446.139999999999</v>
       </c>
-      <c r="E56" t="n">
-        <v>7.0328</v>
-      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1099,9 +1633,16 @@
       <c r="D57" t="n">
         <v>9425.65</v>
       </c>
-      <c r="E57" t="n">
-        <v>7.0121</v>
-      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1118,9 +1659,16 @@
       <c r="D58" t="n">
         <v>9524.4</v>
       </c>
-      <c r="E58" t="n">
-        <v>7.0113</v>
-      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1137,9 +1685,16 @@
       <c r="D59" t="n">
         <v>9524.4</v>
       </c>
-      <c r="E59" t="n">
-        <v>7.0114</v>
-      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1156,9 +1711,16 @@
       <c r="D60" t="n">
         <v>9524.4</v>
       </c>
-      <c r="E60" t="n">
-        <v>7.0117</v>
-      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1175,9 +1737,16 @@
       <c r="D61" t="n">
         <v>9519.370000000001</v>
       </c>
-      <c r="E61" t="n">
-        <v>7.0121</v>
-      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1194,9 +1763,16 @@
       <c r="D62" t="n">
         <v>9519.370000000001</v>
       </c>
-      <c r="E62" t="n">
-        <v>7.0284</v>
-      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1213,9 +1789,16 @@
       <c r="D63" t="n">
         <v>9519.370000000001</v>
       </c>
-      <c r="E63" t="n">
-        <v>7.038</v>
-      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1232,9 +1815,16 @@
       <c r="D64" t="n">
         <v>9519.370000000001</v>
       </c>
-      <c r="E64" t="n">
-        <v>7.0457</v>
-      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1251,9 +1841,16 @@
       <c r="D65" t="n">
         <v>9519.370000000001</v>
       </c>
-      <c r="E65" t="n">
-        <v>7.0494</v>
-      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1270,9 +1867,16 @@
       <c r="D66" t="n">
         <v>9519.370000000001</v>
       </c>
-      <c r="E66" t="n">
-        <v>7.0184</v>
-      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1289,9 +1893,16 @@
       <c r="D67" t="n">
         <v>9519.370000000001</v>
       </c>
-      <c r="E67" t="n">
-        <v>7.0184</v>
-      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1308,9 +1919,16 @@
       <c r="D68" t="n">
         <v>9519.370000000001</v>
       </c>
-      <c r="E68" t="n">
-        <v>7.0195</v>
-      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1327,9 +1945,16 @@
       <c r="D69" t="n">
         <v>9620.030000000001</v>
       </c>
-      <c r="E69" t="n">
-        <v>7.0672</v>
-      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1346,9 +1971,16 @@
       <c r="D70" t="n">
         <v>9594.690000000001</v>
       </c>
-      <c r="E70" t="n">
-        <v>7.0749</v>
-      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1365,9 +1997,16 @@
       <c r="D71" t="n">
         <v>9536.379999999999</v>
       </c>
-      <c r="E71" t="n">
-        <v>7.0673</v>
-      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1384,9 +2023,16 @@
       <c r="D72" t="n">
         <v>9536.379999999999</v>
       </c>
-      <c r="E72" t="n">
-        <v>7.0662</v>
-      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1403,9 +2049,16 @@
       <c r="D73" t="n">
         <v>9536.379999999999</v>
       </c>
-      <c r="E73" t="n">
-        <v>7.0662</v>
-      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1422,9 +2075,16 @@
       <c r="D74" t="n">
         <v>9466.200000000001</v>
       </c>
-      <c r="E74" t="n">
-        <v>7.083</v>
-      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1441,9 +2101,16 @@
       <c r="D75" t="n">
         <v>9346.639999999999</v>
       </c>
-      <c r="E75" t="n">
-        <v>7.1125</v>
-      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1460,9 +2127,16 @@
       <c r="D76" t="n">
         <v>9265.190000000001</v>
       </c>
-      <c r="E76" t="n">
-        <v>7.1214</v>
-      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1479,9 +2153,16 @@
       <c r="D77" t="n">
         <v>9132.91</v>
       </c>
-      <c r="E77" t="n">
-        <v>7.1033</v>
-      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1498,9 +2179,16 @@
       <c r="D78" t="n">
         <v>9132.91</v>
       </c>
-      <c r="E78" t="n">
-        <v>7.1018</v>
-      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1517,9 +2205,16 @@
       <c r="D79" t="n">
         <v>9132.91</v>
       </c>
-      <c r="E79" t="n">
-        <v>7.1018</v>
-      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1536,9 +2231,16 @@
       <c r="D80" t="n">
         <v>9143.26</v>
       </c>
-      <c r="E80" t="n">
-        <v>7.1132</v>
-      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1555,9 +2257,16 @@
       <c r="D81" t="n">
         <v>9094.43</v>
       </c>
-      <c r="E81" t="n">
-        <v>7.1208</v>
-      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1574,9 +2283,16 @@
       <c r="D82" t="n">
         <v>9120.129999999999</v>
       </c>
-      <c r="E82" t="n">
-        <v>7.1285</v>
-      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1593,9 +2309,16 @@
       <c r="D83" t="n">
         <v>9091.540000000001</v>
       </c>
-      <c r="E83" t="n">
-        <v>7.1244</v>
-      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1612,9 +2335,16 @@
       <c r="D84" t="n">
         <v>9091.540000000001</v>
       </c>
-      <c r="E84" t="n">
-        <v>7.1238</v>
-      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1631,9 +2361,16 @@
       <c r="D85" t="n">
         <v>9091.540000000001</v>
       </c>
-      <c r="E85" t="n">
-        <v>7.1211</v>
-      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1650,9 +2387,16 @@
       <c r="D86" t="n">
         <v>9091.540000000001</v>
       </c>
-      <c r="E86" t="n">
-        <v>7.1211</v>
-      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1669,9 +2413,16 @@
       <c r="D87" t="n">
         <v>9108.84</v>
       </c>
-      <c r="E87" t="n">
-        <v>7.1272</v>
-      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1688,9 +2439,16 @@
       <c r="D88" t="n">
         <v>9168.379999999999</v>
       </c>
-      <c r="E88" t="n">
-        <v>7.1372</v>
-      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1707,9 +2465,16 @@
       <c r="D89" t="n">
         <v>9148.73</v>
       </c>
-      <c r="E89" t="n">
-        <v>7.1216</v>
-      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1726,9 +2491,16 @@
       <c r="D90" t="n">
         <v>9134.629999999999</v>
       </c>
-      <c r="E90" t="n">
-        <v>7.1186</v>
-      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1745,9 +2517,16 @@
       <c r="D91" t="n">
         <v>9151.299999999999</v>
       </c>
-      <c r="E91" t="n">
-        <v>7.1237</v>
-      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1764,9 +2543,16 @@
       <c r="D92" t="n">
         <v>9151.299999999999</v>
       </c>
-      <c r="E92" t="n">
-        <v>7.1227</v>
-      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1783,9 +2569,16 @@
       <c r="D93" t="n">
         <v>9151.299999999999</v>
       </c>
-      <c r="E93" t="n">
-        <v>7.1227</v>
-      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1802,9 +2595,16 @@
       <c r="D94" t="n">
         <v>9257.98</v>
       </c>
-      <c r="E94" t="n">
-        <v>7.0956</v>
-      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1821,9 +2621,16 @@
       <c r="D95" t="n">
         <v>9309.9</v>
       </c>
-      <c r="E95" t="n">
-        <v>7.1039</v>
-      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1840,9 +2647,16 @@
       <c r="D96" t="n">
         <v>9287.6</v>
       </c>
-      <c r="E96" t="n">
-        <v>7.1643</v>
-      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1859,9 +2673,16 @@
       <c r="D97" t="n">
         <v>9210.1</v>
       </c>
-      <c r="E97" t="n">
-        <v>7.1618</v>
-      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1878,9 +2699,16 @@
       <c r="D98" t="n">
         <v>9319.23</v>
       </c>
-      <c r="E98" t="n">
-        <v>7.1592</v>
-      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1897,9 +2725,16 @@
       <c r="D99" t="n">
         <v>9319.23</v>
       </c>
-      <c r="E99" t="n">
-        <v>7.1792</v>
-      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1916,9 +2751,16 @@
       <c r="D100" t="n">
         <v>9319.23</v>
       </c>
-      <c r="E100" t="n">
-        <v>7.1792</v>
-      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1935,9 +2777,16 @@
       <c r="D101" t="n">
         <v>9286.059999999999</v>
       </c>
-      <c r="E101" t="n">
-        <v>7.1955</v>
-      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1954,9 +2803,16 @@
       <c r="D102" t="n">
         <v>9383.32</v>
       </c>
-      <c r="E102" t="n">
-        <v>7.2367</v>
-      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1973,9 +2829,16 @@
       <c r="D103" t="n">
         <v>9566.16</v>
       </c>
-      <c r="E103" t="n">
-        <v>7.2103</v>
-      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1992,9 +2855,16 @@
       <c r="D104" t="n">
         <v>9633.940000000001</v>
       </c>
-      <c r="E104" t="n">
-        <v>7.2457</v>
-      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2011,9 +2881,16 @@
       <c r="D105" t="n">
         <v>9599.59</v>
       </c>
-      <c r="E105" t="n">
-        <v>7.2276</v>
-      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2030,9 +2907,16 @@
       <c r="D106" t="n">
         <v>9599.59</v>
       </c>
-      <c r="E106" t="n">
-        <v>7.2325</v>
-      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2049,9 +2933,16 @@
       <c r="D107" t="n">
         <v>9599.59</v>
       </c>
-      <c r="E107" t="n">
-        <v>7.2325</v>
-      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2068,9 +2959,16 @@
       <c r="D108" t="n">
         <v>9571.74</v>
       </c>
-      <c r="E108" t="n">
-        <v>7.2443</v>
-      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2087,9 +2985,16 @@
       <c r="D109" t="n">
         <v>9612.32</v>
       </c>
-      <c r="E109" t="n">
-        <v>7.2404</v>
-      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2106,9 +3011,16 @@
       <c r="D110" t="n">
         <v>9640.16</v>
       </c>
-      <c r="E110" t="n">
-        <v>7.2466</v>
-      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2125,9 +3037,16 @@
       <c r="D111" t="n">
         <v>9675.51</v>
       </c>
-      <c r="E111" t="n">
-        <v>7.2417</v>
-      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2144,9 +3063,16 @@
       <c r="D112" t="n">
         <v>9636.959999999999</v>
       </c>
-      <c r="E112" t="n">
-        <v>7.2468</v>
-      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2163,9 +3089,16 @@
       <c r="D113" t="n">
         <v>9636.959999999999</v>
       </c>
-      <c r="E113" t="n">
-        <v>7.243</v>
-      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2182,9 +3115,16 @@
       <c r="D114" t="n">
         <v>9636.959999999999</v>
       </c>
-      <c r="E114" t="n">
-        <v>7.243</v>
-      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2201,9 +3141,16 @@
       <c r="D115" t="n">
         <v>9643.6</v>
       </c>
-      <c r="E115" t="n">
-        <v>7.247</v>
-      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2220,9 +3167,16 @@
       <c r="D116" t="n">
         <v>9602.02</v>
       </c>
-      <c r="E116" t="n">
-        <v>7.2398</v>
-      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2239,9 +3193,16 @@
       <c r="D117" t="n">
         <v>9570.120000000001</v>
       </c>
-      <c r="E117" t="n">
-        <v>7.2521</v>
-      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2258,9 +3219,16 @@
       <c r="D118" t="n">
         <v>9527.969999999999</v>
       </c>
-      <c r="E118" t="n">
-        <v>7.2512</v>
-      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2277,9 +3245,16 @@
       <c r="D119" t="n">
         <v>9532.559999999999</v>
       </c>
-      <c r="E119" t="n">
-        <v>7.2411</v>
-      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2296,9 +3271,16 @@
       <c r="D120" t="n">
         <v>9532.559999999999</v>
       </c>
-      <c r="E120" t="n">
-        <v>7.2417</v>
-      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2315,9 +3297,16 @@
       <c r="D121" t="n">
         <v>9532.559999999999</v>
       </c>
-      <c r="E121" t="n">
-        <v>7.2417</v>
-      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2334,9 +3323,16 @@
       <c r="D122" t="n">
         <v>9539.860000000001</v>
       </c>
-      <c r="E122" t="n">
-        <v>7.2737</v>
-      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2353,9 +3349,16 @@
       <c r="D123" t="n">
         <v>9480.41</v>
       </c>
-      <c r="E123" t="n">
-        <v>7.2864</v>
-      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2372,9 +3375,16 @@
       <c r="D124" t="n">
         <v>9469.5</v>
       </c>
-      <c r="E124" t="n">
-        <v>7.2735</v>
-      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2391,9 +3401,16 @@
       <c r="D125" t="n">
         <v>9359.15</v>
       </c>
-      <c r="E125" t="n">
-        <v>7.2646</v>
-      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2410,9 +3427,16 @@
       <c r="D126" t="n">
         <v>9343.200000000001</v>
       </c>
-      <c r="E126" t="n">
-        <v>7.2655</v>
-      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2429,9 +3453,16 @@
       <c r="D127" t="n">
         <v>9343.200000000001</v>
       </c>
-      <c r="E127" t="n">
-        <v>7.2703</v>
-      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2448,9 +3479,16 @@
       <c r="D128" t="n">
         <v>9343.200000000001</v>
       </c>
-      <c r="E128" t="n">
-        <v>7.2703</v>
-      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -2467,9 +3505,16 @@
       <c r="D129" t="n">
         <v>9277.66</v>
       </c>
-      <c r="E129" t="n">
-        <v>7.2664</v>
-      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -2486,9 +3531,16 @@
       <c r="D130" t="n">
         <v>9316.67</v>
       </c>
-      <c r="E130" t="n">
-        <v>7.2541</v>
-      </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -2505,9 +3557,16 @@
       <c r="D131" t="n">
         <v>9319.870000000001</v>
       </c>
-      <c r="E131" t="n">
-        <v>7.2691</v>
-      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -2524,9 +3583,16 @@
       <c r="D132" t="n">
         <v>9302.6</v>
       </c>
-      <c r="E132" t="n">
-        <v>7.2666</v>
-      </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -2543,9 +3609,16 @@
       <c r="D133" t="n">
         <v>9276.09</v>
       </c>
-      <c r="E133" t="n">
-        <v>7.2757</v>
-      </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2562,9 +3635,16 @@
       <c r="D134" t="n">
         <v>9276.09</v>
       </c>
-      <c r="E134" t="n">
-        <v>7.2761</v>
-      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -2581,9 +3661,16 @@
       <c r="D135" t="n">
         <v>9276.09</v>
       </c>
-      <c r="E135" t="n">
-        <v>7.2761</v>
-      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2600,9 +3687,16 @@
       <c r="D136" t="n">
         <v>9223.73</v>
       </c>
-      <c r="E136" t="n">
-        <v>7.2843</v>
-      </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -2619,9 +3713,16 @@
       <c r="D137" t="n">
         <v>9196.959999999999</v>
       </c>
-      <c r="E137" t="n">
-        <v>7.2851</v>
-      </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -2638,9 +3739,16 @@
       <c r="D138" t="n">
         <v>9193.42</v>
       </c>
-      <c r="E138" t="n">
-        <v>7.2853</v>
-      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -2657,9 +3765,16 @@
       <c r="D139" t="n">
         <v>9131.610000000001</v>
       </c>
-      <c r="E139" t="n">
-        <v>7.297</v>
-      </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -2676,9 +3791,16 @@
       <c r="D140" t="n">
         <v>9137.66</v>
       </c>
-      <c r="E140" t="n">
-        <v>7.2989</v>
-      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -2695,9 +3817,16 @@
       <c r="D141" t="n">
         <v>9137.66</v>
       </c>
-      <c r="E141" t="n">
-        <v>7.2964</v>
-      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -2714,9 +3843,16 @@
       <c r="D142" t="n">
         <v>9137.66</v>
       </c>
-      <c r="E142" t="n">
-        <v>7.2964</v>
-      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -2733,9 +3869,16 @@
       <c r="D143" t="n">
         <v>9142.030000000001</v>
       </c>
-      <c r="E143" t="n">
-        <v>7.2992</v>
-      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -2752,9 +3895,16 @@
       <c r="D144" t="n">
         <v>9142.450000000001</v>
       </c>
-      <c r="E144" t="n">
-        <v>7.2974</v>
-      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -2771,9 +3921,16 @@
       <c r="D145" t="n">
         <v>9144.33</v>
       </c>
-      <c r="E145" t="n">
-        <v>7.299</v>
-      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -2790,9 +3947,16 @@
       <c r="D146" t="n">
         <v>9144.33</v>
       </c>
-      <c r="E146" t="n">
-        <v>7.2989</v>
-      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -2809,9 +3973,16 @@
       <c r="D147" t="n">
         <v>9135.16</v>
       </c>
-      <c r="E147" t="n">
-        <v>7.2992</v>
-      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -2828,9 +3999,16 @@
       <c r="D148" t="n">
         <v>9074.08</v>
       </c>
-      <c r="E148" t="n">
-        <v>7.2993</v>
-      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -2847,9 +4025,16 @@
       <c r="D149" t="n">
         <v>9077.309999999999</v>
       </c>
-      <c r="E149" t="n">
-        <v>7.2993</v>
-      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -2866,9 +4051,16 @@
       <c r="D150" t="n">
         <v>9077.309999999999</v>
       </c>
-      <c r="E150" t="n">
-        <v>7.2991</v>
-      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -2885,9 +4077,16 @@
       <c r="D151" t="n">
         <v>9081.370000000001</v>
       </c>
-      <c r="E151" t="n">
-        <v>7.2995</v>
-      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -2904,9 +4103,16 @@
       <c r="D152" t="n">
         <v>9055.33</v>
       </c>
-      <c r="E152" t="n">
-        <v>7.3188</v>
-      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -2923,9 +4129,16 @@
       <c r="D153" t="n">
         <v>9055.33</v>
       </c>
-      <c r="E153" t="n">
-        <v>7.3206</v>
-      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -2942,9 +4155,16 @@
       <c r="D154" t="n">
         <v>9055.33</v>
       </c>
-      <c r="E154" t="n">
-        <v>7.3206</v>
-      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -2961,9 +4181,16 @@
       <c r="D155" t="n">
         <v>9108.719999999999</v>
       </c>
-      <c r="E155" t="n">
-        <v>7.3286</v>
-      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -2980,9 +4207,16 @@
       <c r="D156" t="n">
         <v>9085.700000000001</v>
       </c>
-      <c r="E156" t="n">
-        <v>7.3251</v>
-      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -2999,9 +4233,16 @@
       <c r="D157" t="n">
         <v>9090.49</v>
       </c>
-      <c r="E157" t="n">
-        <v>7.3316</v>
-      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3018,9 +4259,16 @@
       <c r="D158" t="n">
         <v>9088.629999999999</v>
       </c>
-      <c r="E158" t="n">
-        <v>7.3322</v>
-      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3037,9 +4285,16 @@
       <c r="D159" t="n">
         <v>9113.33</v>
       </c>
-      <c r="E159" t="n">
-        <v>7.3323</v>
-      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3056,9 +4311,16 @@
       <c r="D160" t="n">
         <v>9113.33</v>
       </c>
-      <c r="E160" t="n">
-        <v>7.3327</v>
-      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3075,9 +4337,16 @@
       <c r="D161" t="n">
         <v>9113.33</v>
       </c>
-      <c r="E161" t="n">
-        <v>7.3327</v>
-      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3094,9 +4363,16 @@
       <c r="D162" t="n">
         <v>9145.290000000001</v>
       </c>
-      <c r="E162" t="n">
-        <v>7.332</v>
-      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3113,9 +4389,16 @@
       <c r="D163" t="n">
         <v>9191.58</v>
       </c>
-      <c r="E163" t="n">
-        <v>7.331</v>
-      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3132,9 +4415,16 @@
       <c r="D164" t="n">
         <v>9276.48</v>
       </c>
-      <c r="E164" t="n">
-        <v>7.3318</v>
-      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3151,9 +4441,16 @@
       <c r="D165" t="n">
         <v>9311.33</v>
       </c>
-      <c r="E165" t="n">
-        <v>7.3319</v>
-      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3170,9 +4467,16 @@
       <c r="D166" t="n">
         <v>9371.52</v>
       </c>
-      <c r="E166" t="n">
-        <v>7.3289</v>
-      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -3189,9 +4493,16 @@
       <c r="D167" t="n">
         <v>9371.52</v>
       </c>
-      <c r="E167" t="n">
-        <v>7.325</v>
-      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -3208,9 +4519,16 @@
       <c r="D168" t="n">
         <v>9371.52</v>
       </c>
-      <c r="E168" t="n">
-        <v>7.325</v>
-      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -3227,9 +4545,16 @@
       <c r="D169" t="n">
         <v>9384.41</v>
       </c>
-      <c r="E169" t="n">
-        <v>7.3143</v>
-      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -3246,9 +4571,16 @@
       <c r="D170" t="n">
         <v>9453.02</v>
       </c>
-      <c r="E170" t="n">
-        <v>7.3143</v>
-      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -3265,9 +4597,16 @@
       <c r="D171" t="n">
         <v>9446.950000000001</v>
       </c>
-      <c r="E171" t="n">
-        <v>7.2714</v>
-      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -3284,9 +4623,16 @@
       <c r="D172" t="n">
         <v>9451.08</v>
       </c>
-      <c r="E172" t="n">
-        <v>7.2878</v>
-      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -3303,9 +4649,16 @@
       <c r="D173" t="n">
         <v>9431.549999999999</v>
       </c>
-      <c r="E173" t="n">
-        <v>7.2437</v>
-      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -3322,9 +4675,16 @@
       <c r="D174" t="n">
         <v>9431.549999999999</v>
       </c>
-      <c r="E174" t="n">
-        <v>7.2441</v>
-      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -3341,9 +4701,16 @@
       <c r="D175" t="n">
         <v>9457.75</v>
       </c>
-      <c r="E175" t="n">
-        <v>7.2576</v>
-      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -3360,9 +4727,16 @@
       <c r="D176" t="n">
         <v>9457.75</v>
       </c>
-      <c r="E176" t="n">
-        <v>7.251</v>
-      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -3379,9 +4753,16 @@
       <c r="D177" t="n">
         <v>9457.75</v>
       </c>
-      <c r="E177" t="n">
-        <v>7.2512</v>
-      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -3398,9 +4779,16 @@
       <c r="D178" t="n">
         <v>9457.75</v>
       </c>
-      <c r="E178" t="n">
-        <v>7.1733</v>
-      </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -3417,9 +4805,16 @@
       <c r="D179" t="n">
         <v>9457.75</v>
       </c>
-      <c r="E179" t="n">
-        <v>7.1871</v>
-      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -3436,9 +4831,16 @@
       <c r="D180" t="n">
         <v>9372.5</v>
       </c>
-      <c r="E180" t="n">
-        <v>7.2891</v>
-      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -3455,9 +4857,16 @@
       <c r="D181" t="n">
         <v>9372.5</v>
       </c>
-      <c r="E181" t="n">
-        <v>7.2891</v>
-      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -3474,9 +4883,16 @@
       <c r="D182" t="n">
         <v>9364.68</v>
       </c>
-      <c r="E182" t="n">
-        <v>7.2887</v>
-      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -3493,9 +4909,16 @@
       <c r="D183" t="n">
         <v>9364.68</v>
       </c>
-      <c r="E183" t="n">
-        <v>7.2878</v>
-      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -3512,9 +4935,16 @@
       <c r="D184" t="n">
         <v>9364.68</v>
       </c>
-      <c r="E184" t="n">
-        <v>7.2878</v>
-      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -3531,9 +4961,16 @@
       <c r="D185" t="n">
         <v>9322.889999999999</v>
       </c>
-      <c r="E185" t="n">
-        <v>7.3057</v>
-      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -3550,9 +4987,16 @@
       <c r="D186" t="n">
         <v>9259.940000000001</v>
       </c>
-      <c r="E186" t="n">
-        <v>7.3052</v>
-      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -3569,9 +5013,16 @@
       <c r="D187" t="n">
         <v>9245.969999999999</v>
       </c>
-      <c r="E187" t="n">
-        <v>7.31</v>
-      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -3588,9 +5039,16 @@
       <c r="D188" t="n">
         <v>9265.719999999999</v>
       </c>
-      <c r="E188" t="n">
-        <v>7.254</v>
-      </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -3607,9 +5065,16 @@
       <c r="D189" t="n">
         <v>9265.719999999999</v>
       </c>
-      <c r="E189" t="n">
-        <v>7.254</v>
-      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -3626,9 +5091,16 @@
       <c r="D190" t="n">
         <v>9252.08</v>
       </c>
-      <c r="E190" t="n">
-        <v>7.254</v>
-      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -3645,9 +5117,16 @@
       <c r="D191" t="n">
         <v>9246.459999999999</v>
       </c>
-      <c r="E191" t="n">
-        <v>7.2796</v>
-      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -3664,9 +5143,16 @@
       <c r="D192" t="n">
         <v>9240.92</v>
       </c>
-      <c r="E192" t="n">
-        <v>7.2838</v>
-      </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -3683,9 +5169,16 @@
       <c r="D193" t="n">
         <v>9271.17</v>
       </c>
-      <c r="E193" t="n">
-        <v>7.256</v>
-      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -3702,9 +5195,16 @@
       <c r="D194" t="n">
         <v>9271.17</v>
       </c>
-      <c r="E194" t="n">
-        <v>7.251</v>
-      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -3721,9 +5221,16 @@
       <c r="D195" t="n">
         <v>9271.17</v>
       </c>
-      <c r="E195" t="n">
-        <v>7.251</v>
-      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -3740,9 +5247,16 @@
       <c r="D196" t="n">
         <v>9238.459999999999</v>
       </c>
-      <c r="E196" t="n">
-        <v>7.251</v>
-      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -3759,9 +5273,16 @@
       <c r="D197" t="n">
         <v>9229.940000000001</v>
       </c>
-      <c r="E197" t="n">
-        <v>7.2481</v>
-      </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -3778,9 +5299,16 @@
       <c r="D198" t="n">
         <v>9220.57</v>
       </c>
-      <c r="E198" t="n">
-        <v>7.2481</v>
-      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -3797,9 +5325,16 @@
       <c r="D199" t="n">
         <v>9158.65</v>
       </c>
-      <c r="E199" t="n">
-        <v>7.2761</v>
-      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -3816,9 +5351,16 @@
       <c r="D200" t="n">
         <v>9101.540000000001</v>
       </c>
-      <c r="E200" t="n">
-        <v>7.2861</v>
-      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -3835,9 +5377,16 @@
       <c r="D201" t="n">
         <v>9101.540000000001</v>
       </c>
-      <c r="E201" t="n">
-        <v>7.2838</v>
-      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -3854,9 +5403,16 @@
       <c r="D202" t="n">
         <v>9101.540000000001</v>
       </c>
-      <c r="E202" t="n">
-        <v>7.2838</v>
-      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -3873,9 +5429,16 @@
       <c r="D203" t="n">
         <v>9104.379999999999</v>
       </c>
-      <c r="E203" t="n">
-        <v>7.2838</v>
-      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -3892,9 +5455,16 @@
       <c r="D204" t="n">
         <v>9079.98</v>
       </c>
-      <c r="E204" t="n">
-        <v>7.2851</v>
-      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -3911,9 +5481,16 @@
       <c r="D205" t="n">
         <v>9093.51</v>
       </c>
-      <c r="E205" t="n">
-        <v>7.2656</v>
-      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -3930,9 +5507,16 @@
       <c r="D206" t="n">
         <v>9121.68</v>
       </c>
-      <c r="E206" t="n">
-        <v>7.2511</v>
-      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -3949,9 +5533,16 @@
       <c r="D207" t="n">
         <v>9142.280000000001</v>
       </c>
-      <c r="E207" t="n">
-        <v>7.2511</v>
-      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -3968,9 +5559,16 @@
       <c r="D208" t="n">
         <v>9142.280000000001</v>
       </c>
-      <c r="E208" t="n">
-        <v>7.2343</v>
-      </c>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -3987,9 +5585,16 @@
       <c r="D209" t="n">
         <v>9142.280000000001</v>
       </c>
-      <c r="E209" t="n">
-        <v>7.2343</v>
-      </c>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -4006,9 +5611,16 @@
       <c r="D210" t="n">
         <v>9148.58</v>
       </c>
-      <c r="E210" t="n">
-        <v>7.2343</v>
-      </c>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -4025,9 +5637,16 @@
       <c r="D211" t="n">
         <v>9106.459999999999</v>
       </c>
-      <c r="E211" t="n">
-        <v>7.2605</v>
-      </c>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr"/>
+      <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -4044,9 +5663,16 @@
       <c r="D212" t="n">
         <v>9141.75</v>
       </c>
-      <c r="E212" t="n">
-        <v>7.2605</v>
-      </c>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -4063,9 +5689,16 @@
       <c r="D213" t="n">
         <v>9119.17</v>
       </c>
-      <c r="E213" t="n">
-        <v>7.2378</v>
-      </c>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -4082,9 +5715,16 @@
       <c r="D214" t="n">
         <v>9119.17</v>
       </c>
-      <c r="E214" t="n">
-        <v>7.2378</v>
-      </c>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -4101,9 +5741,16 @@
       <c r="D215" t="n">
         <v>9119.17</v>
       </c>
-      <c r="E215" t="n">
-        <v>7.2378</v>
-      </c>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr"/>
+      <c r="M215" t="inlineStr"/>
+      <c r="N215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -4120,9 +5767,16 @@
       <c r="D216" t="n">
         <v>9148.059999999999</v>
       </c>
-      <c r="E216" t="n">
-        <v>7.2378</v>
-      </c>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr"/>
+      <c r="M216" t="inlineStr"/>
+      <c r="N216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -4139,9 +5793,16 @@
       <c r="D217" t="n">
         <v>9167.65</v>
       </c>
-      <c r="E217" t="n">
-        <v>7.2332</v>
-      </c>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr"/>
+      <c r="M217" t="inlineStr"/>
+      <c r="N217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -4158,9 +5819,16 @@
       <c r="D218" t="n">
         <v>9148.059999999999</v>
       </c>
-      <c r="E218" t="n">
-        <v>7.2278</v>
-      </c>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr"/>
+      <c r="M218" t="inlineStr"/>
+      <c r="N218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -4177,9 +5845,16 @@
       <c r="D219" t="n">
         <v>9089.959999999999</v>
       </c>
-      <c r="E219" t="n">
-        <v>7.2308</v>
-      </c>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr"/>
+      <c r="M219" t="inlineStr"/>
+      <c r="N219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -4196,9 +5871,16 @@
       <c r="D220" t="n">
         <v>9042.209999999999</v>
       </c>
-      <c r="E220" t="n">
-        <v>7.2482</v>
-      </c>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr"/>
+      <c r="M220" t="inlineStr"/>
+      <c r="N220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -4215,9 +5897,16 @@
       <c r="D221" t="n">
         <v>9042.209999999999</v>
       </c>
-      <c r="E221" t="n">
-        <v>7.2493</v>
-      </c>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr"/>
+      <c r="M221" t="inlineStr"/>
+      <c r="N221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -4234,9 +5923,16 @@
       <c r="D222" t="n">
         <v>9042.209999999999</v>
       </c>
-      <c r="E222" t="n">
-        <v>7.2493</v>
-      </c>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
+      <c r="J222" t="inlineStr"/>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr"/>
+      <c r="M222" t="inlineStr"/>
+      <c r="N222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -4253,9 +5949,16 @@
       <c r="D223" t="n">
         <v>9012.290000000001</v>
       </c>
-      <c r="E223" t="n">
-        <v>7.2492</v>
-      </c>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr"/>
+      <c r="M223" t="inlineStr"/>
+      <c r="N223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -4272,9 +5975,16 @@
       <c r="D224" t="n">
         <v>9005.48</v>
       </c>
-      <c r="E224" t="n">
-        <v>7.2574</v>
-      </c>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr"/>
+      <c r="M224" t="inlineStr"/>
+      <c r="N224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -4291,9 +6001,16 @@
       <c r="D225" t="n">
         <v>9005.48</v>
       </c>
-      <c r="E225" t="n">
-        <v>7.2574</v>
-      </c>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr"/>
+      <c r="M225" t="inlineStr"/>
+      <c r="N225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -4310,9 +6027,16 @@
       <c r="D226" t="n">
         <v>9007.959999999999</v>
       </c>
-      <c r="E226" t="n">
-        <v>7.2574</v>
-      </c>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr"/>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr"/>
+      <c r="M226" t="inlineStr"/>
+      <c r="N226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -4329,9 +6053,16 @@
       <c r="D227" t="n">
         <v>9019.879999999999</v>
       </c>
-      <c r="E227" t="n">
-        <v>7.2574</v>
-      </c>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr"/>
+      <c r="M227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -4348,9 +6079,16 @@
       <c r="D228" t="n">
         <v>8995.6</v>
       </c>
-      <c r="E228" t="n">
-        <v>7.256894049346879</v>
-      </c>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr"/>
+      <c r="L228" t="inlineStr"/>
+      <c r="M228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -4367,9 +6105,16 @@
       <c r="D229" t="n">
         <v>8950.32</v>
       </c>
-      <c r="E229" t="n">
-        <v>7.267441860465116</v>
-      </c>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
+      <c r="J229" t="inlineStr"/>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr"/>
+      <c r="M229" t="inlineStr"/>
+      <c r="N229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -4386,9 +6131,16 @@
       <c r="D230" t="n">
         <v>8950.32</v>
       </c>
-      <c r="E230" t="n">
-        <v>7.267441860465116</v>
-      </c>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr"/>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr"/>
+      <c r="M230" t="inlineStr"/>
+      <c r="N230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -4405,9 +6157,16 @@
       <c r="D231" t="n">
         <v>8950.32</v>
       </c>
-      <c r="E231" t="n">
-        <v>7.267441860465116</v>
-      </c>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr"/>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="inlineStr"/>
+      <c r="N231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -4424,9 +6183,16 @@
       <c r="D232" t="n">
         <v>8950.32</v>
       </c>
-      <c r="E232" t="n">
-        <v>7.267441860465116</v>
-      </c>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
+      <c r="J232" t="inlineStr"/>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -4443,9 +6209,16 @@
       <c r="D233" t="n">
         <v>8772.469999999999</v>
       </c>
-      <c r="E233" t="n">
-        <v>7.283321194464675</v>
-      </c>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr"/>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
+      <c r="J233" t="inlineStr"/>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="inlineStr"/>
+      <c r="N233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -4462,9 +6235,16 @@
       <c r="D234" t="n">
         <v>8708.940000000001</v>
       </c>
-      <c r="E234" t="n">
-        <v>7.309941520467836</v>
-      </c>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
+      <c r="J234" t="inlineStr"/>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr"/>
+      <c r="M234" t="inlineStr"/>
+      <c r="N234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -4481,9 +6261,16 @@
       <c r="D235" t="n">
         <v>8337.559999999999</v>
       </c>
-      <c r="E235" t="n">
-        <v>7.28862973760933</v>
-      </c>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
+      <c r="J235" t="inlineStr"/>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr"/>
+      <c r="M235" t="inlineStr"/>
+      <c r="N235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -4500,9 +6287,16 @@
       <c r="D236" t="n">
         <v>8264.9</v>
       </c>
-      <c r="E236" t="n">
-        <v>7.293946024799417</v>
-      </c>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr"/>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="inlineStr"/>
+      <c r="N236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -4519,9 +6313,16 @@
       <c r="D237" t="n">
         <v>8245.610000000001</v>
       </c>
-      <c r="E237" t="n">
-        <v>7.267441860465116</v>
-      </c>
+      <c r="E237" t="inlineStr"/>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
+      <c r="J237" t="inlineStr"/>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr"/>
+      <c r="N237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -4538,9 +6339,16 @@
       <c r="D238" t="n">
         <v>8245.610000000001</v>
       </c>
-      <c r="E238" t="n">
-        <v>7.272727272727272</v>
-      </c>
+      <c r="E238" t="inlineStr"/>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr"/>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
+      <c r="J238" t="inlineStr"/>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="inlineStr"/>
+      <c r="N238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -4557,9 +6365,16 @@
       <c r="D239" t="n">
         <v>8245.610000000001</v>
       </c>
-      <c r="E239" t="n">
-        <v>7.272727272727272</v>
-      </c>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
+      <c r="J239" t="inlineStr"/>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="inlineStr"/>
+      <c r="N239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -4576,9 +6391,16 @@
       <c r="D240" t="n">
         <v>8245.610000000001</v>
       </c>
-      <c r="E240" t="n">
-        <v>7.272727272727272</v>
-      </c>
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
+      <c r="J240" t="inlineStr"/>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr"/>
+      <c r="N240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -4595,9 +6417,16 @@
       <c r="D241" t="n">
         <v>8245.610000000001</v>
       </c>
-      <c r="E241" t="n">
-        <v>7.272727272727272</v>
-      </c>
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr"/>
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
+      <c r="J241" t="inlineStr"/>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr"/>
+      <c r="M241" t="inlineStr"/>
+      <c r="N241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -4614,9 +6443,16 @@
       <c r="D242" t="n">
         <v>8245.610000000001</v>
       </c>
-      <c r="E242" t="n">
-        <v>7.272727272727272</v>
-      </c>
+      <c r="E242" t="inlineStr"/>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
+      <c r="J242" t="inlineStr"/>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr"/>
+      <c r="M242" t="inlineStr"/>
+      <c r="N242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -4633,9 +6469,16 @@
       <c r="D243" t="n">
         <v>8186.35</v>
       </c>
-      <c r="E243" t="n">
-        <v>7.272727272727272</v>
-      </c>
+      <c r="E243" t="inlineStr"/>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr"/>
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
+      <c r="J243" t="inlineStr"/>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr"/>
+      <c r="M243" t="inlineStr"/>
+      <c r="N243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -4652,9 +6495,16 @@
       <c r="D244" t="n">
         <v>8150.55</v>
       </c>
-      <c r="E244" t="n">
-        <v>7.215007215007215</v>
-      </c>
+      <c r="E244" t="inlineStr"/>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr"/>
+      <c r="J244" t="inlineStr"/>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr"/>
+      <c r="M244" t="inlineStr"/>
+      <c r="N244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -4671,9 +6521,16 @@
       <c r="D245" t="n">
         <v>7956.15</v>
       </c>
-      <c r="E245" t="n">
-        <v>7.225433526011561</v>
-      </c>
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr"/>
+      <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr"/>
+      <c r="J245" t="inlineStr"/>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr"/>
+      <c r="N245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -4690,9 +6547,16 @@
       <c r="D246" t="n">
         <v>7951.77</v>
       </c>
-      <c r="E246" t="n">
-        <v>7.225433526011561</v>
-      </c>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
+      <c r="J246" t="inlineStr"/>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="inlineStr"/>
+      <c r="N246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -4709,9 +6573,16 @@
       <c r="D247" t="n">
         <v>7933.09</v>
       </c>
-      <c r="E247" t="n">
-        <v>7.204610951008645</v>
-      </c>
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr"/>
+      <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
+      <c r="J247" t="inlineStr"/>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="inlineStr"/>
+      <c r="N247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -4728,9 +6599,16 @@
       <c r="D248" t="n">
         <v>7800.58</v>
       </c>
-      <c r="E248" t="n">
-        <v>7.209805335255949</v>
-      </c>
+      <c r="E248" t="inlineStr"/>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr"/>
+      <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr"/>
+      <c r="J248" t="inlineStr"/>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr"/>
+      <c r="M248" t="inlineStr"/>
+      <c r="N248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -4747,9 +6625,16 @@
       <c r="D249" t="n">
         <v>7739.05</v>
       </c>
-      <c r="E249" t="n">
-        <v>7.209805335255949</v>
-      </c>
+      <c r="E249" t="inlineStr"/>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr"/>
+      <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr"/>
+      <c r="J249" t="inlineStr"/>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr"/>
+      <c r="N249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -4766,9 +6651,16 @@
       <c r="D250" t="n">
         <v>7712.45</v>
       </c>
-      <c r="E250" t="n">
-        <v>7.220216606498195</v>
-      </c>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr"/>
+      <c r="G250" t="inlineStr"/>
+      <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr"/>
+      <c r="J250" t="inlineStr"/>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr"/>
+      <c r="M250" t="inlineStr"/>
+      <c r="N250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -4785,9 +6677,16 @@
       <c r="D251" t="n">
         <v>7729.54</v>
       </c>
-      <c r="E251" t="n">
-        <v>7.204610951008645</v>
-      </c>
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="inlineStr"/>
+      <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr"/>
+      <c r="J251" t="inlineStr"/>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr"/>
+      <c r="M251" t="inlineStr"/>
+      <c r="N251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -4804,9 +6703,16 @@
       <c r="D252" t="n">
         <v>7723.66</v>
       </c>
-      <c r="E252" t="n">
-        <v>7.204610951008645</v>
-      </c>
+      <c r="E252" t="inlineStr"/>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr"/>
+      <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr"/>
+      <c r="J252" t="inlineStr"/>
+      <c r="K252" t="inlineStr"/>
+      <c r="L252" t="inlineStr"/>
+      <c r="M252" t="inlineStr"/>
+      <c r="N252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -4823,9 +6729,16 @@
       <c r="D253" t="n">
         <v>7723.66</v>
       </c>
-      <c r="E253" t="n">
-        <v>7.204610951008645</v>
-      </c>
+      <c r="E253" t="inlineStr"/>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr"/>
+      <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr"/>
+      <c r="J253" t="inlineStr"/>
+      <c r="K253" t="inlineStr"/>
+      <c r="L253" t="inlineStr"/>
+      <c r="M253" t="inlineStr"/>
+      <c r="N253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -4842,9 +6755,16 @@
       <c r="D254" t="n">
         <v>7723.66</v>
       </c>
-      <c r="E254" t="n">
-        <v>7.204610951008645</v>
-      </c>
+      <c r="E254" t="inlineStr"/>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr"/>
+      <c r="H254" t="inlineStr"/>
+      <c r="I254" t="inlineStr"/>
+      <c r="J254" t="inlineStr"/>
+      <c r="K254" t="inlineStr"/>
+      <c r="L254" t="inlineStr"/>
+      <c r="M254" t="inlineStr"/>
+      <c r="N254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -4861,9 +6781,16 @@
       <c r="D255" t="n">
         <v>7689.92</v>
       </c>
-      <c r="E255" t="n">
-        <v>7.204610951008645</v>
-      </c>
+      <c r="E255" t="inlineStr"/>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="inlineStr"/>
+      <c r="H255" t="inlineStr"/>
+      <c r="I255" t="inlineStr"/>
+      <c r="J255" t="inlineStr"/>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr"/>
+      <c r="M255" t="inlineStr"/>
+      <c r="N255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -4880,9 +6807,16 @@
       <c r="D256" t="n">
         <v>7618.87</v>
       </c>
-      <c r="E256" t="n">
-        <v>7.204610951008645</v>
-      </c>
+      <c r="E256" t="inlineStr"/>
+      <c r="F256" t="inlineStr"/>
+      <c r="G256" t="inlineStr"/>
+      <c r="H256" t="inlineStr"/>
+      <c r="I256" t="inlineStr"/>
+      <c r="J256" t="inlineStr"/>
+      <c r="K256" t="inlineStr"/>
+      <c r="L256" t="inlineStr"/>
+      <c r="M256" t="inlineStr"/>
+      <c r="N256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -4899,9 +6833,16 @@
       <c r="D257" t="n">
         <v>7546.94</v>
       </c>
-      <c r="E257" t="n">
-        <v>7.204610951008645</v>
-      </c>
+      <c r="E257" t="inlineStr"/>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr"/>
+      <c r="H257" t="inlineStr"/>
+      <c r="I257" t="inlineStr"/>
+      <c r="J257" t="inlineStr"/>
+      <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr"/>
+      <c r="M257" t="inlineStr"/>
+      <c r="N257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -4918,9 +6859,16 @@
       <c r="D258" t="n">
         <v>7394.46</v>
       </c>
-      <c r="E258" t="n">
-        <v>7.204610951008645</v>
-      </c>
+      <c r="E258" t="inlineStr"/>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr"/>
+      <c r="H258" t="inlineStr"/>
+      <c r="I258" t="inlineStr"/>
+      <c r="J258" t="inlineStr"/>
+      <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr"/>
+      <c r="M258" t="inlineStr"/>
+      <c r="N258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -4937,9 +6885,16 @@
       <c r="D259" t="n">
         <v>7394.46</v>
       </c>
-      <c r="E259" t="n">
-        <v>7.204610951008645</v>
-      </c>
+      <c r="E259" t="inlineStr"/>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr"/>
+      <c r="H259" t="inlineStr"/>
+      <c r="I259" t="inlineStr"/>
+      <c r="J259" t="inlineStr"/>
+      <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr"/>
+      <c r="M259" t="inlineStr"/>
+      <c r="N259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -4956,9 +6911,16 @@
       <c r="D260" t="n">
         <v>7404.33</v>
       </c>
-      <c r="E260" t="n">
-        <v>7.204610951008645</v>
-      </c>
+      <c r="E260" t="inlineStr"/>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr"/>
+      <c r="H260" t="inlineStr"/>
+      <c r="I260" t="inlineStr"/>
+      <c r="J260" t="inlineStr"/>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr"/>
+      <c r="M260" t="inlineStr"/>
+      <c r="N260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -4975,9 +6937,16 @@
       <c r="D261" t="n">
         <v>7401.78</v>
       </c>
-      <c r="E261" t="n">
-        <v>7.183908045977012</v>
-      </c>
+      <c r="E261" t="inlineStr"/>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr"/>
+      <c r="H261" t="inlineStr"/>
+      <c r="I261" t="inlineStr"/>
+      <c r="J261" t="inlineStr"/>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr"/>
+      <c r="M261" t="inlineStr"/>
+      <c r="N261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -4994,9 +6963,16 @@
       <c r="D262" t="n">
         <v>7402.81</v>
       </c>
-      <c r="E262" t="n">
-        <v>7.173601147776184</v>
-      </c>
+      <c r="E262" t="inlineStr"/>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr"/>
+      <c r="H262" t="inlineStr"/>
+      <c r="I262" t="inlineStr"/>
+      <c r="J262" t="inlineStr"/>
+      <c r="K262" t="inlineStr"/>
+      <c r="L262" t="inlineStr"/>
+      <c r="M262" t="inlineStr"/>
+      <c r="N262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -5013,9 +6989,16 @@
       <c r="D263" t="n">
         <v>7402.81</v>
       </c>
-      <c r="E263" t="n">
-        <v>7.189072609633357</v>
-      </c>
+      <c r="E263" t="inlineStr"/>
+      <c r="F263" t="inlineStr"/>
+      <c r="G263" t="inlineStr"/>
+      <c r="H263" t="inlineStr"/>
+      <c r="I263" t="inlineStr"/>
+      <c r="J263" t="inlineStr"/>
+      <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr"/>
+      <c r="M263" t="inlineStr"/>
+      <c r="N263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -5032,9 +7015,16 @@
       <c r="D264" t="n">
         <v>7402.81</v>
       </c>
-      <c r="E264" t="n">
-        <v>7.189072609633357</v>
-      </c>
+      <c r="E264" t="inlineStr"/>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="inlineStr"/>
+      <c r="H264" t="inlineStr"/>
+      <c r="I264" t="inlineStr"/>
+      <c r="J264" t="inlineStr"/>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr"/>
+      <c r="M264" t="inlineStr"/>
+      <c r="N264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -5051,9 +7041,16 @@
       <c r="D265" t="n">
         <v>7395.6</v>
       </c>
-      <c r="E265" t="n">
-        <v>7.189072609633357</v>
-      </c>
+      <c r="E265" t="inlineStr"/>
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="inlineStr"/>
+      <c r="H265" t="inlineStr"/>
+      <c r="I265" t="inlineStr"/>
+      <c r="J265" t="inlineStr"/>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
+      <c r="M265" t="inlineStr"/>
+      <c r="N265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -5070,9 +7067,16 @@
       <c r="D266" t="n">
         <v>7416.62</v>
       </c>
-      <c r="E266" t="n">
-        <v>7.178750897343861</v>
-      </c>
+      <c r="E266" t="inlineStr"/>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr"/>
+      <c r="H266" t="inlineStr"/>
+      <c r="I266" t="inlineStr"/>
+      <c r="J266" t="inlineStr"/>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr"/>
+      <c r="M266" t="inlineStr"/>
+      <c r="N266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -5089,9 +7093,16 @@
       <c r="D267" t="n">
         <v>7434.54</v>
       </c>
-      <c r="E267" t="n">
-        <v>7.183908045977012</v>
-      </c>
+      <c r="E267" t="inlineStr"/>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="inlineStr"/>
+      <c r="H267" t="inlineStr"/>
+      <c r="I267" t="inlineStr"/>
+      <c r="J267" t="inlineStr"/>
+      <c r="K267" t="inlineStr"/>
+      <c r="L267" t="inlineStr"/>
+      <c r="M267" t="inlineStr"/>
+      <c r="N267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -5108,9 +7119,16 @@
       <c r="D268" t="n">
         <v>7422.21</v>
       </c>
-      <c r="E268" t="n">
-        <v>7.183908045977012</v>
-      </c>
+      <c r="E268" t="inlineStr"/>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr"/>
+      <c r="H268" t="inlineStr"/>
+      <c r="I268" t="inlineStr"/>
+      <c r="J268" t="inlineStr"/>
+      <c r="K268" t="inlineStr"/>
+      <c r="L268" t="inlineStr"/>
+      <c r="M268" t="inlineStr"/>
+      <c r="N268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -5127,9 +7145,16 @@
       <c r="D269" t="n">
         <v>7417.58</v>
       </c>
-      <c r="E269" t="n">
-        <v>7.189072609633357</v>
-      </c>
+      <c r="E269" t="inlineStr"/>
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="inlineStr"/>
+      <c r="H269" t="inlineStr"/>
+      <c r="I269" t="inlineStr"/>
+      <c r="J269" t="inlineStr"/>
+      <c r="K269" t="inlineStr"/>
+      <c r="L269" t="inlineStr"/>
+      <c r="M269" t="inlineStr"/>
+      <c r="N269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -5146,9 +7171,16 @@
       <c r="D270" t="n">
         <v>7426.37</v>
       </c>
-      <c r="E270" t="n">
-        <v>7.189072609633357</v>
-      </c>
+      <c r="E270" t="inlineStr"/>
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="inlineStr"/>
+      <c r="H270" t="inlineStr"/>
+      <c r="I270" t="inlineStr"/>
+      <c r="J270" t="inlineStr"/>
+      <c r="K270" t="inlineStr"/>
+      <c r="L270" t="inlineStr"/>
+      <c r="M270" t="inlineStr"/>
+      <c r="N270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -5165,9 +7197,16 @@
       <c r="D271" t="n">
         <v>7426.37</v>
       </c>
-      <c r="E271" t="n">
-        <v>7.189072609633357</v>
-      </c>
+      <c r="E271" t="inlineStr"/>
+      <c r="F271" t="inlineStr"/>
+      <c r="G271" t="inlineStr"/>
+      <c r="H271" t="inlineStr"/>
+      <c r="I271" t="inlineStr"/>
+      <c r="J271" t="inlineStr"/>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr"/>
+      <c r="M271" t="inlineStr"/>
+      <c r="N271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -5184,9 +7223,16 @@
       <c r="D272" t="n">
         <v>7426.37</v>
       </c>
-      <c r="E272" t="n">
-        <v>7.189072609633357</v>
-      </c>
+      <c r="E272" t="inlineStr"/>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="inlineStr"/>
+      <c r="H272" t="inlineStr"/>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="inlineStr"/>
+      <c r="N272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -5203,9 +7249,16 @@
       <c r="D273" t="n">
         <v>7365.42</v>
       </c>
-      <c r="E273" t="n">
-        <v>7.189072609633357</v>
-      </c>
+      <c r="E273" t="inlineStr"/>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr"/>
+      <c r="H273" t="inlineStr"/>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="inlineStr"/>
+      <c r="N273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -5222,9 +7275,16 @@
       <c r="D274" t="n">
         <v>7367.97</v>
       </c>
-      <c r="E274" t="n">
-        <v>7.178750897343861</v>
-      </c>
+      <c r="E274" t="inlineStr"/>
+      <c r="F274" t="inlineStr"/>
+      <c r="G274" t="inlineStr"/>
+      <c r="H274" t="inlineStr"/>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="inlineStr"/>
+      <c r="N274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -5241,9 +7301,16 @@
       <c r="D275" t="n">
         <v>7561.72</v>
       </c>
-      <c r="E275" t="n">
-        <v>7.1641</v>
-      </c>
+      <c r="E275" t="inlineStr"/>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="inlineStr"/>
+      <c r="H275" t="inlineStr"/>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="inlineStr"/>
+      <c r="N275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -5260,9 +7327,16 @@
       <c r="D276" t="n">
         <v>7561.72</v>
       </c>
-      <c r="E276" t="n">
-        <v>7.1641</v>
-      </c>
+      <c r="E276" t="inlineStr"/>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr"/>
+      <c r="H276" t="inlineStr"/>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="inlineStr"/>
+      <c r="N276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -5279,9 +7353,16 @@
       <c r="D277" t="n">
         <v>7561.72</v>
       </c>
-      <c r="E277" t="n">
-        <v>7.1641</v>
-      </c>
+      <c r="E277" t="inlineStr"/>
+      <c r="F277" t="inlineStr"/>
+      <c r="G277" t="inlineStr"/>
+      <c r="H277" t="inlineStr"/>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="inlineStr"/>
+      <c r="N277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -5298,9 +7379,16 @@
       <c r="D278" t="n">
         <v>7593.78</v>
       </c>
-      <c r="E278" t="n">
-        <v>7.1652</v>
-      </c>
+      <c r="E278" t="inlineStr"/>
+      <c r="F278" t="inlineStr"/>
+      <c r="G278" t="inlineStr"/>
+      <c r="H278" t="inlineStr"/>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="inlineStr"/>
+      <c r="N278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -5317,9 +7405,16 @@
       <c r="D279" t="n">
         <v>7704.1</v>
       </c>
-      <c r="E279" t="n">
-        <v>7.1654</v>
-      </c>
+      <c r="E279" t="inlineStr"/>
+      <c r="F279" t="inlineStr"/>
+      <c r="G279" t="inlineStr"/>
+      <c r="H279" t="inlineStr"/>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="inlineStr"/>
+      <c r="N279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -5336,9 +7431,16 @@
       <c r="D280" t="n">
         <v>7736.98</v>
       </c>
-      <c r="E280" t="n">
-        <v>7.1749</v>
-      </c>
+      <c r="E280" t="inlineStr"/>
+      <c r="F280" t="inlineStr"/>
+      <c r="G280" t="inlineStr"/>
+      <c r="H280" t="inlineStr"/>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="inlineStr"/>
+      <c r="N280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -5355,9 +7457,16 @@
       <c r="D281" t="n">
         <v>7784.56</v>
       </c>
-      <c r="E281" t="n">
-        <v>7.174</v>
-      </c>
+      <c r="E281" t="inlineStr"/>
+      <c r="F281" t="inlineStr"/>
+      <c r="G281" t="inlineStr"/>
+      <c r="H281" t="inlineStr"/>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="inlineStr"/>
+      <c r="N281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -5374,9 +7483,16 @@
       <c r="D282" t="n">
         <v>7823.8</v>
       </c>
-      <c r="E282" t="n">
-        <v>7.1802</v>
-      </c>
+      <c r="E282" t="inlineStr"/>
+      <c r="F282" t="inlineStr"/>
+      <c r="G282" t="inlineStr"/>
+      <c r="H282" t="inlineStr"/>
+      <c r="I282" t="inlineStr"/>
+      <c r="J282" t="inlineStr"/>
+      <c r="K282" t="inlineStr"/>
+      <c r="L282" t="inlineStr"/>
+      <c r="M282" t="inlineStr"/>
+      <c r="N282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -5393,9 +7509,16 @@
       <c r="D283" t="n">
         <v>7833.91</v>
       </c>
-      <c r="E283" t="n">
-        <v>7.1753</v>
-      </c>
+      <c r="E283" t="inlineStr"/>
+      <c r="F283" t="inlineStr"/>
+      <c r="G283" t="inlineStr"/>
+      <c r="H283" t="inlineStr"/>
+      <c r="I283" t="inlineStr"/>
+      <c r="J283" t="inlineStr"/>
+      <c r="K283" t="inlineStr"/>
+      <c r="L283" t="inlineStr"/>
+      <c r="M283" t="inlineStr"/>
+      <c r="N283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -5412,9 +7535,16 @@
       <c r="D284" t="n">
         <v>7833.91</v>
       </c>
-      <c r="E284" t="n">
-        <v>7.1753</v>
-      </c>
+      <c r="E284" t="inlineStr"/>
+      <c r="F284" t="inlineStr"/>
+      <c r="G284" t="inlineStr"/>
+      <c r="H284" t="inlineStr"/>
+      <c r="I284" t="inlineStr"/>
+      <c r="J284" t="inlineStr"/>
+      <c r="K284" t="inlineStr"/>
+      <c r="L284" t="inlineStr"/>
+      <c r="M284" t="inlineStr"/>
+      <c r="N284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -5431,9 +7561,16 @@
       <c r="D285" t="n">
         <v>7833.91</v>
       </c>
-      <c r="E285" t="n">
-        <v>7.1753</v>
-      </c>
+      <c r="E285" t="inlineStr"/>
+      <c r="F285" t="inlineStr"/>
+      <c r="G285" t="inlineStr"/>
+      <c r="H285" t="inlineStr"/>
+      <c r="I285" t="inlineStr"/>
+      <c r="J285" t="inlineStr"/>
+      <c r="K285" t="inlineStr"/>
+      <c r="L285" t="inlineStr"/>
+      <c r="M285" t="inlineStr"/>
+      <c r="N285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -5450,9 +7587,16 @@
       <c r="D286" t="n">
         <v>7962.75</v>
       </c>
-      <c r="E286" t="n">
-        <v>7.1686</v>
-      </c>
+      <c r="E286" t="inlineStr"/>
+      <c r="F286" t="inlineStr"/>
+      <c r="G286" t="inlineStr"/>
+      <c r="H286" t="inlineStr"/>
+      <c r="I286" t="inlineStr"/>
+      <c r="J286" t="inlineStr"/>
+      <c r="K286" t="inlineStr"/>
+      <c r="L286" t="inlineStr"/>
+      <c r="M286" t="inlineStr"/>
+      <c r="N286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -5469,9 +7613,16 @@
       <c r="D287" t="n">
         <v>7987.43</v>
       </c>
-      <c r="E287" t="n">
-        <v>7.1673</v>
-      </c>
+      <c r="E287" t="inlineStr"/>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="inlineStr"/>
+      <c r="H287" t="inlineStr"/>
+      <c r="I287" t="inlineStr"/>
+      <c r="J287" t="inlineStr"/>
+      <c r="K287" t="inlineStr"/>
+      <c r="L287" t="inlineStr"/>
+      <c r="M287" t="inlineStr"/>
+      <c r="N287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -5488,9 +7639,16 @@
       <c r="D288" t="n">
         <v>7984.7</v>
       </c>
-      <c r="E288" t="n">
-        <v>7.1837</v>
-      </c>
+      <c r="E288" t="inlineStr"/>
+      <c r="F288" t="inlineStr"/>
+      <c r="G288" t="inlineStr"/>
+      <c r="H288" t="inlineStr"/>
+      <c r="I288" t="inlineStr"/>
+      <c r="J288" t="inlineStr"/>
+      <c r="K288" t="inlineStr"/>
+      <c r="L288" t="inlineStr"/>
+      <c r="M288" t="inlineStr"/>
+      <c r="N288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -5507,9 +7665,16 @@
       <c r="D289" t="n">
         <v>8755.49</v>
       </c>
-      <c r="E289" t="n">
-        <v>7.1788</v>
-      </c>
+      <c r="E289" t="inlineStr"/>
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="inlineStr"/>
+      <c r="H289" t="inlineStr"/>
+      <c r="I289" t="inlineStr"/>
+      <c r="J289" t="inlineStr"/>
+      <c r="K289" t="inlineStr"/>
+      <c r="L289" t="inlineStr"/>
+      <c r="M289" t="inlineStr"/>
+      <c r="N289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -5526,9 +7691,16 @@
       <c r="D290" t="n">
         <v>8755.49</v>
       </c>
-      <c r="E290" t="n">
-        <v>7.1788</v>
-      </c>
+      <c r="E290" t="inlineStr"/>
+      <c r="F290" t="inlineStr"/>
+      <c r="G290" t="inlineStr"/>
+      <c r="H290" t="inlineStr"/>
+      <c r="I290" t="inlineStr"/>
+      <c r="J290" t="inlineStr"/>
+      <c r="K290" t="inlineStr"/>
+      <c r="L290" t="inlineStr"/>
+      <c r="M290" t="inlineStr"/>
+      <c r="N290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -5545,9 +7717,16 @@
       <c r="D291" t="n">
         <v>8712.030000000001</v>
       </c>
-      <c r="E291" t="n">
-        <v>7.1841</v>
-      </c>
+      <c r="E291" t="inlineStr"/>
+      <c r="F291" t="inlineStr"/>
+      <c r="G291" t="inlineStr"/>
+      <c r="H291" t="inlineStr"/>
+      <c r="I291" t="inlineStr"/>
+      <c r="J291" t="inlineStr"/>
+      <c r="K291" t="inlineStr"/>
+      <c r="L291" t="inlineStr"/>
+      <c r="M291" t="inlineStr"/>
+      <c r="N291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -5564,9 +7743,16 @@
       <c r="D292" t="n">
         <v>8737.120000000001</v>
       </c>
-      <c r="E292" t="n">
-        <v>7.1831</v>
-      </c>
+      <c r="E292" t="inlineStr"/>
+      <c r="F292" t="inlineStr"/>
+      <c r="G292" t="inlineStr"/>
+      <c r="H292" t="inlineStr"/>
+      <c r="I292" t="inlineStr"/>
+      <c r="J292" t="inlineStr"/>
+      <c r="K292" t="inlineStr"/>
+      <c r="L292" t="inlineStr"/>
+      <c r="M292" t="inlineStr"/>
+      <c r="N292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -5583,9 +7769,16 @@
       <c r="D293" t="n">
         <v>8836.040000000001</v>
       </c>
-      <c r="E293" t="n">
-        <v>7.1815</v>
-      </c>
+      <c r="E293" t="inlineStr"/>
+      <c r="F293" t="inlineStr"/>
+      <c r="G293" t="inlineStr"/>
+      <c r="H293" t="inlineStr"/>
+      <c r="I293" t="inlineStr"/>
+      <c r="J293" t="inlineStr"/>
+      <c r="K293" t="inlineStr"/>
+      <c r="L293" t="inlineStr"/>
+      <c r="M293" t="inlineStr"/>
+      <c r="N293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -5602,9 +7795,16 @@
       <c r="D294" t="n">
         <v>8836.040000000001</v>
       </c>
-      <c r="E294" t="n">
-        <v>7.1815</v>
-      </c>
+      <c r="E294" t="inlineStr"/>
+      <c r="F294" t="inlineStr"/>
+      <c r="G294" t="inlineStr"/>
+      <c r="H294" t="inlineStr"/>
+      <c r="I294" t="inlineStr"/>
+      <c r="J294" t="inlineStr"/>
+      <c r="K294" t="inlineStr"/>
+      <c r="L294" t="inlineStr"/>
+      <c r="M294" t="inlineStr"/>
+      <c r="N294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -5621,9 +7821,16 @@
       <c r="D295" t="n">
         <v>8836.040000000001</v>
       </c>
-      <c r="E295" t="n">
-        <v>7.1815</v>
-      </c>
+      <c r="E295" t="inlineStr"/>
+      <c r="F295" t="inlineStr"/>
+      <c r="G295" t="inlineStr"/>
+      <c r="H295" t="inlineStr"/>
+      <c r="I295" t="inlineStr"/>
+      <c r="J295" t="inlineStr"/>
+      <c r="K295" t="inlineStr"/>
+      <c r="L295" t="inlineStr"/>
+      <c r="M295" t="inlineStr"/>
+      <c r="N295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -5640,9 +7847,16 @@
       <c r="D296" t="n">
         <v>9154.93</v>
       </c>
-      <c r="E296" t="n">
-        <v>7.1815</v>
-      </c>
+      <c r="E296" t="inlineStr"/>
+      <c r="F296" t="inlineStr"/>
+      <c r="G296" t="inlineStr"/>
+      <c r="H296" t="inlineStr"/>
+      <c r="I296" t="inlineStr"/>
+      <c r="J296" t="inlineStr"/>
+      <c r="K296" t="inlineStr"/>
+      <c r="L296" t="inlineStr"/>
+      <c r="M296" t="inlineStr"/>
+      <c r="N296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -5659,9 +7873,16 @@
       <c r="D297" t="n">
         <v>9581.030000000001</v>
       </c>
-      <c r="E297" t="n">
-        <v>7.1882</v>
-      </c>
+      <c r="E297" t="inlineStr"/>
+      <c r="F297" t="inlineStr"/>
+      <c r="G297" t="inlineStr"/>
+      <c r="H297" t="inlineStr"/>
+      <c r="I297" t="inlineStr"/>
+      <c r="J297" t="inlineStr"/>
+      <c r="K297" t="inlineStr"/>
+      <c r="L297" t="inlineStr"/>
+      <c r="M297" t="inlineStr"/>
+      <c r="N297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -5678,9 +7899,16 @@
       <c r="D298" t="n">
         <v>10526.12</v>
       </c>
-      <c r="E298" t="n">
-        <v>7.1824</v>
-      </c>
+      <c r="E298" t="inlineStr"/>
+      <c r="F298" t="inlineStr"/>
+      <c r="G298" t="inlineStr"/>
+      <c r="H298" t="inlineStr"/>
+      <c r="I298" t="inlineStr"/>
+      <c r="J298" t="inlineStr"/>
+      <c r="K298" t="inlineStr"/>
+      <c r="L298" t="inlineStr"/>
+      <c r="M298" t="inlineStr"/>
+      <c r="N298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -5697,9 +7925,16 @@
       <c r="D299" t="n">
         <v>10481.44</v>
       </c>
-      <c r="E299" t="n">
-        <v>7.1762</v>
-      </c>
+      <c r="E299" t="inlineStr"/>
+      <c r="F299" t="inlineStr"/>
+      <c r="G299" t="inlineStr"/>
+      <c r="H299" t="inlineStr"/>
+      <c r="I299" t="inlineStr"/>
+      <c r="J299" t="inlineStr"/>
+      <c r="K299" t="inlineStr"/>
+      <c r="L299" t="inlineStr"/>
+      <c r="M299" t="inlineStr"/>
+      <c r="N299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -5716,9 +7951,16 @@
       <c r="D300" t="n">
         <v>10311.48</v>
       </c>
-      <c r="E300" t="n">
-        <v>7.1804</v>
-      </c>
+      <c r="E300" t="inlineStr"/>
+      <c r="F300" t="inlineStr"/>
+      <c r="G300" t="inlineStr"/>
+      <c r="H300" t="inlineStr"/>
+      <c r="I300" t="inlineStr"/>
+      <c r="J300" t="inlineStr"/>
+      <c r="K300" t="inlineStr"/>
+      <c r="L300" t="inlineStr"/>
+      <c r="M300" t="inlineStr"/>
+      <c r="N300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -5735,9 +7977,16 @@
       <c r="D301" t="n">
         <v>9857.040000000001</v>
       </c>
-      <c r="E301" t="n">
-        <v>7.154</v>
-      </c>
+      <c r="E301" t="inlineStr"/>
+      <c r="F301" t="inlineStr"/>
+      <c r="G301" t="inlineStr"/>
+      <c r="H301" t="inlineStr"/>
+      <c r="I301" t="inlineStr"/>
+      <c r="J301" t="inlineStr"/>
+      <c r="K301" t="inlineStr"/>
+      <c r="L301" t="inlineStr"/>
+      <c r="M301" t="inlineStr"/>
+      <c r="N301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -5754,9 +8003,16 @@
       <c r="D302" t="n">
         <v>9857.040000000001</v>
       </c>
-      <c r="E302" t="n">
-        <v>7.154</v>
-      </c>
+      <c r="E302" t="inlineStr"/>
+      <c r="F302" t="inlineStr"/>
+      <c r="G302" t="inlineStr"/>
+      <c r="H302" t="inlineStr"/>
+      <c r="I302" t="inlineStr"/>
+      <c r="J302" t="inlineStr"/>
+      <c r="K302" t="inlineStr"/>
+      <c r="L302" t="inlineStr"/>
+      <c r="M302" t="inlineStr"/>
+      <c r="N302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -5773,9 +8029,16 @@
       <c r="D303" t="n">
         <v>9132.639999999999</v>
       </c>
-      <c r="E303" t="n">
-        <v>7.1322</v>
-      </c>
+      <c r="E303" t="inlineStr"/>
+      <c r="F303" t="inlineStr"/>
+      <c r="G303" t="inlineStr"/>
+      <c r="H303" t="inlineStr"/>
+      <c r="I303" t="inlineStr"/>
+      <c r="J303" t="inlineStr"/>
+      <c r="K303" t="inlineStr"/>
+      <c r="L303" t="inlineStr"/>
+      <c r="M303" t="inlineStr"/>
+      <c r="N303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -5792,9 +8055,16 @@
       <c r="D304" t="n">
         <v>9211.84</v>
       </c>
-      <c r="E304" t="n">
-        <v>7.1223</v>
-      </c>
+      <c r="E304" t="inlineStr"/>
+      <c r="F304" t="inlineStr"/>
+      <c r="G304" t="inlineStr"/>
+      <c r="H304" t="inlineStr"/>
+      <c r="I304" t="inlineStr"/>
+      <c r="J304" t="inlineStr"/>
+      <c r="K304" t="inlineStr"/>
+      <c r="L304" t="inlineStr"/>
+      <c r="M304" t="inlineStr"/>
+      <c r="N304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -5811,9 +8081,16 @@
       <c r="D305" t="n">
         <v>9339.58</v>
       </c>
-      <c r="E305" t="n">
-        <v>7.1265</v>
-      </c>
+      <c r="E305" t="inlineStr"/>
+      <c r="F305" t="inlineStr"/>
+      <c r="G305" t="inlineStr"/>
+      <c r="H305" t="inlineStr"/>
+      <c r="I305" t="inlineStr"/>
+      <c r="J305" t="inlineStr"/>
+      <c r="K305" t="inlineStr"/>
+      <c r="L305" t="inlineStr"/>
+      <c r="M305" t="inlineStr"/>
+      <c r="N305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -5830,9 +8107,16 @@
       <c r="D306" t="n">
         <v>9339.58</v>
       </c>
-      <c r="E306" t="n">
-        <v>7.1216</v>
-      </c>
+      <c r="E306" t="inlineStr"/>
+      <c r="F306" t="inlineStr"/>
+      <c r="G306" t="inlineStr"/>
+      <c r="H306" t="inlineStr"/>
+      <c r="I306" t="inlineStr"/>
+      <c r="J306" t="inlineStr"/>
+      <c r="K306" t="inlineStr"/>
+      <c r="L306" t="inlineStr"/>
+      <c r="M306" t="inlineStr"/>
+      <c r="N306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -5849,9 +8133,16 @@
       <c r="D307" t="n">
         <v>9339.58</v>
       </c>
-      <c r="E307" t="n">
-        <v>7.1216</v>
-      </c>
+      <c r="E307" t="inlineStr"/>
+      <c r="F307" t="inlineStr"/>
+      <c r="G307" t="inlineStr"/>
+      <c r="H307" t="inlineStr"/>
+      <c r="I307" t="inlineStr"/>
+      <c r="J307" t="inlineStr"/>
+      <c r="K307" t="inlineStr"/>
+      <c r="L307" t="inlineStr"/>
+      <c r="M307" t="inlineStr"/>
+      <c r="N307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -5868,9 +8159,16 @@
       <c r="D308" t="n">
         <v>9504.110000000001</v>
       </c>
-      <c r="E308" t="n">
-        <v>7.1215</v>
-      </c>
+      <c r="E308" t="inlineStr"/>
+      <c r="F308" t="inlineStr"/>
+      <c r="G308" t="inlineStr"/>
+      <c r="H308" t="inlineStr"/>
+      <c r="I308" t="inlineStr"/>
+      <c r="J308" t="inlineStr"/>
+      <c r="K308" t="inlineStr"/>
+      <c r="L308" t="inlineStr"/>
+      <c r="M308" t="inlineStr"/>
+      <c r="N308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -5887,9 +8185,16 @@
       <c r="D309" t="n">
         <v>9752.639999999999</v>
       </c>
-      <c r="E309" t="n">
-        <v>7.1104</v>
-      </c>
+      <c r="E309" t="inlineStr"/>
+      <c r="F309" t="inlineStr"/>
+      <c r="G309" t="inlineStr"/>
+      <c r="H309" t="inlineStr"/>
+      <c r="I309" t="inlineStr"/>
+      <c r="J309" t="inlineStr"/>
+      <c r="K309" t="inlineStr"/>
+      <c r="L309" t="inlineStr"/>
+      <c r="M309" t="inlineStr"/>
+      <c r="N309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -5906,9 +8211,16 @@
       <c r="D310" t="n">
         <v>9842.65</v>
       </c>
-      <c r="E310" t="n">
-        <v>7.0992</v>
-      </c>
+      <c r="E310" t="inlineStr"/>
+      <c r="F310" t="inlineStr"/>
+      <c r="G310" t="inlineStr"/>
+      <c r="H310" t="inlineStr"/>
+      <c r="I310" t="inlineStr"/>
+      <c r="J310" t="inlineStr"/>
+      <c r="K310" t="inlineStr"/>
+      <c r="L310" t="inlineStr"/>
+      <c r="M310" t="inlineStr"/>
+      <c r="N310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -5925,9 +8237,16 @@
       <c r="D311" t="n">
         <v>9950.450000000001</v>
       </c>
-      <c r="E311" t="n">
-        <v>7.099</v>
-      </c>
+      <c r="E311" t="inlineStr"/>
+      <c r="F311" t="inlineStr"/>
+      <c r="G311" t="inlineStr"/>
+      <c r="H311" t="inlineStr"/>
+      <c r="I311" t="inlineStr"/>
+      <c r="J311" t="inlineStr"/>
+      <c r="K311" t="inlineStr"/>
+      <c r="L311" t="inlineStr"/>
+      <c r="M311" t="inlineStr"/>
+      <c r="N311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -5944,9 +8263,16 @@
       <c r="D312" t="n">
         <v>9999.040000000001</v>
       </c>
-      <c r="E312" t="n">
-        <v>7.1106</v>
-      </c>
+      <c r="E312" t="inlineStr"/>
+      <c r="F312" t="inlineStr"/>
+      <c r="G312" t="inlineStr"/>
+      <c r="H312" t="inlineStr"/>
+      <c r="I312" t="inlineStr"/>
+      <c r="J312" t="inlineStr"/>
+      <c r="K312" t="inlineStr"/>
+      <c r="L312" t="inlineStr"/>
+      <c r="M312" t="inlineStr"/>
+      <c r="N312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -5963,9 +8289,16 @@
       <c r="D313" t="n">
         <v>11908.46</v>
       </c>
-      <c r="E313" t="n">
-        <v>7.0472</v>
-      </c>
+      <c r="E313" t="inlineStr"/>
+      <c r="F313" t="inlineStr"/>
+      <c r="G313" t="inlineStr"/>
+      <c r="H313" t="inlineStr"/>
+      <c r="I313" t="inlineStr"/>
+      <c r="J313" t="inlineStr"/>
+      <c r="K313" t="inlineStr"/>
+      <c r="L313" t="inlineStr"/>
+      <c r="M313" t="inlineStr"/>
+      <c r="N313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -5982,9 +8315,16 @@
       <c r="D314" t="n">
         <v>12011.02</v>
       </c>
-      <c r="E314" t="n">
-        <v>7.0472</v>
-      </c>
+      <c r="E314" t="inlineStr"/>
+      <c r="F314" t="inlineStr"/>
+      <c r="G314" t="inlineStr"/>
+      <c r="H314" t="inlineStr"/>
+      <c r="I314" t="inlineStr"/>
+      <c r="J314" t="inlineStr"/>
+      <c r="K314" t="inlineStr"/>
+      <c r="L314" t="inlineStr"/>
+      <c r="M314" t="inlineStr"/>
+      <c r="N314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -6001,9 +8341,16 @@
       <c r="D315" t="n">
         <v>12167.25</v>
       </c>
-      <c r="E315" t="n">
-        <v>7.042</v>
-      </c>
+      <c r="E315" t="inlineStr"/>
+      <c r="F315" t="inlineStr"/>
+      <c r="G315" t="inlineStr"/>
+      <c r="H315" t="inlineStr"/>
+      <c r="I315" t="inlineStr"/>
+      <c r="J315" t="inlineStr"/>
+      <c r="K315" t="inlineStr"/>
+      <c r="L315" t="inlineStr"/>
+      <c r="M315" t="inlineStr"/>
+      <c r="N315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -6020,9 +8367,16 @@
       <c r="D316" t="n">
         <v>12221.45</v>
       </c>
-      <c r="E316" t="n">
-        <v>7.0433</v>
-      </c>
+      <c r="E316" t="inlineStr"/>
+      <c r="F316" t="inlineStr"/>
+      <c r="G316" t="inlineStr"/>
+      <c r="H316" t="inlineStr"/>
+      <c r="I316" t="inlineStr"/>
+      <c r="J316" t="inlineStr"/>
+      <c r="K316" t="inlineStr"/>
+      <c r="L316" t="inlineStr"/>
+      <c r="M316" t="inlineStr"/>
+      <c r="N316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -6039,9 +8393,16 @@
       <c r="D317" t="n">
         <v>12240.56</v>
       </c>
-      <c r="E317" t="n">
-        <v>7.0412</v>
-      </c>
+      <c r="E317" t="inlineStr"/>
+      <c r="F317" t="inlineStr"/>
+      <c r="G317" t="inlineStr"/>
+      <c r="H317" t="inlineStr"/>
+      <c r="I317" t="inlineStr"/>
+      <c r="J317" t="inlineStr"/>
+      <c r="K317" t="inlineStr"/>
+      <c r="L317" t="inlineStr"/>
+      <c r="M317" t="inlineStr"/>
+      <c r="N317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -6058,9 +8419,16 @@
       <c r="D318" t="n">
         <v>12240.56</v>
       </c>
-      <c r="E318" t="n">
-        <v>7.0409</v>
-      </c>
+      <c r="E318" t="inlineStr"/>
+      <c r="F318" t="inlineStr"/>
+      <c r="G318" t="inlineStr"/>
+      <c r="H318" t="inlineStr"/>
+      <c r="I318" t="inlineStr"/>
+      <c r="J318" t="inlineStr"/>
+      <c r="K318" t="inlineStr"/>
+      <c r="L318" t="inlineStr"/>
+      <c r="M318" t="inlineStr"/>
+      <c r="N318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -6077,9 +8445,16 @@
       <c r="D319" t="n">
         <v>12240.56</v>
       </c>
-      <c r="E319" t="n">
-        <v>7.0409</v>
-      </c>
+      <c r="E319" t="inlineStr"/>
+      <c r="F319" t="inlineStr"/>
+      <c r="G319" t="inlineStr"/>
+      <c r="H319" t="inlineStr"/>
+      <c r="I319" t="inlineStr"/>
+      <c r="J319" t="inlineStr"/>
+      <c r="K319" t="inlineStr"/>
+      <c r="L319" t="inlineStr"/>
+      <c r="M319" t="inlineStr"/>
+      <c r="N319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -6096,9 +8471,16 @@
       <c r="D320" t="n">
         <v>12412.25</v>
       </c>
-      <c r="E320" t="n">
-        <v>7.0409</v>
-      </c>
+      <c r="E320" t="inlineStr"/>
+      <c r="F320" t="inlineStr"/>
+      <c r="G320" t="inlineStr"/>
+      <c r="H320" t="inlineStr"/>
+      <c r="I320" t="inlineStr"/>
+      <c r="J320" t="inlineStr"/>
+      <c r="K320" t="inlineStr"/>
+      <c r="L320" t="inlineStr"/>
+      <c r="M320" t="inlineStr"/>
+      <c r="N320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -6115,9 +8497,16 @@
       <c r="D321" t="n">
         <v>12480.6</v>
       </c>
-      <c r="E321" t="n">
-        <v>7.0409</v>
-      </c>
+      <c r="E321" t="inlineStr"/>
+      <c r="F321" t="inlineStr"/>
+      <c r="G321" t="inlineStr"/>
+      <c r="H321" t="inlineStr"/>
+      <c r="I321" t="inlineStr"/>
+      <c r="J321" t="inlineStr"/>
+      <c r="K321" t="inlineStr"/>
+      <c r="L321" t="inlineStr"/>
+      <c r="M321" t="inlineStr"/>
+      <c r="N321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -6134,9 +8523,16 @@
       <c r="D322" t="n">
         <v>12748.63</v>
       </c>
-      <c r="E322" t="n">
-        <v>7.0285</v>
-      </c>
+      <c r="E322" t="inlineStr"/>
+      <c r="F322" t="inlineStr"/>
+      <c r="G322" t="inlineStr"/>
+      <c r="H322" t="inlineStr"/>
+      <c r="I322" t="inlineStr"/>
+      <c r="J322" t="inlineStr"/>
+      <c r="K322" t="inlineStr"/>
+      <c r="L322" t="inlineStr"/>
+      <c r="M322" t="inlineStr"/>
+      <c r="N322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -6153,9 +8549,16 @@
       <c r="D323" t="n">
         <v>13198.72</v>
       </c>
-      <c r="E323" t="n">
-        <v>7.0285</v>
-      </c>
+      <c r="E323" t="inlineStr"/>
+      <c r="F323" t="inlineStr"/>
+      <c r="G323" t="inlineStr"/>
+      <c r="H323" t="inlineStr"/>
+      <c r="I323" t="inlineStr"/>
+      <c r="J323" t="inlineStr"/>
+      <c r="K323" t="inlineStr"/>
+      <c r="L323" t="inlineStr"/>
+      <c r="M323" t="inlineStr"/>
+      <c r="N323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -6172,9 +8575,16 @@
       <c r="D324" t="n">
         <v>14095.3</v>
       </c>
-      <c r="E324" t="n">
-        <v>7.0285</v>
-      </c>
+      <c r="E324" t="inlineStr"/>
+      <c r="F324" t="inlineStr"/>
+      <c r="G324" t="inlineStr"/>
+      <c r="H324" t="inlineStr"/>
+      <c r="I324" t="inlineStr"/>
+      <c r="J324" t="inlineStr"/>
+      <c r="K324" t="inlineStr"/>
+      <c r="L324" t="inlineStr"/>
+      <c r="M324" t="inlineStr"/>
+      <c r="N324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -6191,9 +8601,16 @@
       <c r="D325" t="n">
         <v>14095.3</v>
       </c>
-      <c r="E325" t="n">
-        <v>7.0285</v>
-      </c>
+      <c r="E325" t="inlineStr"/>
+      <c r="F325" t="inlineStr"/>
+      <c r="G325" t="inlineStr"/>
+      <c r="H325" t="inlineStr"/>
+      <c r="I325" t="inlineStr"/>
+      <c r="J325" t="inlineStr"/>
+      <c r="K325" t="inlineStr"/>
+      <c r="L325" t="inlineStr"/>
+      <c r="M325" t="inlineStr"/>
+      <c r="N325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -6210,9 +8627,16 @@
       <c r="D326" t="n">
         <v>14095.3</v>
       </c>
-      <c r="E326" t="n">
-        <v>7.0285</v>
-      </c>
+      <c r="E326" t="inlineStr"/>
+      <c r="F326" t="inlineStr"/>
+      <c r="G326" t="inlineStr"/>
+      <c r="H326" t="inlineStr"/>
+      <c r="I326" t="inlineStr"/>
+      <c r="J326" t="inlineStr"/>
+      <c r="K326" t="inlineStr"/>
+      <c r="L326" t="inlineStr"/>
+      <c r="M326" t="inlineStr"/>
+      <c r="N326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -6229,9 +8653,16 @@
       <c r="D327" t="n">
         <v>14861.35</v>
       </c>
-      <c r="E327" t="n">
-        <v>7.0285</v>
-      </c>
+      <c r="E327" t="inlineStr"/>
+      <c r="F327" t="inlineStr"/>
+      <c r="G327" t="inlineStr"/>
+      <c r="H327" t="inlineStr"/>
+      <c r="I327" t="inlineStr"/>
+      <c r="J327" t="inlineStr"/>
+      <c r="K327" t="inlineStr"/>
+      <c r="L327" t="inlineStr"/>
+      <c r="M327" t="inlineStr"/>
+      <c r="N327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -6248,9 +8679,16 @@
       <c r="D328" t="n">
         <v>14862.62</v>
       </c>
-      <c r="E328" t="n">
-        <v>7.0059</v>
-      </c>
+      <c r="E328" t="inlineStr"/>
+      <c r="F328" t="inlineStr"/>
+      <c r="G328" t="inlineStr"/>
+      <c r="H328" t="inlineStr"/>
+      <c r="I328" t="inlineStr"/>
+      <c r="J328" t="inlineStr"/>
+      <c r="K328" t="inlineStr"/>
+      <c r="L328" t="inlineStr"/>
+      <c r="M328" t="inlineStr"/>
+      <c r="N328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -6267,9 +8705,16 @@
       <c r="D329" t="n">
         <v>14960.52</v>
       </c>
-      <c r="E329" t="n">
-        <v>6.9964</v>
-      </c>
+      <c r="E329" t="inlineStr"/>
+      <c r="F329" t="inlineStr"/>
+      <c r="G329" t="inlineStr"/>
+      <c r="H329" t="inlineStr"/>
+      <c r="I329" t="inlineStr"/>
+      <c r="J329" t="inlineStr"/>
+      <c r="K329" t="inlineStr"/>
+      <c r="L329" t="inlineStr"/>
+      <c r="M329" t="inlineStr"/>
+      <c r="N329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -6286,9 +8731,16 @@
       <c r="D330" t="n">
         <v>14960.52</v>
       </c>
-      <c r="E330" t="n">
-        <v>6.9964</v>
-      </c>
+      <c r="E330" t="inlineStr"/>
+      <c r="F330" t="inlineStr"/>
+      <c r="G330" t="inlineStr"/>
+      <c r="H330" t="inlineStr"/>
+      <c r="I330" t="inlineStr"/>
+      <c r="J330" t="inlineStr"/>
+      <c r="K330" t="inlineStr"/>
+      <c r="L330" t="inlineStr"/>
+      <c r="M330" t="inlineStr"/>
+      <c r="N330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -6305,9 +8757,16 @@
       <c r="D331" t="n">
         <v>14960.52</v>
       </c>
-      <c r="E331" t="n">
-        <v>6.9964</v>
-      </c>
+      <c r="E331" t="inlineStr"/>
+      <c r="F331" t="inlineStr"/>
+      <c r="G331" t="inlineStr"/>
+      <c r="H331" t="inlineStr"/>
+      <c r="I331" t="inlineStr"/>
+      <c r="J331" t="inlineStr"/>
+      <c r="K331" t="inlineStr"/>
+      <c r="L331" t="inlineStr"/>
+      <c r="M331" t="inlineStr"/>
+      <c r="N331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -6324,9 +8783,16 @@
       <c r="D332" t="n">
         <v>14960.52</v>
       </c>
-      <c r="E332" t="n">
-        <v>6.9938</v>
-      </c>
+      <c r="E332" t="inlineStr"/>
+      <c r="F332" t="inlineStr"/>
+      <c r="G332" t="inlineStr"/>
+      <c r="H332" t="inlineStr"/>
+      <c r="I332" t="inlineStr"/>
+      <c r="J332" t="inlineStr"/>
+      <c r="K332" t="inlineStr"/>
+      <c r="L332" t="inlineStr"/>
+      <c r="M332" t="inlineStr"/>
+      <c r="N332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -6343,9 +8809,16 @@
       <c r="D333" t="n">
         <v>14960.52</v>
       </c>
-      <c r="E333" t="n">
-        <v>6.9938</v>
-      </c>
+      <c r="E333" t="inlineStr"/>
+      <c r="F333" t="inlineStr"/>
+      <c r="G333" t="inlineStr"/>
+      <c r="H333" t="inlineStr"/>
+      <c r="I333" t="inlineStr"/>
+      <c r="J333" t="inlineStr"/>
+      <c r="K333" t="inlineStr"/>
+      <c r="L333" t="inlineStr"/>
+      <c r="M333" t="inlineStr"/>
+      <c r="N333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -6362,9 +8835,16 @@
       <c r="D334" t="n">
         <v>15106.81</v>
       </c>
-      <c r="E334" t="n">
-        <v>6.9938</v>
-      </c>
+      <c r="E334" t="inlineStr"/>
+      <c r="F334" t="inlineStr"/>
+      <c r="G334" t="inlineStr"/>
+      <c r="H334" t="inlineStr"/>
+      <c r="I334" t="inlineStr"/>
+      <c r="J334" t="inlineStr"/>
+      <c r="K334" t="inlineStr"/>
+      <c r="L334" t="inlineStr"/>
+      <c r="M334" t="inlineStr"/>
+      <c r="N334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -6381,9 +8861,16 @@
       <c r="D335" t="n">
         <v>16116.07</v>
       </c>
-      <c r="E335" t="n">
-        <v>6.9886</v>
-      </c>
+      <c r="E335" t="inlineStr"/>
+      <c r="F335" t="inlineStr"/>
+      <c r="G335" t="inlineStr"/>
+      <c r="H335" t="inlineStr"/>
+      <c r="I335" t="inlineStr"/>
+      <c r="J335" t="inlineStr"/>
+      <c r="K335" t="inlineStr"/>
+      <c r="L335" t="inlineStr"/>
+      <c r="M335" t="inlineStr"/>
+      <c r="N335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -6400,9 +8887,16 @@
       <c r="D336" t="n">
         <v>16870.14</v>
       </c>
-      <c r="E336" t="n">
-        <v>6.9837</v>
-      </c>
+      <c r="E336" t="inlineStr"/>
+      <c r="F336" t="inlineStr"/>
+      <c r="G336" t="inlineStr"/>
+      <c r="H336" t="inlineStr"/>
+      <c r="I336" t="inlineStr"/>
+      <c r="J336" t="inlineStr"/>
+      <c r="K336" t="inlineStr"/>
+      <c r="L336" t="inlineStr"/>
+      <c r="M336" t="inlineStr"/>
+      <c r="N336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -6419,9 +8913,16 @@
       <c r="D337" t="n">
         <v>17475.53</v>
       </c>
-      <c r="E337" t="n">
-        <v>6.9972</v>
-      </c>
+      <c r="E337" t="inlineStr"/>
+      <c r="F337" t="inlineStr"/>
+      <c r="G337" t="inlineStr"/>
+      <c r="H337" t="inlineStr"/>
+      <c r="I337" t="inlineStr"/>
+      <c r="J337" t="inlineStr"/>
+      <c r="K337" t="inlineStr"/>
+      <c r="L337" t="inlineStr"/>
+      <c r="M337" t="inlineStr"/>
+      <c r="N337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -6438,9 +8939,16 @@
       <c r="D338" t="n">
         <v>17700.38</v>
       </c>
-      <c r="E338" t="n">
-        <v>6.9838</v>
-      </c>
+      <c r="E338" t="inlineStr"/>
+      <c r="F338" t="inlineStr"/>
+      <c r="G338" t="inlineStr"/>
+      <c r="H338" t="inlineStr"/>
+      <c r="I338" t="inlineStr"/>
+      <c r="J338" t="inlineStr"/>
+      <c r="K338" t="inlineStr"/>
+      <c r="L338" t="inlineStr"/>
+      <c r="M338" t="inlineStr"/>
+      <c r="N338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -6457,9 +8965,16 @@
       <c r="D339" t="n">
         <v>17700.38</v>
       </c>
-      <c r="E339" t="n">
-        <v>6.9774</v>
-      </c>
+      <c r="E339" t="inlineStr"/>
+      <c r="F339" t="inlineStr"/>
+      <c r="G339" t="inlineStr"/>
+      <c r="H339" t="inlineStr"/>
+      <c r="I339" t="inlineStr"/>
+      <c r="J339" t="inlineStr"/>
+      <c r="K339" t="inlineStr"/>
+      <c r="L339" t="inlineStr"/>
+      <c r="M339" t="inlineStr"/>
+      <c r="N339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -6476,9 +8991,16 @@
       <c r="D340" t="n">
         <v>17700.38</v>
       </c>
-      <c r="E340" t="n">
-        <v>6.9773</v>
-      </c>
+      <c r="E340" t="inlineStr"/>
+      <c r="F340" t="inlineStr"/>
+      <c r="G340" t="inlineStr"/>
+      <c r="H340" t="inlineStr"/>
+      <c r="I340" t="inlineStr"/>
+      <c r="J340" t="inlineStr"/>
+      <c r="K340" t="inlineStr"/>
+      <c r="L340" t="inlineStr"/>
+      <c r="M340" t="inlineStr"/>
+      <c r="N340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -6495,9 +9017,16 @@
       <c r="D341" t="n">
         <v>19235.69</v>
       </c>
-      <c r="E341" t="n">
-        <v>6.9773</v>
-      </c>
+      <c r="E341" t="inlineStr"/>
+      <c r="F341" t="inlineStr"/>
+      <c r="G341" t="inlineStr"/>
+      <c r="H341" t="inlineStr"/>
+      <c r="I341" t="inlineStr"/>
+      <c r="J341" t="inlineStr"/>
+      <c r="K341" t="inlineStr"/>
+      <c r="L341" t="inlineStr"/>
+      <c r="M341" t="inlineStr"/>
+      <c r="N341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -6514,9 +9043,16 @@
       <c r="D342" t="n">
         <v>20183.67</v>
       </c>
-      <c r="E342" t="n">
-        <v>6.9732</v>
-      </c>
+      <c r="E342" t="inlineStr"/>
+      <c r="F342" t="inlineStr"/>
+      <c r="G342" t="inlineStr"/>
+      <c r="H342" t="inlineStr"/>
+      <c r="I342" t="inlineStr"/>
+      <c r="J342" t="inlineStr"/>
+      <c r="K342" t="inlineStr"/>
+      <c r="L342" t="inlineStr"/>
+      <c r="M342" t="inlineStr"/>
+      <c r="N342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -6533,9 +9069,16 @@
       <c r="D343" t="n">
         <v>20855.45</v>
       </c>
-      <c r="E343" t="n">
-        <v>6.9639</v>
-      </c>
+      <c r="E343" t="inlineStr"/>
+      <c r="F343" t="inlineStr"/>
+      <c r="G343" t="inlineStr"/>
+      <c r="H343" t="inlineStr"/>
+      <c r="I343" t="inlineStr"/>
+      <c r="J343" t="inlineStr"/>
+      <c r="K343" t="inlineStr"/>
+      <c r="L343" t="inlineStr"/>
+      <c r="M343" t="inlineStr"/>
+      <c r="N343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -6552,9 +9095,16 @@
       <c r="D344" t="n">
         <v>19944.44</v>
       </c>
-      <c r="E344" t="n">
-        <v>6.8728</v>
-      </c>
+      <c r="E344" t="inlineStr"/>
+      <c r="F344" t="inlineStr"/>
+      <c r="G344" t="inlineStr"/>
+      <c r="H344" t="inlineStr"/>
+      <c r="I344" t="inlineStr"/>
+      <c r="J344" t="inlineStr"/>
+      <c r="K344" t="inlineStr"/>
+      <c r="L344" t="inlineStr"/>
+      <c r="M344" t="inlineStr"/>
+      <c r="N344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -6571,9 +9121,16 @@
       <c r="D345" t="n">
         <v>19529.09</v>
       </c>
-      <c r="E345" t="n">
-        <v>6.873</v>
-      </c>
+      <c r="E345" t="inlineStr"/>
+      <c r="F345" t="inlineStr"/>
+      <c r="G345" t="inlineStr"/>
+      <c r="H345" t="inlineStr"/>
+      <c r="I345" t="inlineStr"/>
+      <c r="J345" t="inlineStr"/>
+      <c r="K345" t="inlineStr"/>
+      <c r="L345" t="inlineStr"/>
+      <c r="M345" t="inlineStr"/>
+      <c r="N345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -6590,9 +9147,16 @@
       <c r="D346" t="n">
         <v>19106.04</v>
       </c>
-      <c r="E346" t="n">
-        <v>6.9004</v>
-      </c>
+      <c r="E346" t="inlineStr"/>
+      <c r="F346" t="inlineStr"/>
+      <c r="G346" t="inlineStr"/>
+      <c r="H346" t="inlineStr"/>
+      <c r="I346" t="inlineStr"/>
+      <c r="J346" t="inlineStr"/>
+      <c r="K346" t="inlineStr"/>
+      <c r="L346" t="inlineStr"/>
+      <c r="M346" t="inlineStr"/>
+      <c r="N346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -6609,9 +9173,16 @@
       <c r="D347" t="n">
         <v>19106.04</v>
       </c>
-      <c r="E347" t="n">
-        <v>6.8864</v>
-      </c>
+      <c r="E347" t="inlineStr"/>
+      <c r="F347" t="inlineStr"/>
+      <c r="G347" t="inlineStr"/>
+      <c r="H347" t="inlineStr"/>
+      <c r="I347" t="inlineStr"/>
+      <c r="J347" t="inlineStr"/>
+      <c r="K347" t="inlineStr"/>
+      <c r="L347" t="inlineStr"/>
+      <c r="M347" t="inlineStr"/>
+      <c r="N347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -6628,9 +9199,16 @@
       <c r="D348" t="n">
         <v>19106.04</v>
       </c>
-      <c r="E348" t="n">
-        <v>6.8864</v>
-      </c>
+      <c r="E348" t="inlineStr"/>
+      <c r="F348" t="inlineStr"/>
+      <c r="G348" t="inlineStr"/>
+      <c r="H348" t="inlineStr"/>
+      <c r="I348" t="inlineStr"/>
+      <c r="J348" t="inlineStr"/>
+      <c r="K348" t="inlineStr"/>
+      <c r="L348" t="inlineStr"/>
+      <c r="M348" t="inlineStr"/>
+      <c r="N348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -6647,9 +9225,16 @@
       <c r="D349" t="n">
         <v>18714.15</v>
       </c>
-      <c r="E349" t="n">
-        <v>6.8864</v>
-      </c>
+      <c r="E349" t="inlineStr"/>
+      <c r="F349" t="inlineStr"/>
+      <c r="G349" t="inlineStr"/>
+      <c r="H349" t="inlineStr"/>
+      <c r="I349" t="inlineStr"/>
+      <c r="J349" t="inlineStr"/>
+      <c r="K349" t="inlineStr"/>
+      <c r="L349" t="inlineStr"/>
+      <c r="M349" t="inlineStr"/>
+      <c r="N349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -6666,9 +9251,16 @@
       <c r="D350" t="n">
         <v>18894.26</v>
       </c>
-      <c r="E350" t="n">
-        <v>6.8805</v>
-      </c>
+      <c r="E350" t="inlineStr"/>
+      <c r="F350" t="inlineStr"/>
+      <c r="G350" t="inlineStr"/>
+      <c r="H350" t="inlineStr"/>
+      <c r="I350" t="inlineStr"/>
+      <c r="J350" t="inlineStr"/>
+      <c r="K350" t="inlineStr"/>
+      <c r="L350" t="inlineStr"/>
+      <c r="M350" t="inlineStr"/>
+      <c r="N350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -6685,9 +9277,16 @@
       <c r="D351" t="n">
         <v>19547.47</v>
       </c>
-      <c r="E351" t="n">
-        <v>6.8927</v>
-      </c>
+      <c r="E351" t="inlineStr"/>
+      <c r="F351" t="inlineStr"/>
+      <c r="G351" t="inlineStr"/>
+      <c r="H351" t="inlineStr"/>
+      <c r="I351" t="inlineStr"/>
+      <c r="J351" t="inlineStr"/>
+      <c r="K351" t="inlineStr"/>
+      <c r="L351" t="inlineStr"/>
+      <c r="M351" t="inlineStr"/>
+      <c r="N351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -6704,9 +9303,16 @@
       <c r="D352" t="n">
         <v>20010.92</v>
       </c>
-      <c r="E352" t="n">
-        <v>6.9015</v>
-      </c>
+      <c r="E352" t="inlineStr"/>
+      <c r="F352" t="inlineStr"/>
+      <c r="G352" t="inlineStr"/>
+      <c r="H352" t="inlineStr"/>
+      <c r="I352" t="inlineStr"/>
+      <c r="J352" t="inlineStr"/>
+      <c r="K352" t="inlineStr"/>
+      <c r="L352" t="inlineStr"/>
+      <c r="M352" t="inlineStr"/>
+      <c r="N352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -6723,9 +9329,16 @@
       <c r="D353" t="n">
         <v>20160.77</v>
       </c>
-      <c r="E353" t="n">
-        <v>6.9114</v>
-      </c>
+      <c r="E353" t="inlineStr"/>
+      <c r="F353" t="inlineStr"/>
+      <c r="G353" t="inlineStr"/>
+      <c r="H353" t="inlineStr"/>
+      <c r="I353" t="inlineStr"/>
+      <c r="J353" t="inlineStr"/>
+      <c r="K353" t="inlineStr"/>
+      <c r="L353" t="inlineStr"/>
+      <c r="M353" t="inlineStr"/>
+      <c r="N353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -6742,9 +9355,16 @@
       <c r="D354" t="n">
         <v>20160.77</v>
       </c>
-      <c r="E354" t="n">
-        <v>6.9118</v>
-      </c>
+      <c r="E354" t="inlineStr"/>
+      <c r="F354" t="inlineStr"/>
+      <c r="G354" t="inlineStr"/>
+      <c r="H354" t="inlineStr"/>
+      <c r="I354" t="inlineStr"/>
+      <c r="J354" t="inlineStr"/>
+      <c r="K354" t="inlineStr"/>
+      <c r="L354" t="inlineStr"/>
+      <c r="M354" t="inlineStr"/>
+      <c r="N354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -6761,9 +9381,16 @@
       <c r="D355" t="n">
         <v>20160.77</v>
       </c>
-      <c r="E355" t="n">
-        <v>6.9118</v>
-      </c>
+      <c r="E355" t="inlineStr"/>
+      <c r="F355" t="inlineStr"/>
+      <c r="G355" t="inlineStr"/>
+      <c r="H355" t="inlineStr"/>
+      <c r="I355" t="inlineStr"/>
+      <c r="J355" t="inlineStr"/>
+      <c r="K355" t="inlineStr"/>
+      <c r="L355" t="inlineStr"/>
+      <c r="M355" t="inlineStr"/>
+      <c r="N355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -6780,9 +9407,16 @@
       <c r="D356" t="n">
         <v>20991.08</v>
       </c>
-      <c r="E356" t="n">
-        <v>6.9118</v>
-      </c>
+      <c r="E356" t="inlineStr"/>
+      <c r="F356" t="inlineStr"/>
+      <c r="G356" t="inlineStr"/>
+      <c r="H356" t="inlineStr"/>
+      <c r="I356" t="inlineStr"/>
+      <c r="J356" t="inlineStr"/>
+      <c r="K356" t="inlineStr"/>
+      <c r="L356" t="inlineStr"/>
+      <c r="M356" t="inlineStr"/>
+      <c r="N356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -6799,9 +9433,16 @@
       <c r="D357" t="n">
         <v>22511.89</v>
       </c>
-      <c r="E357" t="n">
-        <v>6.8374</v>
-      </c>
+      <c r="E357" t="inlineStr"/>
+      <c r="F357" t="inlineStr"/>
+      <c r="G357" t="inlineStr"/>
+      <c r="H357" t="inlineStr"/>
+      <c r="I357" t="inlineStr"/>
+      <c r="J357" t="inlineStr"/>
+      <c r="K357" t="inlineStr"/>
+      <c r="L357" t="inlineStr"/>
+      <c r="M357" t="inlineStr"/>
+      <c r="N357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -6818,9 +9459,16 @@
       <c r="D358" t="n">
         <v>22823.43</v>
       </c>
-      <c r="E358" t="n">
-        <v>6.8383</v>
-      </c>
+      <c r="E358" t="inlineStr"/>
+      <c r="F358" t="inlineStr"/>
+      <c r="G358" t="inlineStr"/>
+      <c r="H358" t="inlineStr"/>
+      <c r="I358" t="inlineStr"/>
+      <c r="J358" t="inlineStr"/>
+      <c r="K358" t="inlineStr"/>
+      <c r="L358" t="inlineStr"/>
+      <c r="M358" t="inlineStr"/>
+      <c r="N358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -6837,9 +9485,16 @@
       <c r="D359" t="n">
         <v>22823.43</v>
       </c>
-      <c r="E359" t="n">
-        <v>6.8282</v>
-      </c>
+      <c r="E359" t="inlineStr"/>
+      <c r="F359" t="inlineStr"/>
+      <c r="G359" t="inlineStr"/>
+      <c r="H359" t="inlineStr"/>
+      <c r="I359" t="inlineStr"/>
+      <c r="J359" t="inlineStr"/>
+      <c r="K359" t="inlineStr"/>
+      <c r="L359" t="inlineStr"/>
+      <c r="M359" t="inlineStr"/>
+      <c r="N359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -6856,9 +9511,16 @@
       <c r="D360" t="n">
         <v>22823.43</v>
       </c>
-      <c r="E360" t="n">
-        <v>6.8283</v>
-      </c>
+      <c r="E360" t="inlineStr"/>
+      <c r="F360" t="inlineStr"/>
+      <c r="G360" t="inlineStr"/>
+      <c r="H360" t="inlineStr"/>
+      <c r="I360" t="inlineStr"/>
+      <c r="J360" t="inlineStr"/>
+      <c r="K360" t="inlineStr"/>
+      <c r="L360" t="inlineStr"/>
+      <c r="M360" t="inlineStr"/>
+      <c r="N360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -6875,9 +9537,16 @@
       <c r="D361" t="n">
         <v>22823.43</v>
       </c>
-      <c r="E361" t="n">
-        <v>6.8283</v>
-      </c>
+      <c r="E361" t="inlineStr"/>
+      <c r="F361" t="inlineStr"/>
+      <c r="G361" t="inlineStr"/>
+      <c r="H361" t="inlineStr"/>
+      <c r="I361" t="inlineStr"/>
+      <c r="J361" t="inlineStr"/>
+      <c r="K361" t="inlineStr"/>
+      <c r="L361" t="inlineStr"/>
+      <c r="M361" t="inlineStr"/>
+      <c r="N361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -6894,9 +9563,16 @@
       <c r="D362" t="n">
         <v>22823.43</v>
       </c>
-      <c r="E362" t="n">
-        <v>6.8282</v>
-      </c>
+      <c r="E362" t="inlineStr"/>
+      <c r="F362" t="inlineStr"/>
+      <c r="G362" t="inlineStr"/>
+      <c r="H362" t="inlineStr"/>
+      <c r="I362" t="inlineStr"/>
+      <c r="J362" t="inlineStr"/>
+      <c r="K362" t="inlineStr"/>
+      <c r="L362" t="inlineStr"/>
+      <c r="M362" t="inlineStr"/>
+      <c r="N362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -6913,9 +9589,16 @@
       <c r="D363" t="n">
         <v>22823.43</v>
       </c>
-      <c r="E363" t="n">
-        <v>6.8302</v>
-      </c>
+      <c r="E363" t="inlineStr"/>
+      <c r="F363" t="inlineStr"/>
+      <c r="G363" t="inlineStr"/>
+      <c r="H363" t="inlineStr"/>
+      <c r="I363" t="inlineStr"/>
+      <c r="J363" t="inlineStr"/>
+      <c r="K363" t="inlineStr"/>
+      <c r="L363" t="inlineStr"/>
+      <c r="M363" t="inlineStr"/>
+      <c r="N363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -6932,9 +9615,16 @@
       <c r="D364" t="n">
         <v>24263.27</v>
       </c>
-      <c r="E364" t="n">
-        <v>6.8304</v>
-      </c>
+      <c r="E364" t="inlineStr"/>
+      <c r="F364" t="inlineStr"/>
+      <c r="G364" t="inlineStr"/>
+      <c r="H364" t="inlineStr"/>
+      <c r="I364" t="inlineStr"/>
+      <c r="J364" t="inlineStr"/>
+      <c r="K364" t="inlineStr"/>
+      <c r="L364" t="inlineStr"/>
+      <c r="M364" t="inlineStr"/>
+      <c r="N364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -6951,9 +9641,16 @@
       <c r="D365" t="n">
         <v>24700.24</v>
       </c>
-      <c r="E365" t="n">
-        <v>6.8113</v>
-      </c>
+      <c r="E365" t="inlineStr"/>
+      <c r="F365" t="inlineStr"/>
+      <c r="G365" t="inlineStr"/>
+      <c r="H365" t="inlineStr"/>
+      <c r="I365" t="inlineStr"/>
+      <c r="J365" t="inlineStr"/>
+      <c r="K365" t="inlineStr"/>
+      <c r="L365" t="inlineStr"/>
+      <c r="M365" t="inlineStr"/>
+      <c r="N365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -6970,9 +9667,16 @@
       <c r="D366" t="n">
         <v>25143</v>
       </c>
-      <c r="E366" t="n">
-        <v>6.8008</v>
-      </c>
+      <c r="E366" t="inlineStr"/>
+      <c r="F366" t="inlineStr"/>
+      <c r="G366" t="inlineStr"/>
+      <c r="H366" t="inlineStr"/>
+      <c r="I366" t="inlineStr"/>
+      <c r="J366" t="inlineStr"/>
+      <c r="K366" t="inlineStr"/>
+      <c r="L366" t="inlineStr"/>
+      <c r="M366" t="inlineStr"/>
+      <c r="N366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -6989,9 +9693,16 @@
       <c r="D367" t="n">
         <v>25143</v>
       </c>
-      <c r="E367" t="n">
-        <v>6.8008</v>
-      </c>
+      <c r="E367" t="inlineStr"/>
+      <c r="F367" t="inlineStr"/>
+      <c r="G367" t="inlineStr"/>
+      <c r="H367" t="inlineStr"/>
+      <c r="I367" t="inlineStr"/>
+      <c r="J367" t="inlineStr"/>
+      <c r="K367" t="inlineStr"/>
+      <c r="L367" t="inlineStr"/>
+      <c r="M367" t="inlineStr"/>
+      <c r="N367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -7008,9 +9719,16 @@
       <c r="D368" t="n">
         <v>25305</v>
       </c>
-      <c r="E368" t="n">
-        <v>6.8008</v>
-      </c>
+      <c r="E368" t="inlineStr"/>
+      <c r="F368" t="inlineStr"/>
+      <c r="G368" t="inlineStr"/>
+      <c r="H368" t="inlineStr"/>
+      <c r="I368" t="inlineStr"/>
+      <c r="J368" t="inlineStr"/>
+      <c r="K368" t="inlineStr"/>
+      <c r="L368" t="inlineStr"/>
+      <c r="M368" t="inlineStr"/>
+      <c r="N368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -7027,8 +9745,61 @@
       <c r="D369" t="n">
         <v>25984.17</v>
       </c>
-      <c r="E369" t="n">
-        <v>6.795</v>
+      <c r="E369" t="inlineStr"/>
+      <c r="F369" t="inlineStr"/>
+      <c r="G369" t="inlineStr"/>
+      <c r="H369" t="inlineStr"/>
+      <c r="I369" t="inlineStr"/>
+      <c r="J369" t="inlineStr"/>
+      <c r="K369" t="inlineStr"/>
+      <c r="L369" t="inlineStr"/>
+      <c r="M369" t="inlineStr"/>
+      <c r="N369" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-05-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>200500</v>
+      </c>
+      <c r="C370" t="n">
+        <v>29426.87</v>
+      </c>
+      <c r="D370" t="n">
+        <v>26041.48</v>
+      </c>
+      <c r="E370" t="n">
+        <v>108500</v>
+      </c>
+      <c r="F370" t="n">
+        <v>15924.27</v>
+      </c>
+      <c r="G370" t="n">
+        <v>14092.27</v>
+      </c>
+      <c r="H370" t="n">
+        <v>24560</v>
+      </c>
+      <c r="I370" t="n">
+        <v>3604.61</v>
+      </c>
+      <c r="J370" t="n">
+        <v>3189.92</v>
+      </c>
+      <c r="K370" t="n">
+        <v>102000</v>
+      </c>
+      <c r="L370" t="n">
+        <v>14970.28</v>
+      </c>
+      <c r="M370" t="n">
+        <v>13248.04</v>
+      </c>
+      <c r="N370" t="n">
+        <v>0.1472298699960248</v>
       </c>
     </row>
   </sheetData>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N370"/>
+  <dimension ref="A1:N371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9802,6 +9802,52 @@
         <v>0.1472298699960248</v>
       </c>
     </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-05-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>200500</v>
+      </c>
+      <c r="C371" t="n">
+        <v>29426.87</v>
+      </c>
+      <c r="D371" t="n">
+        <v>26041.48</v>
+      </c>
+      <c r="E371" t="n">
+        <v>108500</v>
+      </c>
+      <c r="F371" t="n">
+        <v>15924.27</v>
+      </c>
+      <c r="G371" t="n">
+        <v>14092.27</v>
+      </c>
+      <c r="H371" t="n">
+        <v>24560</v>
+      </c>
+      <c r="I371" t="n">
+        <v>3604.61</v>
+      </c>
+      <c r="J371" t="n">
+        <v>3189.92</v>
+      </c>
+      <c r="K371" t="n">
+        <v>102000</v>
+      </c>
+      <c r="L371" t="n">
+        <v>14970.28</v>
+      </c>
+      <c r="M371" t="n">
+        <v>13248.04</v>
+      </c>
+      <c r="N371" t="n">
+        <v>0.1472298699960248</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N371"/>
+  <dimension ref="A1:N372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9848,6 +9848,52 @@
         <v>0.1472298699960248</v>
       </c>
     </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-05-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>195000</v>
+      </c>
+      <c r="C372" t="n">
+        <v>28662.56</v>
+      </c>
+      <c r="D372" t="n">
+        <v>25365.1</v>
+      </c>
+      <c r="E372" t="n">
+        <v>107380</v>
+      </c>
+      <c r="F372" t="n">
+        <v>15783.52</v>
+      </c>
+      <c r="G372" t="n">
+        <v>13967.71</v>
+      </c>
+      <c r="H372" t="n">
+        <v>24610</v>
+      </c>
+      <c r="I372" t="n">
+        <v>3617.36</v>
+      </c>
+      <c r="J372" t="n">
+        <v>3201.21</v>
+      </c>
+      <c r="K372" t="n">
+        <v>102500</v>
+      </c>
+      <c r="L372" t="n">
+        <v>15066.22</v>
+      </c>
+      <c r="M372" t="n">
+        <v>13332.94</v>
+      </c>
+      <c r="N372" t="n">
+        <v>0.1472537181563834</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N372"/>
+  <dimension ref="A1:N373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9894,6 +9894,52 @@
         <v>0.1472537181563834</v>
       </c>
     </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-05-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>192000</v>
+      </c>
+      <c r="C373" t="n">
+        <v>28204.6</v>
+      </c>
+      <c r="D373" t="n">
+        <v>24959.82</v>
+      </c>
+      <c r="E373" t="n">
+        <v>105540</v>
+      </c>
+      <c r="F373" t="n">
+        <v>15503.72</v>
+      </c>
+      <c r="G373" t="n">
+        <v>13720.1</v>
+      </c>
+      <c r="H373" t="n">
+        <v>24370</v>
+      </c>
+      <c r="I373" t="n">
+        <v>3579.93</v>
+      </c>
+      <c r="J373" t="n">
+        <v>3168.08</v>
+      </c>
+      <c r="K373" t="n">
+        <v>106500</v>
+      </c>
+      <c r="L373" t="n">
+        <v>15644.74</v>
+      </c>
+      <c r="M373" t="n">
+        <v>13844.9</v>
+      </c>
+      <c r="N373" t="n">
+        <v>0.1473817629806488</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N373"/>
+  <dimension ref="A1:N374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9940,6 +9940,52 @@
         <v>0.1473817629806488</v>
       </c>
     </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-05-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>192000</v>
+      </c>
+      <c r="C374" t="n">
+        <v>28204.6</v>
+      </c>
+      <c r="D374" t="n">
+        <v>24959.82</v>
+      </c>
+      <c r="E374" t="n">
+        <v>105540</v>
+      </c>
+      <c r="F374" t="n">
+        <v>15503.72</v>
+      </c>
+      <c r="G374" t="n">
+        <v>13720.1</v>
+      </c>
+      <c r="H374" t="n">
+        <v>24370</v>
+      </c>
+      <c r="I374" t="n">
+        <v>3579.93</v>
+      </c>
+      <c r="J374" t="n">
+        <v>3168.08</v>
+      </c>
+      <c r="K374" t="n">
+        <v>106500</v>
+      </c>
+      <c r="L374" t="n">
+        <v>15644.74</v>
+      </c>
+      <c r="M374" t="n">
+        <v>13844.9</v>
+      </c>
+      <c r="N374" t="n">
+        <v>0.1468450344351606</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N374"/>
+  <dimension ref="A1:N375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9986,6 +9986,52 @@
         <v>0.1468450344351606</v>
       </c>
     </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-05-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>191500</v>
+      </c>
+      <c r="C375" t="n">
+        <v>28026.58</v>
+      </c>
+      <c r="D375" t="n">
+        <v>24802.28</v>
+      </c>
+      <c r="E375" t="n">
+        <v>104130</v>
+      </c>
+      <c r="F375" t="n">
+        <v>15239.73</v>
+      </c>
+      <c r="G375" t="n">
+        <v>13486.48</v>
+      </c>
+      <c r="H375" t="n">
+        <v>24050</v>
+      </c>
+      <c r="I375" t="n">
+        <v>3519.79</v>
+      </c>
+      <c r="J375" t="n">
+        <v>3114.86</v>
+      </c>
+      <c r="K375" t="n">
+        <v>112500</v>
+      </c>
+      <c r="L375" t="n">
+        <v>16464.7</v>
+      </c>
+      <c r="M375" t="n">
+        <v>14570.53</v>
+      </c>
+      <c r="N375" t="n">
+        <v>0.1468450344351606</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N375"/>
+  <dimension ref="A1:N376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10032,6 +10032,52 @@
         <v>0.1468450344351606</v>
       </c>
     </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-05-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>186500</v>
+      </c>
+      <c r="C376" t="n">
+        <v>27347.65</v>
+      </c>
+      <c r="D376" t="n">
+        <v>24201.46</v>
+      </c>
+      <c r="E376" t="n">
+        <v>104265</v>
+      </c>
+      <c r="F376" t="n">
+        <v>15289.02</v>
+      </c>
+      <c r="G376" t="n">
+        <v>13530.11</v>
+      </c>
+      <c r="H376" t="n">
+        <v>24200</v>
+      </c>
+      <c r="I376" t="n">
+        <v>3548.6</v>
+      </c>
+      <c r="J376" t="n">
+        <v>3140.35</v>
+      </c>
+      <c r="K376" t="n">
+        <v>113000</v>
+      </c>
+      <c r="L376" t="n">
+        <v>16569.89</v>
+      </c>
+      <c r="M376" t="n">
+        <v>14663.62</v>
+      </c>
+      <c r="N376" t="n">
+        <v>0.147054498397106</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N376"/>
+  <dimension ref="A1:N377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10078,6 +10078,52 @@
         <v>0.147054498397106</v>
       </c>
     </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-05-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>179000</v>
+      </c>
+      <c r="C377" t="n">
+        <v>26196.02</v>
+      </c>
+      <c r="D377" t="n">
+        <v>23182.32</v>
+      </c>
+      <c r="E377" t="n">
+        <v>103310</v>
+      </c>
+      <c r="F377" t="n">
+        <v>15119.05</v>
+      </c>
+      <c r="G377" t="n">
+        <v>13379.69</v>
+      </c>
+      <c r="H377" t="n">
+        <v>24260</v>
+      </c>
+      <c r="I377" t="n">
+        <v>3550.37</v>
+      </c>
+      <c r="J377" t="n">
+        <v>3141.92</v>
+      </c>
+      <c r="K377" t="n">
+        <v>113500</v>
+      </c>
+      <c r="L377" t="n">
+        <v>16610.32</v>
+      </c>
+      <c r="M377" t="n">
+        <v>14699.4</v>
+      </c>
+      <c r="N377" t="n">
+        <v>0.1467351430667645</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N377"/>
+  <dimension ref="A1:N378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10124,6 +10124,52 @@
         <v>0.1467351430667645</v>
       </c>
     </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-05-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>182000</v>
+      </c>
+      <c r="C378" t="n">
+        <v>26688.56</v>
+      </c>
+      <c r="D378" t="n">
+        <v>23618.2</v>
+      </c>
+      <c r="E378" t="n">
+        <v>105005</v>
+      </c>
+      <c r="F378" t="n">
+        <v>15397.98</v>
+      </c>
+      <c r="G378" t="n">
+        <v>13626.53</v>
+      </c>
+      <c r="H378" t="n">
+        <v>24390</v>
+      </c>
+      <c r="I378" t="n">
+        <v>3576.56</v>
+      </c>
+      <c r="J378" t="n">
+        <v>3165.1</v>
+      </c>
+      <c r="K378" t="n">
+        <v>114000</v>
+      </c>
+      <c r="L378" t="n">
+        <v>16717.01</v>
+      </c>
+      <c r="M378" t="n">
+        <v>14793.82</v>
+      </c>
+      <c r="N378" t="n">
+        <v>0.1470263912372271</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N378"/>
+  <dimension ref="A1:N379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10170,6 +10170,52 @@
         <v>0.1470263912372271</v>
       </c>
     </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-05-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>178000</v>
+      </c>
+      <c r="C379" t="n">
+        <v>26104.68</v>
+      </c>
+      <c r="D379" t="n">
+        <v>23101.49</v>
+      </c>
+      <c r="E379" t="n">
+        <v>104460</v>
+      </c>
+      <c r="F379" t="n">
+        <v>15319.64</v>
+      </c>
+      <c r="G379" t="n">
+        <v>13557.2</v>
+      </c>
+      <c r="H379" t="n">
+        <v>24350</v>
+      </c>
+      <c r="I379" t="n">
+        <v>3571.06</v>
+      </c>
+      <c r="J379" t="n">
+        <v>3160.23</v>
+      </c>
+      <c r="K379" t="n">
+        <v>114000</v>
+      </c>
+      <c r="L379" t="n">
+        <v>16718.73</v>
+      </c>
+      <c r="M379" t="n">
+        <v>14795.34</v>
+      </c>
+      <c r="N379" t="n">
+        <v>0.1469896519285042</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N379"/>
+  <dimension ref="A1:N380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10216,6 +10216,52 @@
         <v>0.1469896519285042</v>
       </c>
     </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-05-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>178000</v>
+      </c>
+      <c r="C380" t="n">
+        <v>26104.68</v>
+      </c>
+      <c r="D380" t="n">
+        <v>23101.49</v>
+      </c>
+      <c r="E380" t="n">
+        <v>104460</v>
+      </c>
+      <c r="F380" t="n">
+        <v>15319.64</v>
+      </c>
+      <c r="G380" t="n">
+        <v>13557.2</v>
+      </c>
+      <c r="H380" t="n">
+        <v>24350</v>
+      </c>
+      <c r="I380" t="n">
+        <v>3571.06</v>
+      </c>
+      <c r="J380" t="n">
+        <v>3160.23</v>
+      </c>
+      <c r="K380" t="n">
+        <v>114000</v>
+      </c>
+      <c r="L380" t="n">
+        <v>16718.73</v>
+      </c>
+      <c r="M380" t="n">
+        <v>14795.34</v>
+      </c>
+      <c r="N380" t="n">
+        <v>0.1471713663389651</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N380"/>
+  <dimension ref="A1:N381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10262,6 +10262,52 @@
         <v>0.1471713663389651</v>
       </c>
     </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-05-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>178000</v>
+      </c>
+      <c r="C381" t="n">
+        <v>26104.68</v>
+      </c>
+      <c r="D381" t="n">
+        <v>23101.49</v>
+      </c>
+      <c r="E381" t="n">
+        <v>104460</v>
+      </c>
+      <c r="F381" t="n">
+        <v>15319.64</v>
+      </c>
+      <c r="G381" t="n">
+        <v>13557.2</v>
+      </c>
+      <c r="H381" t="n">
+        <v>24350</v>
+      </c>
+      <c r="I381" t="n">
+        <v>3571.06</v>
+      </c>
+      <c r="J381" t="n">
+        <v>3160.23</v>
+      </c>
+      <c r="K381" t="n">
+        <v>114000</v>
+      </c>
+      <c r="L381" t="n">
+        <v>16718.73</v>
+      </c>
+      <c r="M381" t="n">
+        <v>14795.34</v>
+      </c>
+      <c r="N381" t="n">
+        <v>0.1471713663389651</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N381"/>
+  <dimension ref="A1:N382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10308,6 +10308,52 @@
         <v>0.1471713663389651</v>
       </c>
     </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-05-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>183250</v>
+      </c>
+      <c r="C382" t="n">
+        <v>26940.21</v>
+      </c>
+      <c r="D382" t="n">
+        <v>23840.89</v>
+      </c>
+      <c r="E382" t="n">
+        <v>105490</v>
+      </c>
+      <c r="F382" t="n">
+        <v>15508.45</v>
+      </c>
+      <c r="G382" t="n">
+        <v>13724.29</v>
+      </c>
+      <c r="H382" t="n">
+        <v>24310</v>
+      </c>
+      <c r="I382" t="n">
+        <v>3573.9</v>
+      </c>
+      <c r="J382" t="n">
+        <v>3162.74</v>
+      </c>
+      <c r="K382" t="n">
+        <v>115000</v>
+      </c>
+      <c r="L382" t="n">
+        <v>16906.54</v>
+      </c>
+      <c r="M382" t="n">
+        <v>14961.54</v>
+      </c>
+      <c r="N382" t="n">
+        <v>0.1471713663389651</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N382"/>
+  <dimension ref="A1:N383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10354,6 +10354,52 @@
         <v>0.1471713663389651</v>
       </c>
     </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-05-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>180000</v>
+      </c>
+      <c r="C383" t="n">
+        <v>26460.47</v>
+      </c>
+      <c r="D383" t="n">
+        <v>23416.35</v>
+      </c>
+      <c r="E383" t="n">
+        <v>104740</v>
+      </c>
+      <c r="F383" t="n">
+        <v>15397.05</v>
+      </c>
+      <c r="G383" t="n">
+        <v>13625.71</v>
+      </c>
+      <c r="H383" t="n">
+        <v>24080</v>
+      </c>
+      <c r="I383" t="n">
+        <v>3539.82</v>
+      </c>
+      <c r="J383" t="n">
+        <v>3132.59</v>
+      </c>
+      <c r="K383" t="n">
+        <v>116000</v>
+      </c>
+      <c r="L383" t="n">
+        <v>17052.3</v>
+      </c>
+      <c r="M383" t="n">
+        <v>15090.53</v>
+      </c>
+      <c r="N383" t="n">
+        <v>0.1471713663389651</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N383"/>
+  <dimension ref="A1:N384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10400,6 +10400,52 @@
         <v>0.1471713663389651</v>
       </c>
     </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-05-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>177000</v>
+      </c>
+      <c r="C384" t="n">
+        <v>26024.05</v>
+      </c>
+      <c r="D384" t="n">
+        <v>23030.14</v>
+      </c>
+      <c r="E384" t="n">
+        <v>104955</v>
+      </c>
+      <c r="F384" t="n">
+        <v>15431.38</v>
+      </c>
+      <c r="G384" t="n">
+        <v>13656.09</v>
+      </c>
+      <c r="H384" t="n">
+        <v>24390</v>
+      </c>
+      <c r="I384" t="n">
+        <v>3586.03</v>
+      </c>
+      <c r="J384" t="n">
+        <v>3173.47</v>
+      </c>
+      <c r="K384" t="n">
+        <v>116000</v>
+      </c>
+      <c r="L384" t="n">
+        <v>17055.31</v>
+      </c>
+      <c r="M384" t="n">
+        <v>15093.2</v>
+      </c>
+      <c r="N384" t="n">
+        <v>0.1473513593162897</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N384"/>
+  <dimension ref="A1:N385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10446,6 +10446,52 @@
         <v>0.1473513593162897</v>
       </c>
     </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-05-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>175500</v>
+      </c>
+      <c r="C385" t="n">
+        <v>25811.1</v>
+      </c>
+      <c r="D385" t="n">
+        <v>22841.68</v>
+      </c>
+      <c r="E385" t="n">
+        <v>103580</v>
+      </c>
+      <c r="F385" t="n">
+        <v>15233.7</v>
+      </c>
+      <c r="G385" t="n">
+        <v>13481.15</v>
+      </c>
+      <c r="H385" t="n">
+        <v>24140</v>
+      </c>
+      <c r="I385" t="n">
+        <v>3550.31</v>
+      </c>
+      <c r="J385" t="n">
+        <v>3141.87</v>
+      </c>
+      <c r="K385" t="n">
+        <v>117500</v>
+      </c>
+      <c r="L385" t="n">
+        <v>17280.94</v>
+      </c>
+      <c r="M385" t="n">
+        <v>15292.86</v>
+      </c>
+      <c r="N385" t="n">
+        <v>0.1475143826523086</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N385"/>
+  <dimension ref="A1:N386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10492,6 +10492,52 @@
         <v>0.1475143826523086</v>
       </c>
     </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-05-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>177500</v>
+      </c>
+      <c r="C386" t="n">
+        <v>26119.07</v>
+      </c>
+      <c r="D386" t="n">
+        <v>23114.22</v>
+      </c>
+      <c r="E386" t="n">
+        <v>104785</v>
+      </c>
+      <c r="F386" t="n">
+        <v>15419.08</v>
+      </c>
+      <c r="G386" t="n">
+        <v>13645.21</v>
+      </c>
+      <c r="H386" t="n">
+        <v>24210</v>
+      </c>
+      <c r="I386" t="n">
+        <v>3562.49</v>
+      </c>
+      <c r="J386" t="n">
+        <v>3152.65</v>
+      </c>
+      <c r="K386" t="n">
+        <v>117500</v>
+      </c>
+      <c r="L386" t="n">
+        <v>17290.09</v>
+      </c>
+      <c r="M386" t="n">
+        <v>15300.97</v>
+      </c>
+      <c r="N386" t="n">
+        <v>0.1474991518798767</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N386"/>
+  <dimension ref="A1:N387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10538,6 +10538,50 @@
         <v>0.1474991518798767</v>
       </c>
     </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-05-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>177500</v>
+      </c>
+      <c r="C387" t="n">
+        <v>26119.07</v>
+      </c>
+      <c r="D387" t="n">
+        <v>23114.22</v>
+      </c>
+      <c r="E387" t="n">
+        <v>104785</v>
+      </c>
+      <c r="F387" t="n">
+        <v>15419.08</v>
+      </c>
+      <c r="G387" t="n">
+        <v>13645.21</v>
+      </c>
+      <c r="H387" t="n">
+        <v>24210</v>
+      </c>
+      <c r="I387" t="n">
+        <v>3562.49</v>
+      </c>
+      <c r="J387" t="n">
+        <v>3152.65</v>
+      </c>
+      <c r="K387" t="n">
+        <v>117500</v>
+      </c>
+      <c r="L387" t="n">
+        <v>17290.09</v>
+      </c>
+      <c r="M387" t="n">
+        <v>15300.97</v>
+      </c>
+      <c r="N387" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N387"/>
+  <dimension ref="A1:N388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10582,6 +10582,52 @@
       </c>
       <c r="N387" t="inlineStr"/>
     </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-05-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>177500</v>
+      </c>
+      <c r="C388" t="n">
+        <v>26119.07</v>
+      </c>
+      <c r="D388" t="n">
+        <v>23114.22</v>
+      </c>
+      <c r="E388" t="n">
+        <v>104785</v>
+      </c>
+      <c r="F388" t="n">
+        <v>15419.08</v>
+      </c>
+      <c r="G388" t="n">
+        <v>13645.21</v>
+      </c>
+      <c r="H388" t="n">
+        <v>24210</v>
+      </c>
+      <c r="I388" t="n">
+        <v>3562.49</v>
+      </c>
+      <c r="J388" t="n">
+        <v>3152.65</v>
+      </c>
+      <c r="K388" t="n">
+        <v>117500</v>
+      </c>
+      <c r="L388" t="n">
+        <v>17290.09</v>
+      </c>
+      <c r="M388" t="n">
+        <v>15300.97</v>
+      </c>
+      <c r="N388" t="n">
+        <v>0.1477890754315441</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N388"/>
+  <dimension ref="A1:N389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10628,6 +10628,52 @@
         <v>0.1477890754315441</v>
       </c>
     </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>179000</v>
+      </c>
+      <c r="C389" t="n">
+        <v>26380.56</v>
+      </c>
+      <c r="D389" t="n">
+        <v>23345.63</v>
+      </c>
+      <c r="E389" t="n">
+        <v>104775</v>
+      </c>
+      <c r="F389" t="n">
+        <v>15441.47</v>
+      </c>
+      <c r="G389" t="n">
+        <v>13665.02</v>
+      </c>
+      <c r="H389" t="n">
+        <v>24190</v>
+      </c>
+      <c r="I389" t="n">
+        <v>3565.06</v>
+      </c>
+      <c r="J389" t="n">
+        <v>3154.92</v>
+      </c>
+      <c r="K389" t="n">
+        <v>117500</v>
+      </c>
+      <c r="L389" t="n">
+        <v>17316.85</v>
+      </c>
+      <c r="M389" t="n">
+        <v>15324.64</v>
+      </c>
+      <c r="N389" t="n">
+        <v>0.1477890754315441</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N389"/>
+  <dimension ref="A1:N390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10674,6 +10674,52 @@
         <v>0.1477890754315441</v>
       </c>
     </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-06-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>175750</v>
+      </c>
+      <c r="C390" t="n">
+        <v>25897.38</v>
+      </c>
+      <c r="D390" t="n">
+        <v>22918.04</v>
+      </c>
+      <c r="E390" t="n">
+        <v>105795</v>
+      </c>
+      <c r="F390" t="n">
+        <v>15589.27</v>
+      </c>
+      <c r="G390" t="n">
+        <v>13795.81</v>
+      </c>
+      <c r="H390" t="n">
+        <v>24330</v>
+      </c>
+      <c r="I390" t="n">
+        <v>3585.11</v>
+      </c>
+      <c r="J390" t="n">
+        <v>3172.66</v>
+      </c>
+      <c r="K390" t="n">
+        <v>117500</v>
+      </c>
+      <c r="L390" t="n">
+        <v>17314.04</v>
+      </c>
+      <c r="M390" t="n">
+        <v>15322.16</v>
+      </c>
+      <c r="N390" t="n">
+        <v>0.147815290013599</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N390"/>
+  <dimension ref="A1:N391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10720,6 +10720,52 @@
         <v>0.147815290013599</v>
       </c>
     </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-06-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>170500</v>
+      </c>
+      <c r="C391" t="n">
+        <v>25134.89</v>
+      </c>
+      <c r="D391" t="n">
+        <v>22243.26</v>
+      </c>
+      <c r="E391" t="n">
+        <v>106645</v>
+      </c>
+      <c r="F391" t="n">
+        <v>15721.47</v>
+      </c>
+      <c r="G391" t="n">
+        <v>13912.8</v>
+      </c>
+      <c r="H391" t="n">
+        <v>24460</v>
+      </c>
+      <c r="I391" t="n">
+        <v>3605.86</v>
+      </c>
+      <c r="J391" t="n">
+        <v>3191.03</v>
+      </c>
+      <c r="K391" t="n">
+        <v>117500</v>
+      </c>
+      <c r="L391" t="n">
+        <v>17321.7</v>
+      </c>
+      <c r="M391" t="n">
+        <v>15328.94</v>
+      </c>
+      <c r="N391" t="n">
+        <v>0.1478721201904593</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N391"/>
+  <dimension ref="A1:N392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10766,6 +10766,52 @@
         <v>0.1478721201904593</v>
       </c>
     </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-06-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>168250</v>
+      </c>
+      <c r="C392" t="n">
+        <v>24767.41</v>
+      </c>
+      <c r="D392" t="n">
+        <v>21918.07</v>
+      </c>
+      <c r="E392" t="n">
+        <v>105210</v>
+      </c>
+      <c r="F392" t="n">
+        <v>15487.55</v>
+      </c>
+      <c r="G392" t="n">
+        <v>13705.79</v>
+      </c>
+      <c r="H392" t="n">
+        <v>24210</v>
+      </c>
+      <c r="I392" t="n">
+        <v>3563.86</v>
+      </c>
+      <c r="J392" t="n">
+        <v>3153.86</v>
+      </c>
+      <c r="K392" t="n">
+        <v>116500</v>
+      </c>
+      <c r="L392" t="n">
+        <v>17149.5</v>
+      </c>
+      <c r="M392" t="n">
+        <v>15176.55</v>
+      </c>
+      <c r="N392" t="n">
+        <v>0.1477235796377818</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N392"/>
+  <dimension ref="A1:N393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10812,6 +10812,52 @@
         <v>0.1477235796377818</v>
       </c>
     </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-06-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>163000</v>
+      </c>
+      <c r="C393" t="n">
+        <v>23989.29</v>
+      </c>
+      <c r="D393" t="n">
+        <v>21229.46</v>
+      </c>
+      <c r="E393" t="n">
+        <v>105265</v>
+      </c>
+      <c r="F393" t="n">
+        <v>15492.22</v>
+      </c>
+      <c r="G393" t="n">
+        <v>13709.93</v>
+      </c>
+      <c r="H393" t="n">
+        <v>24200</v>
+      </c>
+      <c r="I393" t="n">
+        <v>3561.6</v>
+      </c>
+      <c r="J393" t="n">
+        <v>3151.86</v>
+      </c>
+      <c r="K393" t="n">
+        <v>115500</v>
+      </c>
+      <c r="L393" t="n">
+        <v>16998.54</v>
+      </c>
+      <c r="M393" t="n">
+        <v>15042.96</v>
+      </c>
+      <c r="N393" t="n">
+        <v>0.1476254447216522</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N393"/>
+  <dimension ref="A1:N394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10858,6 +10858,52 @@
         <v>0.1476254447216522</v>
       </c>
     </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-06-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>163000</v>
+      </c>
+      <c r="C394" t="n">
+        <v>23989.29</v>
+      </c>
+      <c r="D394" t="n">
+        <v>21229.46</v>
+      </c>
+      <c r="E394" t="n">
+        <v>105265</v>
+      </c>
+      <c r="F394" t="n">
+        <v>15492.22</v>
+      </c>
+      <c r="G394" t="n">
+        <v>13709.93</v>
+      </c>
+      <c r="H394" t="n">
+        <v>24200</v>
+      </c>
+      <c r="I394" t="n">
+        <v>3561.6</v>
+      </c>
+      <c r="J394" t="n">
+        <v>3151.86</v>
+      </c>
+      <c r="K394" t="n">
+        <v>115500</v>
+      </c>
+      <c r="L394" t="n">
+        <v>16998.54</v>
+      </c>
+      <c r="M394" t="n">
+        <v>15042.96</v>
+      </c>
+      <c r="N394" t="n">
+        <v>0.1478065507863308</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N394"/>
+  <dimension ref="A1:N395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10904,6 +10904,52 @@
         <v>0.1478065507863308</v>
       </c>
     </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-06-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>163000</v>
+      </c>
+      <c r="C395" t="n">
+        <v>23989.29</v>
+      </c>
+      <c r="D395" t="n">
+        <v>21229.46</v>
+      </c>
+      <c r="E395" t="n">
+        <v>105265</v>
+      </c>
+      <c r="F395" t="n">
+        <v>15492.22</v>
+      </c>
+      <c r="G395" t="n">
+        <v>13709.93</v>
+      </c>
+      <c r="H395" t="n">
+        <v>24200</v>
+      </c>
+      <c r="I395" t="n">
+        <v>3561.6</v>
+      </c>
+      <c r="J395" t="n">
+        <v>3151.86</v>
+      </c>
+      <c r="K395" t="n">
+        <v>115500</v>
+      </c>
+      <c r="L395" t="n">
+        <v>16998.54</v>
+      </c>
+      <c r="M395" t="n">
+        <v>15042.96</v>
+      </c>
+      <c r="N395" t="n">
+        <v>0.1478065507863308</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N395"/>
+  <dimension ref="A1:N396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10950,6 +10950,52 @@
         <v>0.1478065507863308</v>
       </c>
     </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-06-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>163750</v>
+      </c>
+      <c r="C396" t="n">
+        <v>24077.34</v>
+      </c>
+      <c r="D396" t="n">
+        <v>21307.38</v>
+      </c>
+      <c r="E396" t="n">
+        <v>104100</v>
+      </c>
+      <c r="F396" t="n">
+        <v>15306.57</v>
+      </c>
+      <c r="G396" t="n">
+        <v>13545.64</v>
+      </c>
+      <c r="H396" t="n">
+        <v>24000</v>
+      </c>
+      <c r="I396" t="n">
+        <v>3528.89</v>
+      </c>
+      <c r="J396" t="n">
+        <v>3122.91</v>
+      </c>
+      <c r="K396" t="n">
+        <v>115500</v>
+      </c>
+      <c r="L396" t="n">
+        <v>16982.8</v>
+      </c>
+      <c r="M396" t="n">
+        <v>15029.02</v>
+      </c>
+      <c r="N396" t="n">
+        <v>0.1478065507863308</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N396"/>
+  <dimension ref="A1:N397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10996,6 +10996,52 @@
         <v>0.1478065507863308</v>
       </c>
     </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-06-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>163750</v>
+      </c>
+      <c r="C397" t="n">
+        <v>24070.97</v>
+      </c>
+      <c r="D397" t="n">
+        <v>21301.74</v>
+      </c>
+      <c r="E397" t="n">
+        <v>104170</v>
+      </c>
+      <c r="F397" t="n">
+        <v>15312.81</v>
+      </c>
+      <c r="G397" t="n">
+        <v>13551.16</v>
+      </c>
+      <c r="H397" t="n">
+        <v>23900</v>
+      </c>
+      <c r="I397" t="n">
+        <v>3513.26</v>
+      </c>
+      <c r="J397" t="n">
+        <v>3109.08</v>
+      </c>
+      <c r="K397" t="n">
+        <v>114000</v>
+      </c>
+      <c r="L397" t="n">
+        <v>16757.81</v>
+      </c>
+      <c r="M397" t="n">
+        <v>14829.92</v>
+      </c>
+      <c r="N397" t="n">
+        <v>0.147412179194245</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N397"/>
+  <dimension ref="A1:N398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11042,6 +11042,52 @@
         <v>0.147412179194245</v>
       </c>
     </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-06-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>157500</v>
+      </c>
+      <c r="C398" t="n">
+        <v>23145.43</v>
+      </c>
+      <c r="D398" t="n">
+        <v>20482.68</v>
+      </c>
+      <c r="E398" t="n">
+        <v>103160</v>
+      </c>
+      <c r="F398" t="n">
+        <v>15159.89</v>
+      </c>
+      <c r="G398" t="n">
+        <v>13415.83</v>
+      </c>
+      <c r="H398" t="n">
+        <v>23470</v>
+      </c>
+      <c r="I398" t="n">
+        <v>3449.04</v>
+      </c>
+      <c r="J398" t="n">
+        <v>3052.24</v>
+      </c>
+      <c r="K398" t="n">
+        <v>108000</v>
+      </c>
+      <c r="L398" t="n">
+        <v>15871.15</v>
+      </c>
+      <c r="M398" t="n">
+        <v>14045.27</v>
+      </c>
+      <c r="N398" t="n">
+        <v>0.1472645607834475</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N398"/>
+  <dimension ref="A1:N399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11088,6 +11088,52 @@
         <v>0.1472645607834475</v>
       </c>
     </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>157000</v>
+      </c>
+      <c r="C399" t="n">
+        <v>23005.01</v>
+      </c>
+      <c r="D399" t="n">
+        <v>20358.42</v>
+      </c>
+      <c r="E399" t="n">
+        <v>101085</v>
+      </c>
+      <c r="F399" t="n">
+        <v>14811.86</v>
+      </c>
+      <c r="G399" t="n">
+        <v>13107.84</v>
+      </c>
+      <c r="H399" t="n">
+        <v>22850</v>
+      </c>
+      <c r="I399" t="n">
+        <v>3348.18</v>
+      </c>
+      <c r="J399" t="n">
+        <v>2962.99</v>
+      </c>
+      <c r="K399" t="n">
+        <v>107500</v>
+      </c>
+      <c r="L399" t="n">
+        <v>15751.84</v>
+      </c>
+      <c r="M399" t="n">
+        <v>13939.68</v>
+      </c>
+      <c r="N399" t="n">
+        <v>0.1472645607834475</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N399"/>
+  <dimension ref="A1:N400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11134,6 +11134,52 @@
         <v>0.1472645607834475</v>
       </c>
     </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-06-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>152500</v>
+      </c>
+      <c r="C400" t="n">
+        <v>22376.78</v>
+      </c>
+      <c r="D400" t="n">
+        <v>19802.46</v>
+      </c>
+      <c r="E400" t="n">
+        <v>101570</v>
+      </c>
+      <c r="F400" t="n">
+        <v>14903.67</v>
+      </c>
+      <c r="G400" t="n">
+        <v>13189.09</v>
+      </c>
+      <c r="H400" t="n">
+        <v>22880</v>
+      </c>
+      <c r="I400" t="n">
+        <v>3357.25</v>
+      </c>
+      <c r="J400" t="n">
+        <v>2971.02</v>
+      </c>
+      <c r="K400" t="n">
+        <v>106500</v>
+      </c>
+      <c r="L400" t="n">
+        <v>15627.06</v>
+      </c>
+      <c r="M400" t="n">
+        <v>13829.26</v>
+      </c>
+      <c r="N400" t="n">
+        <v>0.1469745293140699</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N400"/>
+  <dimension ref="A1:N401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11180,6 +11180,52 @@
         <v>0.1469745293140699</v>
       </c>
     </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-06-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>152500</v>
+      </c>
+      <c r="C401" t="n">
+        <v>22376.78</v>
+      </c>
+      <c r="D401" t="n">
+        <v>19802.46</v>
+      </c>
+      <c r="E401" t="n">
+        <v>101570</v>
+      </c>
+      <c r="F401" t="n">
+        <v>14903.67</v>
+      </c>
+      <c r="G401" t="n">
+        <v>13189.09</v>
+      </c>
+      <c r="H401" t="n">
+        <v>22880</v>
+      </c>
+      <c r="I401" t="n">
+        <v>3357.25</v>
+      </c>
+      <c r="J401" t="n">
+        <v>2971.02</v>
+      </c>
+      <c r="K401" t="n">
+        <v>106500</v>
+      </c>
+      <c r="L401" t="n">
+        <v>15627.06</v>
+      </c>
+      <c r="M401" t="n">
+        <v>13829.26</v>
+      </c>
+      <c r="N401" t="n">
+        <v>0.147097761172075</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N401"/>
+  <dimension ref="A1:N402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11226,6 +11226,52 @@
         <v>0.147097761172075</v>
       </c>
     </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-06-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>152500</v>
+      </c>
+      <c r="C402" t="n">
+        <v>22376.78</v>
+      </c>
+      <c r="D402" t="n">
+        <v>19802.46</v>
+      </c>
+      <c r="E402" t="n">
+        <v>101570</v>
+      </c>
+      <c r="F402" t="n">
+        <v>14903.67</v>
+      </c>
+      <c r="G402" t="n">
+        <v>13189.09</v>
+      </c>
+      <c r="H402" t="n">
+        <v>22880</v>
+      </c>
+      <c r="I402" t="n">
+        <v>3357.25</v>
+      </c>
+      <c r="J402" t="n">
+        <v>2971.02</v>
+      </c>
+      <c r="K402" t="n">
+        <v>106500</v>
+      </c>
+      <c r="L402" t="n">
+        <v>15627.06</v>
+      </c>
+      <c r="M402" t="n">
+        <v>13829.26</v>
+      </c>
+      <c r="N402" t="n">
+        <v>0.147097761172075</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N402"/>
+  <dimension ref="A1:N403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11272,6 +11272,52 @@
         <v>0.147097761172075</v>
       </c>
     </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-06-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>151750</v>
+      </c>
+      <c r="C403" t="n">
+        <v>22256.61</v>
+      </c>
+      <c r="D403" t="n">
+        <v>19696.11</v>
+      </c>
+      <c r="E403" t="n">
+        <v>102450</v>
+      </c>
+      <c r="F403" t="n">
+        <v>15025.96</v>
+      </c>
+      <c r="G403" t="n">
+        <v>13297.31</v>
+      </c>
+      <c r="H403" t="n">
+        <v>22940</v>
+      </c>
+      <c r="I403" t="n">
+        <v>3364.52</v>
+      </c>
+      <c r="J403" t="n">
+        <v>2977.45</v>
+      </c>
+      <c r="K403" t="n">
+        <v>106500</v>
+      </c>
+      <c r="L403" t="n">
+        <v>15619.96</v>
+      </c>
+      <c r="M403" t="n">
+        <v>13822.97</v>
+      </c>
+      <c r="N403" t="n">
+        <v>0.147097761172075</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N403"/>
+  <dimension ref="A1:N404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11318,6 +11318,52 @@
         <v>0.147097761172075</v>
       </c>
     </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-06-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>156500</v>
+      </c>
+      <c r="C404" t="n">
+        <v>22967.42</v>
+      </c>
+      <c r="D404" t="n">
+        <v>20325.15</v>
+      </c>
+      <c r="E404" t="n">
+        <v>102200</v>
+      </c>
+      <c r="F404" t="n">
+        <v>14998.53</v>
+      </c>
+      <c r="G404" t="n">
+        <v>13273.04</v>
+      </c>
+      <c r="H404" t="n">
+        <v>22500</v>
+      </c>
+      <c r="I404" t="n">
+        <v>3302.03</v>
+      </c>
+      <c r="J404" t="n">
+        <v>2922.15</v>
+      </c>
+      <c r="K404" t="n">
+        <v>103500</v>
+      </c>
+      <c r="L404" t="n">
+        <v>15189.32</v>
+      </c>
+      <c r="M404" t="n">
+        <v>13441.87</v>
+      </c>
+      <c r="N404" t="n">
+        <v>0.1471886959081543</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N404"/>
+  <dimension ref="A1:N405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11364,6 +11364,52 @@
         <v>0.1471886959081543</v>
       </c>
     </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>160000</v>
+      </c>
+      <c r="C405" t="n">
+        <v>23517.31</v>
+      </c>
+      <c r="D405" t="n">
+        <v>20811.78</v>
+      </c>
+      <c r="E405" t="n">
+        <v>102080</v>
+      </c>
+      <c r="F405" t="n">
+        <v>15004.04</v>
+      </c>
+      <c r="G405" t="n">
+        <v>13277.91</v>
+      </c>
+      <c r="H405" t="n">
+        <v>22260</v>
+      </c>
+      <c r="I405" t="n">
+        <v>3271.85</v>
+      </c>
+      <c r="J405" t="n">
+        <v>2895.44</v>
+      </c>
+      <c r="K405" t="n">
+        <v>103500</v>
+      </c>
+      <c r="L405" t="n">
+        <v>15212.76</v>
+      </c>
+      <c r="M405" t="n">
+        <v>13462.62</v>
+      </c>
+      <c r="N405" t="n">
+        <v>0.1471908623912628</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N405"/>
+  <dimension ref="A1:N406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11410,6 +11410,50 @@
         <v>0.1471908623912628</v>
       </c>
     </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>162500</v>
+      </c>
+      <c r="C406" t="n">
+        <v>23872.83</v>
+      </c>
+      <c r="D406" t="n">
+        <v>21126.4</v>
+      </c>
+      <c r="E406" t="n">
+        <v>102400</v>
+      </c>
+      <c r="F406" t="n">
+        <v>15043.56</v>
+      </c>
+      <c r="G406" t="n">
+        <v>13312.88</v>
+      </c>
+      <c r="H406" t="n">
+        <v>22540</v>
+      </c>
+      <c r="I406" t="n">
+        <v>3311.35</v>
+      </c>
+      <c r="J406" t="n">
+        <v>2930.39</v>
+      </c>
+      <c r="K406" t="n">
+        <v>102500</v>
+      </c>
+      <c r="L406" t="n">
+        <v>15058.25</v>
+      </c>
+      <c r="M406" t="n">
+        <v>13325.88</v>
+      </c>
+      <c r="N406" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N406"/>
+  <dimension ref="A1:N407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11454,6 +11454,52 @@
       </c>
       <c r="N406" t="inlineStr"/>
     </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>165250</v>
+      </c>
+      <c r="C407" t="n">
+        <v>24294.33</v>
+      </c>
+      <c r="D407" t="n">
+        <v>21499.4</v>
+      </c>
+      <c r="E407" t="n">
+        <v>103075</v>
+      </c>
+      <c r="F407" t="n">
+        <v>15153.63</v>
+      </c>
+      <c r="G407" t="n">
+        <v>13410.29</v>
+      </c>
+      <c r="H407" t="n">
+        <v>22760</v>
+      </c>
+      <c r="I407" t="n">
+        <v>3346.07</v>
+      </c>
+      <c r="J407" t="n">
+        <v>2961.13</v>
+      </c>
+      <c r="K407" t="n">
+        <v>102500</v>
+      </c>
+      <c r="L407" t="n">
+        <v>15069.1</v>
+      </c>
+      <c r="M407" t="n">
+        <v>13335.48</v>
+      </c>
+      <c r="N407" t="n">
+        <v>0.1472949286356071</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N407"/>
+  <dimension ref="A1:N408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11500,6 +11500,52 @@
         <v>0.1472949286356071</v>
       </c>
     </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-07-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>165250</v>
+      </c>
+      <c r="C408" t="n">
+        <v>24294.33</v>
+      </c>
+      <c r="D408" t="n">
+        <v>21499.4</v>
+      </c>
+      <c r="E408" t="n">
+        <v>103075</v>
+      </c>
+      <c r="F408" t="n">
+        <v>15153.63</v>
+      </c>
+      <c r="G408" t="n">
+        <v>13410.29</v>
+      </c>
+      <c r="H408" t="n">
+        <v>22760</v>
+      </c>
+      <c r="I408" t="n">
+        <v>3346.07</v>
+      </c>
+      <c r="J408" t="n">
+        <v>2961.13</v>
+      </c>
+      <c r="K408" t="n">
+        <v>102500</v>
+      </c>
+      <c r="L408" t="n">
+        <v>15069.1</v>
+      </c>
+      <c r="M408" t="n">
+        <v>13335.48</v>
+      </c>
+      <c r="N408" t="n">
+        <v>0.1472949286356071</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N408"/>
+  <dimension ref="A1:N409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11546,6 +11546,52 @@
         <v>0.1472949286356071</v>
       </c>
     </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-07-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>165250</v>
+      </c>
+      <c r="C409" t="n">
+        <v>24294.33</v>
+      </c>
+      <c r="D409" t="n">
+        <v>21499.4</v>
+      </c>
+      <c r="E409" t="n">
+        <v>103075</v>
+      </c>
+      <c r="F409" t="n">
+        <v>15153.63</v>
+      </c>
+      <c r="G409" t="n">
+        <v>13410.29</v>
+      </c>
+      <c r="H409" t="n">
+        <v>22760</v>
+      </c>
+      <c r="I409" t="n">
+        <v>3346.07</v>
+      </c>
+      <c r="J409" t="n">
+        <v>2961.13</v>
+      </c>
+      <c r="K409" t="n">
+        <v>102500</v>
+      </c>
+      <c r="L409" t="n">
+        <v>15069.1</v>
+      </c>
+      <c r="M409" t="n">
+        <v>13335.48</v>
+      </c>
+      <c r="N409" t="n">
+        <v>0.1472949286356071</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N409"/>
+  <dimension ref="A1:N410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11592,6 +11592,52 @@
         <v>0.1472949286356071</v>
       </c>
     </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>165250</v>
+      </c>
+      <c r="C410" t="n">
+        <v>24306.12</v>
+      </c>
+      <c r="D410" t="n">
+        <v>21509.84</v>
+      </c>
+      <c r="E410" t="n">
+        <v>103250</v>
+      </c>
+      <c r="F410" t="n">
+        <v>15186.73</v>
+      </c>
+      <c r="G410" t="n">
+        <v>13439.58</v>
+      </c>
+      <c r="H410" t="n">
+        <v>22840</v>
+      </c>
+      <c r="I410" t="n">
+        <v>3359.47</v>
+      </c>
+      <c r="J410" t="n">
+        <v>2972.98</v>
+      </c>
+      <c r="K410" t="n">
+        <v>102500</v>
+      </c>
+      <c r="L410" t="n">
+        <v>15076.41</v>
+      </c>
+      <c r="M410" t="n">
+        <v>13341.96</v>
+      </c>
+      <c r="N410" t="n">
+        <v>0.1472949286356071</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N410"/>
+  <dimension ref="A1:N411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11638,6 +11638,52 @@
         <v>0.1472949286356071</v>
       </c>
     </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>164500</v>
+      </c>
+      <c r="C411" t="n">
+        <v>24148.56</v>
+      </c>
+      <c r="D411" t="n">
+        <v>21370.41</v>
+      </c>
+      <c r="E411" t="n">
+        <v>103205</v>
+      </c>
+      <c r="F411" t="n">
+        <v>15150.47</v>
+      </c>
+      <c r="G411" t="n">
+        <v>13407.5</v>
+      </c>
+      <c r="H411" t="n">
+        <v>22940</v>
+      </c>
+      <c r="I411" t="n">
+        <v>3367.59</v>
+      </c>
+      <c r="J411" t="n">
+        <v>2980.16</v>
+      </c>
+      <c r="K411" t="n">
+        <v>100500</v>
+      </c>
+      <c r="L411" t="n">
+        <v>14753.38</v>
+      </c>
+      <c r="M411" t="n">
+        <v>13056.08</v>
+      </c>
+      <c r="N411" t="n">
+        <v>0.1471367194397034</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N411"/>
+  <dimension ref="A1:N412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11684,6 +11684,52 @@
         <v>0.1471367194397034</v>
       </c>
     </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>164000</v>
+      </c>
+      <c r="C412" t="n">
+        <v>24075.16</v>
+      </c>
+      <c r="D412" t="n">
+        <v>21305.45</v>
+      </c>
+      <c r="E412" t="n">
+        <v>102995</v>
+      </c>
+      <c r="F412" t="n">
+        <v>15119.64</v>
+      </c>
+      <c r="G412" t="n">
+        <v>13380.21</v>
+      </c>
+      <c r="H412" t="n">
+        <v>23040</v>
+      </c>
+      <c r="I412" t="n">
+        <v>3382.27</v>
+      </c>
+      <c r="J412" t="n">
+        <v>2993.16</v>
+      </c>
+      <c r="K412" t="n">
+        <v>98500</v>
+      </c>
+      <c r="L412" t="n">
+        <v>14459.78</v>
+      </c>
+      <c r="M412" t="n">
+        <v>12796.26</v>
+      </c>
+      <c r="N412" t="n">
+        <v>0.1471843631332607</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N412"/>
+  <dimension ref="A1:N413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11730,6 +11730,52 @@
         <v>0.1471843631332607</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-07-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>158500</v>
+      </c>
+      <c r="C413" t="n">
+        <v>23236.38</v>
+      </c>
+      <c r="D413" t="n">
+        <v>20563.17</v>
+      </c>
+      <c r="E413" t="n">
+        <v>102560</v>
+      </c>
+      <c r="F413" t="n">
+        <v>15035.48</v>
+      </c>
+      <c r="G413" t="n">
+        <v>13305.73</v>
+      </c>
+      <c r="H413" t="n">
+        <v>22950</v>
+      </c>
+      <c r="I413" t="n">
+        <v>3364.51</v>
+      </c>
+      <c r="J413" t="n">
+        <v>2977.44</v>
+      </c>
+      <c r="K413" t="n">
+        <v>96500</v>
+      </c>
+      <c r="L413" t="n">
+        <v>14147.07</v>
+      </c>
+      <c r="M413" t="n">
+        <v>12519.53</v>
+      </c>
+      <c r="N413" t="n">
+        <v>0.1469896519285042</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N413"/>
+  <dimension ref="A1:N414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11776,6 +11776,50 @@
         <v>0.1469896519285042</v>
       </c>
     </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-07-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>155000</v>
+      </c>
+      <c r="C414" t="n">
+        <v>22761.65</v>
+      </c>
+      <c r="D414" t="n">
+        <v>20143.05</v>
+      </c>
+      <c r="E414" t="n">
+        <v>104170</v>
+      </c>
+      <c r="F414" t="n">
+        <v>15297.3</v>
+      </c>
+      <c r="G414" t="n">
+        <v>13537.43</v>
+      </c>
+      <c r="H414" t="n">
+        <v>23120</v>
+      </c>
+      <c r="I414" t="n">
+        <v>3395.16</v>
+      </c>
+      <c r="J414" t="n">
+        <v>3004.56</v>
+      </c>
+      <c r="K414" t="n">
+        <v>96500</v>
+      </c>
+      <c r="L414" t="n">
+        <v>14170.96</v>
+      </c>
+      <c r="M414" t="n">
+        <v>12540.67</v>
+      </c>
+      <c r="N414" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N414"/>
+  <dimension ref="A1:N415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11820,6 +11820,52 @@
       </c>
       <c r="N414" t="inlineStr"/>
     </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-07-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>146500</v>
+      </c>
+      <c r="C415" t="n">
+        <v>21578.71</v>
+      </c>
+      <c r="D415" t="n">
+        <v>19096.2</v>
+      </c>
+      <c r="E415" t="n">
+        <v>106495</v>
+      </c>
+      <c r="F415" t="n">
+        <v>15686.17</v>
+      </c>
+      <c r="G415" t="n">
+        <v>13881.57</v>
+      </c>
+      <c r="H415" t="n">
+        <v>23260</v>
+      </c>
+      <c r="I415" t="n">
+        <v>3426.08</v>
+      </c>
+      <c r="J415" t="n">
+        <v>3031.93</v>
+      </c>
+      <c r="K415" t="n">
+        <v>102500</v>
+      </c>
+      <c r="L415" t="n">
+        <v>15097.73</v>
+      </c>
+      <c r="M415" t="n">
+        <v>13360.82</v>
+      </c>
+      <c r="N415" t="n">
+        <v>0.1476450612727004</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N415"/>
+  <dimension ref="A1:N416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11866,6 +11866,52 @@
         <v>0.1476450612727004</v>
       </c>
     </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-07-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>145500</v>
+      </c>
+      <c r="C416" t="n">
+        <v>21414.69</v>
+      </c>
+      <c r="D416" t="n">
+        <v>18951.06</v>
+      </c>
+      <c r="E416" t="n">
+        <v>105200</v>
+      </c>
+      <c r="F416" t="n">
+        <v>15483.34</v>
+      </c>
+      <c r="G416" t="n">
+        <v>13702.07</v>
+      </c>
+      <c r="H416" t="n">
+        <v>23200</v>
+      </c>
+      <c r="I416" t="n">
+        <v>3414.58</v>
+      </c>
+      <c r="J416" t="n">
+        <v>3021.75</v>
+      </c>
+      <c r="K416" t="n">
+        <v>103500</v>
+      </c>
+      <c r="L416" t="n">
+        <v>15233.13</v>
+      </c>
+      <c r="M416" t="n">
+        <v>13480.65</v>
+      </c>
+      <c r="N416" t="n">
+        <v>0.1477061238958967</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N416"/>
+  <dimension ref="A1:N417"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11912,6 +11912,52 @@
         <v>0.1477061238958967</v>
       </c>
     </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-07-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>145500</v>
+      </c>
+      <c r="C417" t="n">
+        <v>21414.69</v>
+      </c>
+      <c r="D417" t="n">
+        <v>18951.06</v>
+      </c>
+      <c r="E417" t="n">
+        <v>105200</v>
+      </c>
+      <c r="F417" t="n">
+        <v>15483.34</v>
+      </c>
+      <c r="G417" t="n">
+        <v>13702.07</v>
+      </c>
+      <c r="H417" t="n">
+        <v>23200</v>
+      </c>
+      <c r="I417" t="n">
+        <v>3414.58</v>
+      </c>
+      <c r="J417" t="n">
+        <v>3021.75</v>
+      </c>
+      <c r="K417" t="n">
+        <v>103500</v>
+      </c>
+      <c r="L417" t="n">
+        <v>15233.13</v>
+      </c>
+      <c r="M417" t="n">
+        <v>13480.65</v>
+      </c>
+      <c r="N417" t="n">
+        <v>0.1476646830377579</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N417"/>
+  <dimension ref="A1:N418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11958,6 +11958,52 @@
         <v>0.1476646830377579</v>
       </c>
     </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-07-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>145500</v>
+      </c>
+      <c r="C418" t="n">
+        <v>21414.69</v>
+      </c>
+      <c r="D418" t="n">
+        <v>18951.06</v>
+      </c>
+      <c r="E418" t="n">
+        <v>105200</v>
+      </c>
+      <c r="F418" t="n">
+        <v>15483.34</v>
+      </c>
+      <c r="G418" t="n">
+        <v>13702.07</v>
+      </c>
+      <c r="H418" t="n">
+        <v>23200</v>
+      </c>
+      <c r="I418" t="n">
+        <v>3414.58</v>
+      </c>
+      <c r="J418" t="n">
+        <v>3021.75</v>
+      </c>
+      <c r="K418" t="n">
+        <v>103500</v>
+      </c>
+      <c r="L418" t="n">
+        <v>15233.13</v>
+      </c>
+      <c r="M418" t="n">
+        <v>13480.65</v>
+      </c>
+      <c r="N418" t="n">
+        <v>0.1476646830377579</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N418"/>
+  <dimension ref="A1:N419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12004,6 +12004,52 @@
         <v>0.1476646830377579</v>
       </c>
     </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-07-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>146500</v>
+      </c>
+      <c r="C419" t="n">
+        <v>21583.16</v>
+      </c>
+      <c r="D419" t="n">
+        <v>19100.14</v>
+      </c>
+      <c r="E419" t="n">
+        <v>105575</v>
+      </c>
+      <c r="F419" t="n">
+        <v>15553.87</v>
+      </c>
+      <c r="G419" t="n">
+        <v>13764.49</v>
+      </c>
+      <c r="H419" t="n">
+        <v>23200</v>
+      </c>
+      <c r="I419" t="n">
+        <v>3417.95</v>
+      </c>
+      <c r="J419" t="n">
+        <v>3024.73</v>
+      </c>
+      <c r="K419" t="n">
+        <v>105000</v>
+      </c>
+      <c r="L419" t="n">
+        <v>15469.16</v>
+      </c>
+      <c r="M419" t="n">
+        <v>13689.52</v>
+      </c>
+      <c r="N419" t="n">
+        <v>0.1476646830377579</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N419"/>
+  <dimension ref="A1:N420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12050,6 +12050,52 @@
         <v>0.1476646830377579</v>
       </c>
     </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-07-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>145500</v>
+      </c>
+      <c r="C420" t="n">
+        <v>21457.33</v>
+      </c>
+      <c r="D420" t="n">
+        <v>18988.79</v>
+      </c>
+      <c r="E420" t="n">
+        <v>105240</v>
+      </c>
+      <c r="F420" t="n">
+        <v>15520.06</v>
+      </c>
+      <c r="G420" t="n">
+        <v>13734.57</v>
+      </c>
+      <c r="H420" t="n">
+        <v>23200</v>
+      </c>
+      <c r="I420" t="n">
+        <v>3421.37</v>
+      </c>
+      <c r="J420" t="n">
+        <v>3027.76</v>
+      </c>
+      <c r="K420" t="n">
+        <v>107000</v>
+      </c>
+      <c r="L420" t="n">
+        <v>15779.62</v>
+      </c>
+      <c r="M420" t="n">
+        <v>13964.26</v>
+      </c>
+      <c r="N420" t="n">
+        <v>0.1477956282053177</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N420"/>
+  <dimension ref="A1:N421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12096,6 +12096,52 @@
         <v>0.1477956282053177</v>
       </c>
     </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-07-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>146000</v>
+      </c>
+      <c r="C421" t="n">
+        <v>21519.64</v>
+      </c>
+      <c r="D421" t="n">
+        <v>19043.93</v>
+      </c>
+      <c r="E421" t="n">
+        <v>105230</v>
+      </c>
+      <c r="F421" t="n">
+        <v>15510.35</v>
+      </c>
+      <c r="G421" t="n">
+        <v>13725.98</v>
+      </c>
+      <c r="H421" t="n">
+        <v>23400</v>
+      </c>
+      <c r="I421" t="n">
+        <v>3449.04</v>
+      </c>
+      <c r="J421" t="n">
+        <v>3052.25</v>
+      </c>
+      <c r="K421" t="n">
+        <v>107500</v>
+      </c>
+      <c r="L421" t="n">
+        <v>15844.94</v>
+      </c>
+      <c r="M421" t="n">
+        <v>14022.07</v>
+      </c>
+      <c r="N421" t="n">
+        <v>0.1476821289855715</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N421"/>
+  <dimension ref="A1:N422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12142,6 +12142,52 @@
         <v>0.1476821289855715</v>
       </c>
     </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-07-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>146000</v>
+      </c>
+      <c r="C422" t="n">
+        <v>21515.2</v>
+      </c>
+      <c r="D422" t="n">
+        <v>19040</v>
+      </c>
+      <c r="E422" t="n">
+        <v>105525</v>
+      </c>
+      <c r="F422" t="n">
+        <v>15550.63</v>
+      </c>
+      <c r="G422" t="n">
+        <v>13761.62</v>
+      </c>
+      <c r="H422" t="n">
+        <v>23630</v>
+      </c>
+      <c r="I422" t="n">
+        <v>3482.22</v>
+      </c>
+      <c r="J422" t="n">
+        <v>3081.61</v>
+      </c>
+      <c r="K422" t="n">
+        <v>107500</v>
+      </c>
+      <c r="L422" t="n">
+        <v>15841.67</v>
+      </c>
+      <c r="M422" t="n">
+        <v>14019.18</v>
+      </c>
+      <c r="N422" t="n">
+        <v>0.1477912596249058</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N422"/>
+  <dimension ref="A1:N423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12188,6 +12188,52 @@
         <v>0.1477912596249058</v>
       </c>
     </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-07-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>143000</v>
+      </c>
+      <c r="C423" t="n">
+        <v>21123.85</v>
+      </c>
+      <c r="D423" t="n">
+        <v>18693.67</v>
+      </c>
+      <c r="E423" t="n">
+        <v>105990</v>
+      </c>
+      <c r="F423" t="n">
+        <v>15656.76</v>
+      </c>
+      <c r="G423" t="n">
+        <v>13855.54</v>
+      </c>
+      <c r="H423" t="n">
+        <v>23630</v>
+      </c>
+      <c r="I423" t="n">
+        <v>3490.61</v>
+      </c>
+      <c r="J423" t="n">
+        <v>3089.03</v>
+      </c>
+      <c r="K423" t="n">
+        <v>107500</v>
+      </c>
+      <c r="L423" t="n">
+        <v>15879.82</v>
+      </c>
+      <c r="M423" t="n">
+        <v>14052.93</v>
+      </c>
+      <c r="N423" t="n">
+        <v>0.1480319156810208</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N423"/>
+  <dimension ref="A1:N424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12234,6 +12234,52 @@
         <v>0.1480319156810208</v>
       </c>
     </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>143000</v>
+      </c>
+      <c r="C424" t="n">
+        <v>21123.85</v>
+      </c>
+      <c r="D424" t="n">
+        <v>18693.67</v>
+      </c>
+      <c r="E424" t="n">
+        <v>105990</v>
+      </c>
+      <c r="F424" t="n">
+        <v>15656.76</v>
+      </c>
+      <c r="G424" t="n">
+        <v>13855.54</v>
+      </c>
+      <c r="H424" t="n">
+        <v>23630</v>
+      </c>
+      <c r="I424" t="n">
+        <v>3490.61</v>
+      </c>
+      <c r="J424" t="n">
+        <v>3089.03</v>
+      </c>
+      <c r="K424" t="n">
+        <v>107500</v>
+      </c>
+      <c r="L424" t="n">
+        <v>15879.82</v>
+      </c>
+      <c r="M424" t="n">
+        <v>14052.93</v>
+      </c>
+      <c r="N424" t="n">
+        <v>0.1481196214062477</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N424"/>
+  <dimension ref="A1:N425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12280,6 +12280,52 @@
         <v>0.1481196214062477</v>
       </c>
     </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-08-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>143000</v>
+      </c>
+      <c r="C425" t="n">
+        <v>21123.85</v>
+      </c>
+      <c r="D425" t="n">
+        <v>18693.67</v>
+      </c>
+      <c r="E425" t="n">
+        <v>105990</v>
+      </c>
+      <c r="F425" t="n">
+        <v>15656.76</v>
+      </c>
+      <c r="G425" t="n">
+        <v>13855.54</v>
+      </c>
+      <c r="H425" t="n">
+        <v>23630</v>
+      </c>
+      <c r="I425" t="n">
+        <v>3490.61</v>
+      </c>
+      <c r="J425" t="n">
+        <v>3089.03</v>
+      </c>
+      <c r="K425" t="n">
+        <v>107500</v>
+      </c>
+      <c r="L425" t="n">
+        <v>15879.82</v>
+      </c>
+      <c r="M425" t="n">
+        <v>14052.93</v>
+      </c>
+      <c r="N425" t="n">
+        <v>0.1481196214062477</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N425"/>
+  <dimension ref="A1:N426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12326,6 +12326,52 @@
         <v>0.1481196214062477</v>
       </c>
     </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-08-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>140000</v>
+      </c>
+      <c r="C426" t="n">
+        <v>20677.94</v>
+      </c>
+      <c r="D426" t="n">
+        <v>18299.06</v>
+      </c>
+      <c r="E426" t="n">
+        <v>106065</v>
+      </c>
+      <c r="F426" t="n">
+        <v>15665.76</v>
+      </c>
+      <c r="G426" t="n">
+        <v>13863.5</v>
+      </c>
+      <c r="H426" t="n">
+        <v>23500</v>
+      </c>
+      <c r="I426" t="n">
+        <v>3470.94</v>
+      </c>
+      <c r="J426" t="n">
+        <v>3071.63</v>
+      </c>
+      <c r="K426" t="n">
+        <v>107500</v>
+      </c>
+      <c r="L426" t="n">
+        <v>15877.7</v>
+      </c>
+      <c r="M426" t="n">
+        <v>14051.07</v>
+      </c>
+      <c r="N426" t="n">
+        <v>0.1481196214062477</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N426"/>
+  <dimension ref="A1:N427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12372,6 +12372,52 @@
         <v>0.1481196214062477</v>
       </c>
     </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-08-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>140000</v>
+      </c>
+      <c r="C427" t="n">
+        <v>20669.09</v>
+      </c>
+      <c r="D427" t="n">
+        <v>18291.23</v>
+      </c>
+      <c r="E427" t="n">
+        <v>106880</v>
+      </c>
+      <c r="F427" t="n">
+        <v>15779.37</v>
+      </c>
+      <c r="G427" t="n">
+        <v>13964.05</v>
+      </c>
+      <c r="H427" t="n">
+        <v>23730</v>
+      </c>
+      <c r="I427" t="n">
+        <v>3503.41</v>
+      </c>
+      <c r="J427" t="n">
+        <v>3100.36</v>
+      </c>
+      <c r="K427" t="n">
+        <v>107500</v>
+      </c>
+      <c r="L427" t="n">
+        <v>15870.91</v>
+      </c>
+      <c r="M427" t="n">
+        <v>14045.05</v>
+      </c>
+      <c r="N427" t="n">
+        <v>0.1480911056481948</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N427"/>
+  <dimension ref="A1:N428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12418,6 +12418,52 @@
         <v>0.1480911056481948</v>
       </c>
     </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>140250</v>
+      </c>
+      <c r="C428" t="n">
+        <v>20734.47</v>
+      </c>
+      <c r="D428" t="n">
+        <v>18349.08</v>
+      </c>
+      <c r="E428" t="n">
+        <v>107275</v>
+      </c>
+      <c r="F428" t="n">
+        <v>15859.46</v>
+      </c>
+      <c r="G428" t="n">
+        <v>14034.92</v>
+      </c>
+      <c r="H428" t="n">
+        <v>23690</v>
+      </c>
+      <c r="I428" t="n">
+        <v>3502.31</v>
+      </c>
+      <c r="J428" t="n">
+        <v>3099.39</v>
+      </c>
+      <c r="K428" t="n">
+        <v>107500</v>
+      </c>
+      <c r="L428" t="n">
+        <v>15892.73</v>
+      </c>
+      <c r="M428" t="n">
+        <v>14064.36</v>
+      </c>
+      <c r="N428" t="n">
+        <v>0.1480691779199242</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N428"/>
+  <dimension ref="A1:N429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12464,6 +12464,52 @@
         <v>0.1480691779199242</v>
       </c>
     </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-08-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>141500</v>
+      </c>
+      <c r="C429" t="n">
+        <v>20915.55</v>
+      </c>
+      <c r="D429" t="n">
+        <v>18509.34</v>
+      </c>
+      <c r="E429" t="n">
+        <v>108060</v>
+      </c>
+      <c r="F429" t="n">
+        <v>15972.68</v>
+      </c>
+      <c r="G429" t="n">
+        <v>14135.12</v>
+      </c>
+      <c r="H429" t="n">
+        <v>23800</v>
+      </c>
+      <c r="I429" t="n">
+        <v>3517.95</v>
+      </c>
+      <c r="J429" t="n">
+        <v>3113.23</v>
+      </c>
+      <c r="K429" t="n">
+        <v>107500</v>
+      </c>
+      <c r="L429" t="n">
+        <v>15889.91</v>
+      </c>
+      <c r="M429" t="n">
+        <v>14061.87</v>
+      </c>
+      <c r="N429" t="n">
+        <v>0.1481481481481481</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N429"/>
+  <dimension ref="A1:N430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12510,6 +12510,52 @@
         <v>0.1481481481481481</v>
       </c>
     </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-08-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>142750</v>
+      </c>
+      <c r="C430" t="n">
+        <v>21094.71</v>
+      </c>
+      <c r="D430" t="n">
+        <v>18667.88</v>
+      </c>
+      <c r="E430" t="n">
+        <v>108420</v>
+      </c>
+      <c r="F430" t="n">
+        <v>16021.63</v>
+      </c>
+      <c r="G430" t="n">
+        <v>14178.44</v>
+      </c>
+      <c r="H430" t="n">
+        <v>23980</v>
+      </c>
+      <c r="I430" t="n">
+        <v>3543.62</v>
+      </c>
+      <c r="J430" t="n">
+        <v>3135.94</v>
+      </c>
+      <c r="K430" t="n">
+        <v>107500</v>
+      </c>
+      <c r="L430" t="n">
+        <v>15885.68</v>
+      </c>
+      <c r="M430" t="n">
+        <v>14058.13</v>
+      </c>
+      <c r="N430" t="n">
+        <v>0.1481700992739665</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N430"/>
+  <dimension ref="A1:N431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12556,6 +12556,52 @@
         <v>0.1481700992739665</v>
       </c>
     </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-08-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>142750</v>
+      </c>
+      <c r="C431" t="n">
+        <v>21094.71</v>
+      </c>
+      <c r="D431" t="n">
+        <v>18667.88</v>
+      </c>
+      <c r="E431" t="n">
+        <v>108420</v>
+      </c>
+      <c r="F431" t="n">
+        <v>16021.63</v>
+      </c>
+      <c r="G431" t="n">
+        <v>14178.44</v>
+      </c>
+      <c r="H431" t="n">
+        <v>23980</v>
+      </c>
+      <c r="I431" t="n">
+        <v>3543.62</v>
+      </c>
+      <c r="J431" t="n">
+        <v>3135.94</v>
+      </c>
+      <c r="K431" t="n">
+        <v>107500</v>
+      </c>
+      <c r="L431" t="n">
+        <v>15885.68</v>
+      </c>
+      <c r="M431" t="n">
+        <v>14058.13</v>
+      </c>
+      <c r="N431" t="n">
+        <v>0.1482008417807813</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N431"/>
+  <dimension ref="A1:N432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12602,6 +12602,52 @@
         <v>0.1482008417807813</v>
       </c>
     </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-08-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>142750</v>
+      </c>
+      <c r="C432" t="n">
+        <v>21094.71</v>
+      </c>
+      <c r="D432" t="n">
+        <v>18667.88</v>
+      </c>
+      <c r="E432" t="n">
+        <v>108420</v>
+      </c>
+      <c r="F432" t="n">
+        <v>16021.63</v>
+      </c>
+      <c r="G432" t="n">
+        <v>14178.44</v>
+      </c>
+      <c r="H432" t="n">
+        <v>23980</v>
+      </c>
+      <c r="I432" t="n">
+        <v>3543.62</v>
+      </c>
+      <c r="J432" t="n">
+        <v>3135.94</v>
+      </c>
+      <c r="K432" t="n">
+        <v>107500</v>
+      </c>
+      <c r="L432" t="n">
+        <v>15885.68</v>
+      </c>
+      <c r="M432" t="n">
+        <v>14058.13</v>
+      </c>
+      <c r="N432" t="n">
+        <v>0.1482008417807813</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N432"/>
+  <dimension ref="A1:N433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12648,6 +12648,52 @@
         <v>0.1482008417807813</v>
       </c>
     </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-08-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>144500</v>
+      </c>
+      <c r="C433" t="n">
+        <v>21367.84</v>
+      </c>
+      <c r="D433" t="n">
+        <v>18909.59</v>
+      </c>
+      <c r="E433" t="n">
+        <v>107945</v>
+      </c>
+      <c r="F433" t="n">
+        <v>15962.29</v>
+      </c>
+      <c r="G433" t="n">
+        <v>14125.92</v>
+      </c>
+      <c r="H433" t="n">
+        <v>23990</v>
+      </c>
+      <c r="I433" t="n">
+        <v>3547.5</v>
+      </c>
+      <c r="J433" t="n">
+        <v>3139.38</v>
+      </c>
+      <c r="K433" t="n">
+        <v>107500</v>
+      </c>
+      <c r="L433" t="n">
+        <v>15896.49</v>
+      </c>
+      <c r="M433" t="n">
+        <v>14067.69</v>
+      </c>
+      <c r="N433" t="n">
+        <v>0.1482008417807813</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N433"/>
+  <dimension ref="A1:N434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12694,6 +12694,52 @@
         <v>0.1482008417807813</v>
       </c>
     </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-08-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>144750</v>
+      </c>
+      <c r="C434" t="n">
+        <v>21408.29</v>
+      </c>
+      <c r="D434" t="n">
+        <v>18945.39</v>
+      </c>
+      <c r="E434" t="n">
+        <v>108615</v>
+      </c>
+      <c r="F434" t="n">
+        <v>16063.98</v>
+      </c>
+      <c r="G434" t="n">
+        <v>14215.91</v>
+      </c>
+      <c r="H434" t="n">
+        <v>24100</v>
+      </c>
+      <c r="I434" t="n">
+        <v>3564.35</v>
+      </c>
+      <c r="J434" t="n">
+        <v>3154.29</v>
+      </c>
+      <c r="K434" t="n">
+        <v>107500</v>
+      </c>
+      <c r="L434" t="n">
+        <v>15899.07</v>
+      </c>
+      <c r="M434" t="n">
+        <v>14069.98</v>
+      </c>
+      <c r="N434" t="n">
+        <v>0.1482008417807813</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N434"/>
+  <dimension ref="A1:N435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12740,6 +12740,52 @@
         <v>0.1482008417807813</v>
       </c>
     </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-08-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>160500</v>
+      </c>
+      <c r="C435" t="n">
+        <v>23818.71</v>
+      </c>
+      <c r="D435" t="n">
+        <v>21078.51</v>
+      </c>
+      <c r="E435" t="n">
+        <v>107965</v>
+      </c>
+      <c r="F435" t="n">
+        <v>16022.35</v>
+      </c>
+      <c r="G435" t="n">
+        <v>14179.07</v>
+      </c>
+      <c r="H435" t="n">
+        <v>23800</v>
+      </c>
+      <c r="I435" t="n">
+        <v>3532</v>
+      </c>
+      <c r="J435" t="n">
+        <v>3125.66</v>
+      </c>
+      <c r="K435" t="n">
+        <v>113500</v>
+      </c>
+      <c r="L435" t="n">
+        <v>16843.76</v>
+      </c>
+      <c r="M435" t="n">
+        <v>14905.98</v>
+      </c>
+      <c r="N435" t="n">
+        <v>0.1487829554246266</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N435"/>
+  <dimension ref="A1:N436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12786,6 +12786,52 @@
         <v>0.1487829554246266</v>
       </c>
     </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>157000</v>
+      </c>
+      <c r="C436" t="n">
+        <v>23298.95</v>
+      </c>
+      <c r="D436" t="n">
+        <v>20618.54</v>
+      </c>
+      <c r="E436" t="n">
+        <v>108440</v>
+      </c>
+      <c r="F436" t="n">
+        <v>16092.6</v>
+      </c>
+      <c r="G436" t="n">
+        <v>14241.24</v>
+      </c>
+      <c r="H436" t="n">
+        <v>23740</v>
+      </c>
+      <c r="I436" t="n">
+        <v>3523.04</v>
+      </c>
+      <c r="J436" t="n">
+        <v>3117.73</v>
+      </c>
+      <c r="K436" t="n">
+        <v>115000</v>
+      </c>
+      <c r="L436" t="n">
+        <v>17066.11</v>
+      </c>
+      <c r="M436" t="n">
+        <v>15102.75</v>
+      </c>
+      <c r="N436" t="n">
+        <v>0.148760822349826</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N436"/>
+  <dimension ref="A1:N437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12832,6 +12832,50 @@
         <v>0.148760822349826</v>
       </c>
     </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>152750</v>
+      </c>
+      <c r="C437" t="n">
+        <v>22674.31</v>
+      </c>
+      <c r="D437" t="n">
+        <v>20065.76</v>
+      </c>
+      <c r="E437" t="n">
+        <v>109575</v>
+      </c>
+      <c r="F437" t="n">
+        <v>16265.38</v>
+      </c>
+      <c r="G437" t="n">
+        <v>14394.14</v>
+      </c>
+      <c r="H437" t="n">
+        <v>23870</v>
+      </c>
+      <c r="I437" t="n">
+        <v>3543.28</v>
+      </c>
+      <c r="J437" t="n">
+        <v>3135.64</v>
+      </c>
+      <c r="K437" t="n">
+        <v>118000</v>
+      </c>
+      <c r="L437" t="n">
+        <v>17515.99</v>
+      </c>
+      <c r="M437" t="n">
+        <v>15500.88</v>
+      </c>
+      <c r="N437" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N437"/>
+  <dimension ref="A1:N438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12876,6 +12876,52 @@
       </c>
       <c r="N437" t="inlineStr"/>
     </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>152500</v>
+      </c>
+      <c r="C438" t="n">
+        <v>22628.8</v>
+      </c>
+      <c r="D438" t="n">
+        <v>20025.49</v>
+      </c>
+      <c r="E438" t="n">
+        <v>109370</v>
+      </c>
+      <c r="F438" t="n">
+        <v>16228.93</v>
+      </c>
+      <c r="G438" t="n">
+        <v>14361.88</v>
+      </c>
+      <c r="H438" t="n">
+        <v>23920</v>
+      </c>
+      <c r="I438" t="n">
+        <v>3549.38</v>
+      </c>
+      <c r="J438" t="n">
+        <v>3141.05</v>
+      </c>
+      <c r="K438" t="n">
+        <v>119000</v>
+      </c>
+      <c r="L438" t="n">
+        <v>17657.88</v>
+      </c>
+      <c r="M438" t="n">
+        <v>15626.44</v>
+      </c>
+      <c r="N438" t="n">
+        <v>0.1487497582816428</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N438"/>
+  <dimension ref="A1:N439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12922,6 +12922,52 @@
         <v>0.1487497582816428</v>
       </c>
     </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-08-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>153000</v>
+      </c>
+      <c r="C439" t="n">
+        <v>22710.41</v>
+      </c>
+      <c r="D439" t="n">
+        <v>20097.7</v>
+      </c>
+      <c r="E439" t="n">
+        <v>109595</v>
+      </c>
+      <c r="F439" t="n">
+        <v>16267.63</v>
+      </c>
+      <c r="G439" t="n">
+        <v>14396.13</v>
+      </c>
+      <c r="H439" t="n">
+        <v>23900</v>
+      </c>
+      <c r="I439" t="n">
+        <v>3547.57</v>
+      </c>
+      <c r="J439" t="n">
+        <v>3139.44</v>
+      </c>
+      <c r="K439" t="n">
+        <v>120000</v>
+      </c>
+      <c r="L439" t="n">
+        <v>17812.08</v>
+      </c>
+      <c r="M439" t="n">
+        <v>15762.9</v>
+      </c>
+      <c r="N439" t="n">
+        <v>0.1488117382699147</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N439"/>
+  <dimension ref="A1:N440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12968,6 +12968,50 @@
         <v>0.1488117382699147</v>
       </c>
     </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>153000</v>
+      </c>
+      <c r="C440" t="n">
+        <v>22710.41</v>
+      </c>
+      <c r="D440" t="n">
+        <v>20097.7</v>
+      </c>
+      <c r="E440" t="n">
+        <v>109595</v>
+      </c>
+      <c r="F440" t="n">
+        <v>16267.63</v>
+      </c>
+      <c r="G440" t="n">
+        <v>14396.13</v>
+      </c>
+      <c r="H440" t="n">
+        <v>23900</v>
+      </c>
+      <c r="I440" t="n">
+        <v>3547.57</v>
+      </c>
+      <c r="J440" t="n">
+        <v>3139.44</v>
+      </c>
+      <c r="K440" t="n">
+        <v>120000</v>
+      </c>
+      <c r="L440" t="n">
+        <v>17812.08</v>
+      </c>
+      <c r="M440" t="n">
+        <v>15762.9</v>
+      </c>
+      <c r="N440" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N440"/>
+  <dimension ref="A1:N441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13012,6 +13012,52 @@
       </c>
       <c r="N440" t="inlineStr"/>
     </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-08-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>153000</v>
+      </c>
+      <c r="C441" t="n">
+        <v>22710.41</v>
+      </c>
+      <c r="D441" t="n">
+        <v>20097.7</v>
+      </c>
+      <c r="E441" t="n">
+        <v>109595</v>
+      </c>
+      <c r="F441" t="n">
+        <v>16267.63</v>
+      </c>
+      <c r="G441" t="n">
+        <v>14396.13</v>
+      </c>
+      <c r="H441" t="n">
+        <v>23900</v>
+      </c>
+      <c r="I441" t="n">
+        <v>3547.57</v>
+      </c>
+      <c r="J441" t="n">
+        <v>3139.44</v>
+      </c>
+      <c r="K441" t="n">
+        <v>120000</v>
+      </c>
+      <c r="L441" t="n">
+        <v>17812.08</v>
+      </c>
+      <c r="M441" t="n">
+        <v>15762.9</v>
+      </c>
+      <c r="N441" t="n">
+        <v>0.1486590949634299</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N441"/>
+  <dimension ref="A1:N442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13058,6 +13058,52 @@
         <v>0.1486590949634299</v>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-08-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>158500</v>
+      </c>
+      <c r="C442" t="n">
+        <v>23493.66</v>
+      </c>
+      <c r="D442" t="n">
+        <v>20790.85</v>
+      </c>
+      <c r="E442" t="n">
+        <v>109410</v>
+      </c>
+      <c r="F442" t="n">
+        <v>16217.3</v>
+      </c>
+      <c r="G442" t="n">
+        <v>14351.59</v>
+      </c>
+      <c r="H442" t="n">
+        <v>23970</v>
+      </c>
+      <c r="I442" t="n">
+        <v>3552.95</v>
+      </c>
+      <c r="J442" t="n">
+        <v>3144.21</v>
+      </c>
+      <c r="K442" t="n">
+        <v>120000</v>
+      </c>
+      <c r="L442" t="n">
+        <v>17787</v>
+      </c>
+      <c r="M442" t="n">
+        <v>15740.71</v>
+      </c>
+      <c r="N442" t="n">
+        <v>0.1486590949634299</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N442"/>
+  <dimension ref="A1:N443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13104,6 +13104,52 @@
         <v>0.1486590949634299</v>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-09-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>160000</v>
+      </c>
+      <c r="C443" t="n">
+        <v>23752.62</v>
+      </c>
+      <c r="D443" t="n">
+        <v>21020.01</v>
+      </c>
+      <c r="E443" t="n">
+        <v>110420</v>
+      </c>
+      <c r="F443" t="n">
+        <v>16392.27</v>
+      </c>
+      <c r="G443" t="n">
+        <v>14506.44</v>
+      </c>
+      <c r="H443" t="n">
+        <v>24110</v>
+      </c>
+      <c r="I443" t="n">
+        <v>3579.22</v>
+      </c>
+      <c r="J443" t="n">
+        <v>3167.45</v>
+      </c>
+      <c r="K443" t="n">
+        <v>120000</v>
+      </c>
+      <c r="L443" t="n">
+        <v>17814.46</v>
+      </c>
+      <c r="M443" t="n">
+        <v>15765.01</v>
+      </c>
+      <c r="N443" t="n">
+        <v>0.1488050950864558</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N443"/>
+  <dimension ref="A1:N444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13150,6 +13150,52 @@
         <v>0.1488050950864558</v>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>156500</v>
+      </c>
+      <c r="C444" t="n">
+        <v>23229.58</v>
+      </c>
+      <c r="D444" t="n">
+        <v>20557.15</v>
+      </c>
+      <c r="E444" t="n">
+        <v>108755</v>
+      </c>
+      <c r="F444" t="n">
+        <v>16142.7</v>
+      </c>
+      <c r="G444" t="n">
+        <v>14285.58</v>
+      </c>
+      <c r="H444" t="n">
+        <v>24080</v>
+      </c>
+      <c r="I444" t="n">
+        <v>3574.24</v>
+      </c>
+      <c r="J444" t="n">
+        <v>3163.04</v>
+      </c>
+      <c r="K444" t="n">
+        <v>120000</v>
+      </c>
+      <c r="L444" t="n">
+        <v>17811.82</v>
+      </c>
+      <c r="M444" t="n">
+        <v>15762.67</v>
+      </c>
+      <c r="N444" t="n">
+        <v>0.1487895966314035</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N444"/>
+  <dimension ref="A1:N445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13196,6 +13196,52 @@
         <v>0.1487895966314035</v>
       </c>
     </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>156000</v>
+      </c>
+      <c r="C445" t="n">
+        <v>23160.86</v>
+      </c>
+      <c r="D445" t="n">
+        <v>20496.34</v>
+      </c>
+      <c r="E445" t="n">
+        <v>109345</v>
+      </c>
+      <c r="F445" t="n">
+        <v>16234.13</v>
+      </c>
+      <c r="G445" t="n">
+        <v>14366.49</v>
+      </c>
+      <c r="H445" t="n">
+        <v>24350</v>
+      </c>
+      <c r="I445" t="n">
+        <v>3615.17</v>
+      </c>
+      <c r="J445" t="n">
+        <v>3199.27</v>
+      </c>
+      <c r="K445" t="n">
+        <v>120000</v>
+      </c>
+      <c r="L445" t="n">
+        <v>17816.05</v>
+      </c>
+      <c r="M445" t="n">
+        <v>15766.42</v>
+      </c>
+      <c r="N445" t="n">
+        <v>0.1488272413382546</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N445"/>
+  <dimension ref="A1:N446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13242,6 +13242,52 @@
         <v>0.1488272413382546</v>
       </c>
     </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>152000</v>
+      </c>
+      <c r="C446" t="n">
+        <v>22564.99</v>
+      </c>
+      <c r="D446" t="n">
+        <v>19969.01</v>
+      </c>
+      <c r="E446" t="n">
+        <v>109975</v>
+      </c>
+      <c r="F446" t="n">
+        <v>16326.21</v>
+      </c>
+      <c r="G446" t="n">
+        <v>14447.98</v>
+      </c>
+      <c r="H446" t="n">
+        <v>24360</v>
+      </c>
+      <c r="I446" t="n">
+        <v>3616.34</v>
+      </c>
+      <c r="J446" t="n">
+        <v>3200.3</v>
+      </c>
+      <c r="K446" t="n">
+        <v>120000</v>
+      </c>
+      <c r="L446" t="n">
+        <v>17814.46</v>
+      </c>
+      <c r="M446" t="n">
+        <v>15765.01</v>
+      </c>
+      <c r="N446" t="n">
+        <v>0.1488804192472606</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N446"/>
+  <dimension ref="A1:N447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13288,6 +13288,52 @@
         <v>0.1488804192472606</v>
       </c>
     </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>152000</v>
+      </c>
+      <c r="C447" t="n">
+        <v>22564.99</v>
+      </c>
+      <c r="D447" t="n">
+        <v>19969.01</v>
+      </c>
+      <c r="E447" t="n">
+        <v>109975</v>
+      </c>
+      <c r="F447" t="n">
+        <v>16326.21</v>
+      </c>
+      <c r="G447" t="n">
+        <v>14447.98</v>
+      </c>
+      <c r="H447" t="n">
+        <v>24360</v>
+      </c>
+      <c r="I447" t="n">
+        <v>3616.34</v>
+      </c>
+      <c r="J447" t="n">
+        <v>3200.3</v>
+      </c>
+      <c r="K447" t="n">
+        <v>120000</v>
+      </c>
+      <c r="L447" t="n">
+        <v>17814.46</v>
+      </c>
+      <c r="M447" t="n">
+        <v>15765.01</v>
+      </c>
+      <c r="N447" t="n">
+        <v>0.1490024287395885</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
